--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128815136</v>
+        <v>128813071</v>
       </c>
       <c r="B2" t="n">
-        <v>86954</v>
+        <v>86976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717412</v>
+        <v>717455</v>
       </c>
       <c r="R2" t="n">
-        <v>6373217</v>
+        <v>6373115</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,75 +743,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128806033</v>
+        <v>128815135</v>
       </c>
       <c r="B3" t="n">
-        <v>86954</v>
+        <v>86756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717315</v>
+        <v>717476</v>
       </c>
       <c r="R3" t="n">
-        <v>6373232</v>
+        <v>6373242</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,51 +861,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128813034</v>
+        <v>128805999</v>
       </c>
       <c r="B4" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -906,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717425</v>
+        <v>717287</v>
       </c>
       <c r="R4" t="n">
-        <v>6373083</v>
+        <v>6373354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,19 +947,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,44 +964,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128813071</v>
+        <v>128806048</v>
       </c>
       <c r="B5" t="n">
-        <v>86976</v>
+        <v>90916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>449</v>
+        <v>4188</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717455</v>
+        <v>717322</v>
       </c>
       <c r="R5" t="n">
-        <v>6373115</v>
+        <v>6373213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,19 +1044,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128815135</v>
+        <v>128806348</v>
       </c>
       <c r="B6" t="n">
-        <v>86756</v>
+        <v>86917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,34 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717476</v>
+        <v>717239</v>
       </c>
       <c r="R6" t="n">
-        <v>6373242</v>
+        <v>6373234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,19 +1158,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128805999</v>
+        <v>128815113</v>
       </c>
       <c r="B7" t="n">
         <v>86999</v>
@@ -1213,14 +1201,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717287</v>
+        <v>717317</v>
       </c>
       <c r="R7" t="n">
-        <v>6373354</v>
+        <v>6373308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806048</v>
+        <v>128806072</v>
       </c>
       <c r="B8" t="n">
-        <v>90916</v>
+        <v>86917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1290,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717322</v>
+        <v>717289</v>
       </c>
       <c r="R8" t="n">
-        <v>6373213</v>
+        <v>6373288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128806348</v>
+        <v>128813022</v>
       </c>
       <c r="B9" t="n">
-        <v>86917</v>
+        <v>92796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1387,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1411,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717239</v>
+        <v>717130</v>
       </c>
       <c r="R9" t="n">
-        <v>6373234</v>
+        <v>6373194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,9 +1432,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,57 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128815113</v>
+        <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>86999</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717317</v>
+        <v>717370</v>
       </c>
       <c r="R10" t="n">
-        <v>6373308</v>
+        <v>6373322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,57 +1556,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128806072</v>
+        <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717289</v>
+        <v>717412</v>
       </c>
       <c r="R11" t="n">
-        <v>6373288</v>
+        <v>6373217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,50 +1647,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128813022</v>
+        <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>92796</v>
+        <v>86954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717130</v>
+        <v>717315</v>
       </c>
       <c r="R12" t="n">
-        <v>6373194</v>
+        <v>6373232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1735,71 +1734,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128806006</v>
+        <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>92429</v>
+        <v>86954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717370</v>
+        <v>717425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373322</v>
+        <v>6373083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,9 +1832,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,12 +1859,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128815145</v>
+        <v>128806343</v>
       </c>
       <c r="B17" t="n">
-        <v>86920</v>
+        <v>86709</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,34 +2173,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037417</v>
+        <v>249278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717299</v>
+        <v>717258</v>
       </c>
       <c r="R17" t="n">
-        <v>6373241</v>
+        <v>6373299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,6 +2238,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2248,22 +2256,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128806343</v>
+        <v>128815145</v>
       </c>
       <c r="B18" t="n">
-        <v>86709</v>
+        <v>86920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,37 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>249278</v>
+        <v>6037417</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717258</v>
+        <v>717299</v>
       </c>
       <c r="R18" t="n">
-        <v>6373299</v>
+        <v>6373241</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,11 +2341,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2354,12 +2354,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2580,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813032</v>
+        <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717409</v>
+        <v>717316</v>
       </c>
       <c r="R21" t="n">
-        <v>6373057</v>
+        <v>6373307</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,19 +2648,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,57 +2665,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128806311</v>
+        <v>128815134</v>
       </c>
       <c r="B22" t="n">
-        <v>86999</v>
+        <v>86756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>717316</v>
       </c>
       <c r="R22" t="n">
-        <v>6373307</v>
+        <v>6373365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,57 +2762,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128815134</v>
+        <v>128813032</v>
       </c>
       <c r="B23" t="n">
-        <v>86756</v>
+        <v>86954</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717316</v>
+        <v>717409</v>
       </c>
       <c r="R23" t="n">
-        <v>6373365</v>
+        <v>6373057</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,9 +2842,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2869,12 +2869,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3175,45 +3175,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128815122</v>
+        <v>128806042</v>
       </c>
       <c r="B27" t="n">
-        <v>86999</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717534</v>
+        <v>717134</v>
       </c>
       <c r="R27" t="n">
-        <v>6373182</v>
+        <v>6373159</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3254,50 +3263,51 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128805998</v>
+        <v>128813051</v>
       </c>
       <c r="B28" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717299</v>
+        <v>717385</v>
       </c>
       <c r="R28" t="n">
-        <v>6373359</v>
+        <v>6373091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3340,9 +3350,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3357,12 +3377,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3476,45 +3496,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128813051</v>
+        <v>128815122</v>
       </c>
       <c r="B30" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717385</v>
+        <v>717534</v>
       </c>
       <c r="R30" t="n">
-        <v>6373091</v>
+        <v>6373182</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3544,19 +3564,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3571,66 +3581,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128806042</v>
+        <v>128805998</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>86999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>3767</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717134</v>
+        <v>717299</v>
       </c>
       <c r="R31" t="n">
-        <v>6373159</v>
+        <v>6373359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,7 +3672,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3690,45 +3690,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128815154</v>
+        <v>128813070</v>
       </c>
       <c r="B32" t="n">
-        <v>86917</v>
+        <v>86976</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717416</v>
+        <v>717323</v>
       </c>
       <c r="R32" t="n">
-        <v>6373159</v>
+        <v>6373241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,9 +3758,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,44 +3785,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128806349</v>
+        <v>128813068</v>
       </c>
       <c r="B33" t="n">
-        <v>86917</v>
+        <v>86976</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3822,10 +3832,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717337</v>
+        <v>717085</v>
       </c>
       <c r="R33" t="n">
-        <v>6373337</v>
+        <v>6373275</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3855,9 +3865,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3872,19 +3892,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128806351</v>
+        <v>128815154</v>
       </c>
       <c r="B34" t="n">
         <v>86917</v>
@@ -3915,14 +3935,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717390</v>
+        <v>717416</v>
       </c>
       <c r="R34" t="n">
-        <v>6373317</v>
+        <v>6373159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,44 +3989,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806002</v>
+        <v>128806349</v>
       </c>
       <c r="B35" t="n">
-        <v>86999</v>
+        <v>86917</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4016,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717297</v>
+        <v>717337</v>
       </c>
       <c r="R35" t="n">
-        <v>6373295</v>
+        <v>6373337</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,44 +4086,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128806025</v>
+        <v>128806351</v>
       </c>
       <c r="B36" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4113,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717284</v>
+        <v>717390</v>
       </c>
       <c r="R36" t="n">
-        <v>6373347</v>
+        <v>6373317</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4157,49 +4177,52 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128806317</v>
+        <v>128806002</v>
       </c>
       <c r="B37" t="n">
-        <v>92798</v>
+        <v>86999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6047725</v>
+        <v>3767</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4207,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717367</v>
+        <v>717297</v>
       </c>
       <c r="R37" t="n">
-        <v>6373322</v>
+        <v>6373295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4251,51 +4274,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128813070</v>
+        <v>128806025</v>
       </c>
       <c r="B38" t="n">
-        <v>86976</v>
+        <v>86954</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4305,10 +4327,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717323</v>
+        <v>717284</v>
       </c>
       <c r="R38" t="n">
-        <v>6373241</v>
+        <v>6373347</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4338,73 +4360,60 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128813068</v>
+        <v>128806317</v>
       </c>
       <c r="B39" t="n">
-        <v>86976</v>
+        <v>92798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>449</v>
+        <v>6047725</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4412,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717085</v>
+        <v>717367</v>
       </c>
       <c r="R39" t="n">
-        <v>6373275</v>
+        <v>6373322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,39 +4454,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4591,32 +4591,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128815143</v>
+        <v>128815140</v>
       </c>
       <c r="B41" t="n">
-        <v>90955</v>
+        <v>86976</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3286</v>
+        <v>449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717335</v>
+        <v>717460</v>
       </c>
       <c r="R41" t="n">
-        <v>6373383</v>
+        <v>6373180</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4688,32 +4688,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815140</v>
+        <v>128815143</v>
       </c>
       <c r="B42" t="n">
-        <v>86976</v>
+        <v>90955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>3286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717460</v>
+        <v>717335</v>
       </c>
       <c r="R42" t="n">
-        <v>6373180</v>
+        <v>6373383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,32 +5087,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128813067</v>
+        <v>128806053</v>
       </c>
       <c r="B46" t="n">
-        <v>86976</v>
+        <v>86780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717325</v>
+        <v>717382</v>
       </c>
       <c r="R46" t="n">
-        <v>6373229</v>
+        <v>6373309</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,19 +5155,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5182,22 +5172,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128806053</v>
+        <v>128806345</v>
       </c>
       <c r="B47" t="n">
-        <v>86780</v>
+        <v>86917</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5205,21 +5195,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5229,10 +5219,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717382</v>
+        <v>717170</v>
       </c>
       <c r="R47" t="n">
-        <v>6373309</v>
+        <v>6373195</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5279,44 +5269,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128806345</v>
+        <v>128813046</v>
       </c>
       <c r="B48" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5316,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717170</v>
+        <v>717216</v>
       </c>
       <c r="R48" t="n">
-        <v>6373195</v>
+        <v>6373176</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5359,9 +5349,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5376,19 +5376,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128813046</v>
+        <v>128813040</v>
       </c>
       <c r="B49" t="n">
         <v>86954</v>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717216</v>
+        <v>717487</v>
       </c>
       <c r="R49" t="n">
-        <v>6373176</v>
+        <v>6373202</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5495,32 +5495,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128813040</v>
+        <v>128813067</v>
       </c>
       <c r="B50" t="n">
-        <v>86954</v>
+        <v>86976</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717487</v>
+        <v>717325</v>
       </c>
       <c r="R50" t="n">
-        <v>6373202</v>
+        <v>6373229</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5602,10 +5602,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128815131</v>
+        <v>128815141</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>86976</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5613,21 +5613,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717416</v>
+        <v>717505</v>
       </c>
       <c r="R51" t="n">
-        <v>6373162</v>
+        <v>6373241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,18 +5675,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5705,10 +5699,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128815141</v>
+        <v>128815131</v>
       </c>
       <c r="B52" t="n">
-        <v>86976</v>
+        <v>91030</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5716,21 +5710,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5740,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717505</v>
+        <v>717416</v>
       </c>
       <c r="R52" t="n">
-        <v>6373241</v>
+        <v>6373162</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5778,12 +5772,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128806322</v>
+        <v>128806330</v>
       </c>
       <c r="B62" t="n">
-        <v>86954</v>
+        <v>107533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6697,21 +6697,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717234</v>
+        <v>717069</v>
       </c>
       <c r="R62" t="n">
-        <v>6373222</v>
+        <v>6373282</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6765,7 +6765,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6784,10 +6783,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128806330</v>
+        <v>128806322</v>
       </c>
       <c r="B63" t="n">
-        <v>107533</v>
+        <v>86954</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6795,21 +6794,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6819,10 +6818,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717069</v>
+        <v>717234</v>
       </c>
       <c r="R63" t="n">
-        <v>6373282</v>
+        <v>6373222</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6863,6 +6862,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128806326</v>
+        <v>128813066</v>
       </c>
       <c r="B64" t="n">
-        <v>86930</v>
+        <v>86976</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1988</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717084</v>
+        <v>717515</v>
       </c>
       <c r="R64" t="n">
-        <v>6373294</v>
+        <v>6373166</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,9 +6949,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6966,19 +6976,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128813066</v>
+        <v>128806333</v>
       </c>
       <c r="B65" t="n">
         <v>86976</v>
@@ -7013,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717515</v>
+        <v>717331</v>
       </c>
       <c r="R65" t="n">
-        <v>6373166</v>
+        <v>6373327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7046,19 +7056,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,44 +7073,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128806333</v>
+        <v>128806326</v>
       </c>
       <c r="B66" t="n">
-        <v>86976</v>
+        <v>86930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717331</v>
+        <v>717084</v>
       </c>
       <c r="R66" t="n">
-        <v>6373327</v>
+        <v>6373294</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7182,32 +7182,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813079</v>
+        <v>128813044</v>
       </c>
       <c r="B67" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717315</v>
+        <v>717135</v>
       </c>
       <c r="R67" t="n">
-        <v>6373221</v>
+        <v>6373174</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7289,32 +7289,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128806350</v>
+        <v>128806036</v>
       </c>
       <c r="B68" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717330</v>
+        <v>717449</v>
       </c>
       <c r="R68" t="n">
-        <v>6373328</v>
+        <v>6373281</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,50 +7368,51 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128813012</v>
+        <v>128813079</v>
       </c>
       <c r="B69" t="n">
-        <v>86999</v>
+        <v>86917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7421,10 +7422,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717435</v>
+        <v>717315</v>
       </c>
       <c r="R69" t="n">
-        <v>6373156</v>
+        <v>6373221</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7456,7 +7457,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7466,7 +7467,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7493,48 +7494,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806342</v>
+        <v>128806350</v>
       </c>
       <c r="B70" t="n">
-        <v>86709</v>
+        <v>86917</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717179</v>
+        <v>717330</v>
       </c>
       <c r="R70" t="n">
-        <v>6373227</v>
+        <v>6373328</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7569,18 +7567,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7599,32 +7591,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128813044</v>
+        <v>128813012</v>
       </c>
       <c r="B71" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7626,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717135</v>
+        <v>717435</v>
       </c>
       <c r="R71" t="n">
-        <v>6373174</v>
+        <v>6373156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7669,7 +7661,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7679,7 +7671,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7706,10 +7698,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806036</v>
+        <v>128806342</v>
       </c>
       <c r="B72" t="n">
-        <v>86954</v>
+        <v>86709</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7717,34 +7709,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717449</v>
+        <v>717179</v>
       </c>
       <c r="R72" t="n">
-        <v>6373281</v>
+        <v>6373227</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7779,6 +7774,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7792,44 +7792,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128806046</v>
+        <v>128813020</v>
       </c>
       <c r="B73" t="n">
-        <v>86976</v>
+        <v>57713</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7839,13 +7839,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717129</v>
+        <v>717395</v>
       </c>
       <c r="R73" t="n">
-        <v>6373201</v>
+        <v>6373086</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7872,9 +7872,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7889,44 +7899,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128813020</v>
+        <v>128806046</v>
       </c>
       <c r="B74" t="n">
-        <v>57713</v>
+        <v>86976</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7936,13 +7946,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717395</v>
+        <v>717129</v>
       </c>
       <c r="R74" t="n">
-        <v>6373086</v>
+        <v>6373201</v>
       </c>
       <c r="S74" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7969,19 +7979,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,12 +7996,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128815128</v>
+        <v>128806047</v>
       </c>
       <c r="B76" t="n">
-        <v>91030</v>
+        <v>86976</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8126,34 +8126,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717418</v>
+        <v>717290</v>
       </c>
       <c r="R76" t="n">
-        <v>6373171</v>
+        <v>6373221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8194,29 +8194,28 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806047</v>
+        <v>128806316</v>
       </c>
       <c r="B77" t="n">
-        <v>86976</v>
+        <v>86802</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8224,34 +8223,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717290</v>
+        <v>717125</v>
       </c>
       <c r="R77" t="n">
-        <v>6373221</v>
+        <v>6373250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8292,25 +8294,26 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128806316</v>
+        <v>128813077</v>
       </c>
       <c r="B78" t="n">
         <v>86802</v>
@@ -8339,19 +8342,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717125</v>
+        <v>717116</v>
       </c>
       <c r="R78" t="n">
-        <v>6373250</v>
+        <v>6373207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,40 +8381,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128813077</v>
+        <v>128815128</v>
       </c>
       <c r="B79" t="n">
-        <v>86802</v>
+        <v>91030</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8422,34 +8431,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>1357</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717116</v>
+        <v>717418</v>
       </c>
       <c r="R79" t="n">
-        <v>6373207</v>
+        <v>6373171</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8479,71 +8488,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128806026</v>
+        <v>128806001</v>
       </c>
       <c r="B80" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717211</v>
+        <v>717159</v>
       </c>
       <c r="R80" t="n">
-        <v>6373375</v>
+        <v>6373378</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8597,7 +8597,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8609,52 +8608,52 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128806031</v>
+        <v>128815117</v>
       </c>
       <c r="B81" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717071</v>
+        <v>717416</v>
       </c>
       <c r="R81" t="n">
-        <v>6373294</v>
+        <v>6373167</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8695,29 +8694,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128813055</v>
+        <v>128806067</v>
       </c>
       <c r="B82" t="n">
-        <v>98653</v>
+        <v>86917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8725,21 +8723,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8749,10 +8747,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717326</v>
+        <v>717298</v>
       </c>
       <c r="R82" t="n">
-        <v>6373144</v>
+        <v>6373345</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8782,19 +8780,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8809,44 +8797,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128806001</v>
+        <v>128813055</v>
       </c>
       <c r="B83" t="n">
-        <v>86999</v>
+        <v>98653</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3767</v>
+        <v>219874</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8856,10 +8844,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717159</v>
+        <v>717326</v>
       </c>
       <c r="R83" t="n">
-        <v>6373378</v>
+        <v>6373144</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8889,9 +8877,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8906,57 +8904,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128815117</v>
+        <v>128806031</v>
       </c>
       <c r="B84" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717416</v>
+        <v>717071</v>
       </c>
       <c r="R84" t="n">
-        <v>6373167</v>
+        <v>6373294</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,50 +8995,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128806067</v>
+        <v>128806026</v>
       </c>
       <c r="B85" t="n">
-        <v>86917</v>
+        <v>86954</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9050,10 +9049,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717298</v>
+        <v>717211</v>
       </c>
       <c r="R85" t="n">
-        <v>6373345</v>
+        <v>6373375</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,6 +9093,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9105,17 +9105,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128813061</v>
+        <v>128815130</v>
       </c>
       <c r="B86" t="n">
-        <v>86870</v>
+        <v>91030</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9123,34 +9123,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>248956</v>
+        <v>1357</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717085</v>
+        <v>717326</v>
       </c>
       <c r="R86" t="n">
-        <v>6373261</v>
+        <v>6373267</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,71 +9180,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806318</v>
+        <v>128813078</v>
       </c>
       <c r="B87" t="n">
-        <v>86954</v>
+        <v>86802</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9254,10 +9245,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717062</v>
+        <v>717243</v>
       </c>
       <c r="R87" t="n">
-        <v>6373304</v>
+        <v>6373192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9287,83 +9278,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806007</v>
+        <v>128815156</v>
       </c>
       <c r="B88" t="n">
-        <v>57713</v>
+        <v>86917</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717083</v>
+        <v>717444</v>
       </c>
       <c r="R88" t="n">
-        <v>6373260</v>
+        <v>6373273</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9410,22 +9402,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128813078</v>
+        <v>128815120</v>
       </c>
       <c r="B89" t="n">
-        <v>86802</v>
+        <v>86999</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9433,34 +9425,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717243</v>
+        <v>717479</v>
       </c>
       <c r="R89" t="n">
-        <v>6373192</v>
+        <v>6373226</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9490,19 +9482,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9517,57 +9499,65 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128815130</v>
+        <v>128806007</v>
       </c>
       <c r="B90" t="n">
-        <v>91030</v>
+        <v>57713</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717326</v>
+        <v>717083</v>
       </c>
       <c r="R90" t="n">
-        <v>6373267</v>
+        <v>6373260</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9608,64 +9598,63 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128815156</v>
+        <v>128813061</v>
       </c>
       <c r="B91" t="n">
-        <v>86917</v>
+        <v>86870</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717444</v>
+        <v>717085</v>
       </c>
       <c r="R91" t="n">
-        <v>6373273</v>
+        <v>6373261</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9695,9 +9684,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9712,57 +9711,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128815120</v>
+        <v>128806318</v>
       </c>
       <c r="B92" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717479</v>
+        <v>717062</v>
       </c>
       <c r="R92" t="n">
-        <v>6373226</v>
+        <v>6373304</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9803,18 +9802,19 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10837,32 +10837,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128815129</v>
+        <v>128815151</v>
       </c>
       <c r="B103" t="n">
-        <v>91030</v>
+        <v>86917</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717424</v>
+        <v>717270</v>
       </c>
       <c r="R103" t="n">
-        <v>6373165</v>
+        <v>6373304</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10934,7 +10934,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128815151</v>
+        <v>128815149</v>
       </c>
       <c r="B104" t="n">
         <v>86917</v>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717270</v>
+        <v>717269</v>
       </c>
       <c r="R104" t="n">
-        <v>6373304</v>
+        <v>6373207</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815149</v>
+        <v>128815110</v>
       </c>
       <c r="B105" t="n">
-        <v>86917</v>
+        <v>86999</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717269</v>
+        <v>717281</v>
       </c>
       <c r="R105" t="n">
-        <v>6373207</v>
+        <v>6373300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128815110</v>
+        <v>128815129</v>
       </c>
       <c r="B106" t="n">
-        <v>86999</v>
+        <v>91030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11139,21 +11139,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717281</v>
+        <v>717424</v>
       </c>
       <c r="R106" t="n">
-        <v>6373300</v>
+        <v>6373165</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11225,45 +11225,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806323</v>
+        <v>128813073</v>
       </c>
       <c r="B107" t="n">
-        <v>86954</v>
+        <v>92818</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717241</v>
+        <v>717453</v>
       </c>
       <c r="R107" t="n">
-        <v>6373264</v>
+        <v>6373125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11293,9 +11296,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11311,19 +11324,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806028</v>
+        <v>128806323</v>
       </c>
       <c r="B108" t="n">
         <v>86954</v>
@@ -11358,10 +11371,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717179</v>
+        <v>717241</v>
       </c>
       <c r="R108" t="n">
-        <v>6373374</v>
+        <v>6373264</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11409,19 +11422,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806320</v>
+        <v>128806028</v>
       </c>
       <c r="B109" t="n">
         <v>86954</v>
@@ -11456,10 +11469,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717131</v>
+        <v>717179</v>
       </c>
       <c r="R109" t="n">
-        <v>6373249</v>
+        <v>6373374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11507,60 +11520,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128813073</v>
+        <v>128806320</v>
       </c>
       <c r="B110" t="n">
-        <v>92818</v>
+        <v>86954</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717453</v>
+        <v>717131</v>
       </c>
       <c r="R110" t="n">
-        <v>6373125</v>
+        <v>6373249</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11590,19 +11600,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,57 +11618,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813568</v>
+        <v>128815121</v>
       </c>
       <c r="B111" t="n">
-        <v>86897</v>
+        <v>86999</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717322</v>
+        <v>717499</v>
       </c>
       <c r="R111" t="n">
-        <v>6373203</v>
+        <v>6373239</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,19 +11698,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11725,44 +11715,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128813048</v>
+        <v>128806313</v>
       </c>
       <c r="B112" t="n">
-        <v>86954</v>
+        <v>86999</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11772,10 +11762,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717248</v>
+        <v>717369</v>
       </c>
       <c r="R112" t="n">
-        <v>6373196</v>
+        <v>6373319</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11805,19 +11795,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11832,44 +11812,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128813063</v>
+        <v>128813568</v>
       </c>
       <c r="B113" t="n">
-        <v>92248</v>
+        <v>86897</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>232138</v>
+        <v>473</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11879,10 +11859,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717511</v>
+        <v>717322</v>
       </c>
       <c r="R113" t="n">
-        <v>6373145</v>
+        <v>6373203</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11914,7 +11894,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11924,7 +11904,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11944,52 +11924,55 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Via Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128815139</v>
+        <v>128806055</v>
       </c>
       <c r="B114" t="n">
-        <v>86870</v>
+        <v>86709</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717313</v>
+        <v>717283</v>
       </c>
       <c r="R114" t="n">
-        <v>6373361</v>
+        <v>6373299</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12024,34 +12007,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815121</v>
+        <v>128815139</v>
       </c>
       <c r="B115" t="n">
-        <v>86999</v>
+        <v>86870</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12059,21 +12048,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12083,10 +12072,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717499</v>
+        <v>717313</v>
       </c>
       <c r="R115" t="n">
-        <v>6373239</v>
+        <v>6373361</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12145,10 +12134,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806313</v>
+        <v>128813063</v>
       </c>
       <c r="B116" t="n">
-        <v>86999</v>
+        <v>92248</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12156,21 +12145,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3767</v>
+        <v>232138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12180,10 +12169,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717369</v>
+        <v>717511</v>
       </c>
       <c r="R116" t="n">
-        <v>6373319</v>
+        <v>6373145</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12213,9 +12202,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12230,22 +12229,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Via Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806055</v>
+        <v>128813048</v>
       </c>
       <c r="B117" t="n">
-        <v>86709</v>
+        <v>86954</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12253,37 +12252,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717283</v>
+        <v>717248</v>
       </c>
       <c r="R117" t="n">
-        <v>6373299</v>
+        <v>6373196</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12313,14 +12309,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12329,19 +12330,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13349,45 +13349,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128815115</v>
+        <v>128813049</v>
       </c>
       <c r="B128" t="n">
-        <v>86999</v>
+        <v>86954</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717424</v>
+        <v>717330</v>
       </c>
       <c r="R128" t="n">
-        <v>6373147</v>
+        <v>6373178</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13417,9 +13417,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13434,42 +13444,46 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128815126</v>
+        <v>128815115</v>
       </c>
       <c r="B129" t="n">
-        <v>87020</v>
+        <v>86999</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3624</v>
+        <v>3767</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13477,10 +13491,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717337</v>
+        <v>717424</v>
       </c>
       <c r="R129" t="n">
-        <v>6373382</v>
+        <v>6373147</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13539,10 +13553,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128813080</v>
+        <v>128815126</v>
       </c>
       <c r="B130" t="n">
-        <v>86917</v>
+        <v>87020</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13550,34 +13564,30 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717456</v>
+        <v>717337</v>
       </c>
       <c r="R130" t="n">
-        <v>6373273</v>
+        <v>6373382</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13607,19 +13617,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>08:59</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13634,44 +13634,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813049</v>
+        <v>128813080</v>
       </c>
       <c r="B131" t="n">
-        <v>86954</v>
+        <v>86917</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13681,10 +13681,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717330</v>
+        <v>717456</v>
       </c>
       <c r="R131" t="n">
-        <v>6373178</v>
+        <v>6373273</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13753,48 +13753,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813075</v>
+        <v>128813018</v>
       </c>
       <c r="B132" t="n">
-        <v>86870</v>
+        <v>110746</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>248956</v>
+        <v>219711</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717344</v>
+        <v>717512</v>
       </c>
       <c r="R132" t="n">
-        <v>6373206</v>
+        <v>6373149</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13826,7 +13823,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13836,12 +13833,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13850,7 +13842,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13869,45 +13860,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813018</v>
+        <v>128813075</v>
       </c>
       <c r="B133" t="n">
-        <v>110746</v>
+        <v>86870</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219711</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717512</v>
+        <v>717344</v>
       </c>
       <c r="R133" t="n">
-        <v>6373149</v>
+        <v>6373206</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13939,7 +13933,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13949,7 +13943,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13958,6 +13957,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13976,32 +13976,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128813027</v>
+        <v>128806319</v>
       </c>
       <c r="B134" t="n">
-        <v>91003</v>
+        <v>86954</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717343</v>
+        <v>717087</v>
       </c>
       <c r="R134" t="n">
-        <v>6373129</v>
+        <v>6373291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14044,39 +14044,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14374,32 +14365,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806319</v>
+        <v>128813027</v>
       </c>
       <c r="B138" t="n">
-        <v>86954</v>
+        <v>91003</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14409,10 +14400,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717087</v>
+        <v>717343</v>
       </c>
       <c r="R138" t="n">
-        <v>6373291</v>
+        <v>6373129</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,30 +14433,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128813071</v>
       </c>
       <c r="B2" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128815135</v>
       </c>
       <c r="B3" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128805999</v>
       </c>
       <c r="B4" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128806048</v>
       </c>
       <c r="B5" t="n">
-        <v>90916</v>
+        <v>90921</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128806348</v>
       </c>
       <c r="B6" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128815113</v>
       </c>
       <c r="B7" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128806072</v>
       </c>
       <c r="B8" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>128813022</v>
       </c>
       <c r="B9" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,45 +1871,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128805997</v>
+        <v>128815145</v>
       </c>
       <c r="B14" t="n">
-        <v>86999</v>
+        <v>86924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>6037417</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717416</v>
+        <v>717299</v>
       </c>
       <c r="R14" t="n">
-        <v>6373282</v>
+        <v>6373241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,50 +1950,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128806003</v>
+        <v>128813050</v>
       </c>
       <c r="B15" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717431</v>
+        <v>717330</v>
       </c>
       <c r="R15" t="n">
-        <v>6373255</v>
+        <v>6373140</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,9 +2037,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,57 +2064,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815153</v>
+        <v>128813054</v>
       </c>
       <c r="B16" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717341</v>
+        <v>717402</v>
       </c>
       <c r="R16" t="n">
-        <v>6373251</v>
+        <v>6373098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,9 +2144,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,60 +2171,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128806343</v>
+        <v>128805997</v>
       </c>
       <c r="B17" t="n">
-        <v>86709</v>
+        <v>87003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717258</v>
+        <v>717416</v>
       </c>
       <c r="R17" t="n">
-        <v>6373299</v>
+        <v>6373282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2238,75 +2256,69 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128815145</v>
+        <v>128806003</v>
       </c>
       <c r="B18" t="n">
-        <v>86920</v>
+        <v>87003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6037417</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717299</v>
+        <v>717431</v>
       </c>
       <c r="R18" t="n">
-        <v>6373241</v>
+        <v>6373255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,64 +2359,63 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813050</v>
+        <v>128815153</v>
       </c>
       <c r="B19" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717330</v>
+        <v>717341</v>
       </c>
       <c r="R19" t="n">
-        <v>6373140</v>
+        <v>6373251</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,19 +2445,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2461,22 +2462,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813054</v>
+        <v>128806343</v>
       </c>
       <c r="B20" t="n">
-        <v>86954</v>
+        <v>86713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2484,34 +2485,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717402</v>
+        <v>717258</v>
       </c>
       <c r="R20" t="n">
-        <v>6373098</v>
+        <v>6373299</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,19 +2545,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:50</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2562,18 +2561,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
         <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128815134</v>
       </c>
       <c r="B22" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>128813032</v>
       </c>
       <c r="B23" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128806324</v>
       </c>
       <c r="B24" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>128806027</v>
       </c>
       <c r="B25" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>128806029</v>
       </c>
       <c r="B26" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,54 +3175,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128806042</v>
+        <v>128815122</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>87003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717134</v>
+        <v>717534</v>
       </c>
       <c r="R27" t="n">
-        <v>6373159</v>
+        <v>6373182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3263,51 +3254,50 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128813051</v>
+        <v>128805998</v>
       </c>
       <c r="B28" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717385</v>
+        <v>717299</v>
       </c>
       <c r="R28" t="n">
-        <v>6373091</v>
+        <v>6373359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3350,19 +3340,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,12 +3357,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3392,7 +3372,7 @@
         <v>128813028</v>
       </c>
       <c r="B29" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,45 +3476,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128815122</v>
+        <v>128806042</v>
       </c>
       <c r="B30" t="n">
-        <v>86999</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717534</v>
+        <v>717134</v>
       </c>
       <c r="R30" t="n">
-        <v>6373182</v>
+        <v>6373159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3575,50 +3564,51 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128805998</v>
+        <v>128813051</v>
       </c>
       <c r="B31" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3628,10 +3618,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717299</v>
+        <v>717385</v>
       </c>
       <c r="R31" t="n">
-        <v>6373359</v>
+        <v>6373091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3661,9 +3651,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3678,57 +3678,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128813070</v>
+        <v>128815154</v>
       </c>
       <c r="B32" t="n">
-        <v>86976</v>
+        <v>86921</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717323</v>
+        <v>717416</v>
       </c>
       <c r="R32" t="n">
-        <v>6373241</v>
+        <v>6373159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,19 +3758,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3785,44 +3775,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128813068</v>
+        <v>128806349</v>
       </c>
       <c r="B33" t="n">
-        <v>86976</v>
+        <v>86921</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3832,10 +3822,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717085</v>
+        <v>717337</v>
       </c>
       <c r="R33" t="n">
-        <v>6373275</v>
+        <v>6373337</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,19 +3855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3892,22 +3872,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128815154</v>
+        <v>128806351</v>
       </c>
       <c r="B34" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,14 +3915,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717416</v>
+        <v>717390</v>
       </c>
       <c r="R34" t="n">
-        <v>6373159</v>
+        <v>6373317</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3989,44 +3969,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806349</v>
+        <v>128806002</v>
       </c>
       <c r="B35" t="n">
-        <v>86917</v>
+        <v>87003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4016,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717337</v>
+        <v>717297</v>
       </c>
       <c r="R35" t="n">
-        <v>6373337</v>
+        <v>6373295</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4086,44 +4066,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128806351</v>
+        <v>128813070</v>
       </c>
       <c r="B36" t="n">
-        <v>86917</v>
+        <v>86980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4133,10 +4113,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717390</v>
+        <v>717323</v>
       </c>
       <c r="R36" t="n">
-        <v>6373317</v>
+        <v>6373241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,9 +4146,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,22 +4173,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128806002</v>
+        <v>128813068</v>
       </c>
       <c r="B37" t="n">
-        <v>86999</v>
+        <v>86980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,21 +4196,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4230,10 +4220,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717297</v>
+        <v>717085</v>
       </c>
       <c r="R37" t="n">
-        <v>6373295</v>
+        <v>6373275</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4263,9 +4253,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,12 +4280,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
         <v>128806025</v>
       </c>
       <c r="B38" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128806317</v>
       </c>
       <c r="B39" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>128813065</v>
       </c>
       <c r="B40" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>128815140</v>
       </c>
       <c r="B41" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4688,32 +4688,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815143</v>
+        <v>128815114</v>
       </c>
       <c r="B42" t="n">
-        <v>90955</v>
+        <v>87003</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3286</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717335</v>
+        <v>717431</v>
       </c>
       <c r="R42" t="n">
-        <v>6373383</v>
+        <v>6373147</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4785,32 +4785,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128815114</v>
+        <v>128815143</v>
       </c>
       <c r="B43" t="n">
-        <v>86999</v>
+        <v>90960</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>3286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717431</v>
+        <v>717335</v>
       </c>
       <c r="R43" t="n">
-        <v>6373147</v>
+        <v>6373383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4885,7 +4885,7 @@
         <v>128813036</v>
       </c>
       <c r="B44" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>128806035</v>
       </c>
       <c r="B45" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5087,32 +5087,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128806053</v>
+        <v>128813046</v>
       </c>
       <c r="B46" t="n">
-        <v>86780</v>
+        <v>86958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717382</v>
+        <v>717216</v>
       </c>
       <c r="R46" t="n">
-        <v>6373309</v>
+        <v>6373176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,9 +5155,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,44 +5182,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128806345</v>
+        <v>128813040</v>
       </c>
       <c r="B47" t="n">
-        <v>86917</v>
+        <v>86958</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5219,10 +5229,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717170</v>
+        <v>717487</v>
       </c>
       <c r="R47" t="n">
-        <v>6373195</v>
+        <v>6373202</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5252,9 +5262,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5269,44 +5289,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128813046</v>
+        <v>128813067</v>
       </c>
       <c r="B48" t="n">
-        <v>86954</v>
+        <v>86980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5316,10 +5336,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717216</v>
+        <v>717325</v>
       </c>
       <c r="R48" t="n">
-        <v>6373176</v>
+        <v>6373229</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,7 +5371,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5361,7 +5381,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5388,32 +5408,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128813040</v>
+        <v>128806053</v>
       </c>
       <c r="B49" t="n">
-        <v>86954</v>
+        <v>86784</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5423,10 +5443,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717487</v>
+        <v>717382</v>
       </c>
       <c r="R49" t="n">
-        <v>6373202</v>
+        <v>6373309</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5456,19 +5476,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5483,44 +5493,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128813067</v>
+        <v>128806345</v>
       </c>
       <c r="B50" t="n">
-        <v>86976</v>
+        <v>86921</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5530,10 +5540,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717325</v>
+        <v>717170</v>
       </c>
       <c r="R50" t="n">
-        <v>6373229</v>
+        <v>6373195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5563,19 +5573,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5590,57 +5590,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128815141</v>
+        <v>128806334</v>
       </c>
       <c r="B51" t="n">
-        <v>86976</v>
+        <v>90960</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>449</v>
+        <v>3286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717505</v>
+        <v>717324</v>
       </c>
       <c r="R51" t="n">
-        <v>6373241</v>
+        <v>6373355</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,22 +5687,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128815131</v>
+        <v>128815141</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>86980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717416</v>
+        <v>717505</v>
       </c>
       <c r="R52" t="n">
-        <v>6373162</v>
+        <v>6373241</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5772,18 +5772,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5802,32 +5796,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128806334</v>
+        <v>128806069</v>
       </c>
       <c r="B53" t="n">
-        <v>90955</v>
+        <v>86921</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5837,10 +5831,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717324</v>
+        <v>717117</v>
       </c>
       <c r="R53" t="n">
-        <v>6373355</v>
+        <v>6373208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5887,22 +5881,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128806069</v>
+        <v>128806074</v>
       </c>
       <c r="B54" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5934,10 +5928,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717117</v>
+        <v>717445</v>
       </c>
       <c r="R54" t="n">
-        <v>6373208</v>
+        <v>6373269</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5996,45 +5990,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806074</v>
+        <v>128815131</v>
       </c>
       <c r="B55" t="n">
-        <v>86917</v>
+        <v>91035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717445</v>
+        <v>717416</v>
       </c>
       <c r="R55" t="n">
-        <v>6373269</v>
+        <v>6373162</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,24 +6063,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6096,7 +6096,7 @@
         <v>128813042</v>
       </c>
       <c r="B56" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>128806034</v>
       </c>
       <c r="B57" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>128815116</v>
       </c>
       <c r="B58" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>128815152</v>
       </c>
       <c r="B59" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>128806054</v>
       </c>
       <c r="B60" t="n">
-        <v>86780</v>
+        <v>86784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>128815148</v>
       </c>
       <c r="B61" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>128806330</v>
       </c>
       <c r="B62" t="n">
-        <v>107533</v>
+        <v>107539</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>128806322</v>
       </c>
       <c r="B63" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>128813066</v>
       </c>
       <c r="B64" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>128806333</v>
       </c>
       <c r="B65" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128806326</v>
+        <v>128813079</v>
       </c>
       <c r="B66" t="n">
-        <v>86930</v>
+        <v>86921</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1988</v>
+        <v>3674</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717084</v>
+        <v>717315</v>
       </c>
       <c r="R66" t="n">
-        <v>6373294</v>
+        <v>6373221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7153,9 +7153,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,44 +7180,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813044</v>
+        <v>128806350</v>
       </c>
       <c r="B67" t="n">
-        <v>86954</v>
+        <v>86921</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7217,10 +7227,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717135</v>
+        <v>717330</v>
       </c>
       <c r="R67" t="n">
-        <v>6373174</v>
+        <v>6373328</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7250,19 +7260,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7277,44 +7277,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128806036</v>
+        <v>128813012</v>
       </c>
       <c r="B68" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717449</v>
+        <v>717435</v>
       </c>
       <c r="R68" t="n">
-        <v>6373281</v>
+        <v>6373156</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7357,40 +7357,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128813079</v>
+        <v>128806326</v>
       </c>
       <c r="B69" t="n">
-        <v>86917</v>
+        <v>86934</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7398,21 +7407,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7422,10 +7431,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717315</v>
+        <v>717084</v>
       </c>
       <c r="R69" t="n">
-        <v>6373221</v>
+        <v>6373294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7455,19 +7464,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7482,57 +7481,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806350</v>
+        <v>128806342</v>
       </c>
       <c r="B70" t="n">
-        <v>86917</v>
+        <v>86713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717330</v>
+        <v>717179</v>
       </c>
       <c r="R70" t="n">
-        <v>6373328</v>
+        <v>6373227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7567,12 +7569,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7591,32 +7599,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128813012</v>
+        <v>128813044</v>
       </c>
       <c r="B71" t="n">
-        <v>86999</v>
+        <v>86958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7626,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717435</v>
+        <v>717135</v>
       </c>
       <c r="R71" t="n">
-        <v>6373156</v>
+        <v>6373174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7661,7 +7669,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7671,7 +7679,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7698,10 +7706,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806342</v>
+        <v>128806036</v>
       </c>
       <c r="B72" t="n">
-        <v>86709</v>
+        <v>86958</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7709,37 +7717,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717179</v>
+        <v>717449</v>
       </c>
       <c r="R72" t="n">
-        <v>6373227</v>
+        <v>6373281</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7774,11 +7779,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7792,60 +7792,69 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128813020</v>
+        <v>128806041</v>
       </c>
       <c r="B73" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717395</v>
+        <v>717150</v>
       </c>
       <c r="R73" t="n">
-        <v>6373086</v>
+        <v>6373384</v>
       </c>
       <c r="S73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7872,39 +7881,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7914,7 +7914,7 @@
         <v>128806046</v>
       </c>
       <c r="B74" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,57 +8008,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128806041</v>
+        <v>128813020</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717150</v>
+        <v>717395</v>
       </c>
       <c r="R75" t="n">
-        <v>6373384</v>
+        <v>6373086</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8085,40 +8076,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128806047</v>
+        <v>128806001</v>
       </c>
       <c r="B76" t="n">
-        <v>86976</v>
+        <v>87003</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8126,21 +8126,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717290</v>
+        <v>717159</v>
       </c>
       <c r="R76" t="n">
-        <v>6373221</v>
+        <v>6373378</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8212,10 +8212,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806316</v>
+        <v>128815117</v>
       </c>
       <c r="B77" t="n">
-        <v>86802</v>
+        <v>87003</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,37 +8223,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717125</v>
+        <v>717416</v>
       </c>
       <c r="R77" t="n">
-        <v>6373250</v>
+        <v>6373167</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,51 +8291,50 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128813077</v>
+        <v>128806067</v>
       </c>
       <c r="B78" t="n">
-        <v>86802</v>
+        <v>86921</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8348,10 +8344,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717116</v>
+        <v>717298</v>
       </c>
       <c r="R78" t="n">
-        <v>6373207</v>
+        <v>6373345</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,19 +8377,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8408,22 +8394,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128815128</v>
+        <v>128806047</v>
       </c>
       <c r="B79" t="n">
-        <v>91030</v>
+        <v>86980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8431,34 +8417,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717418</v>
+        <v>717290</v>
       </c>
       <c r="R79" t="n">
-        <v>6373171</v>
+        <v>6373221</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,29 +8485,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128806001</v>
+        <v>128806316</v>
       </c>
       <c r="B80" t="n">
-        <v>86999</v>
+        <v>86806</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8529,34 +8514,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717159</v>
+        <v>717125</v>
       </c>
       <c r="R80" t="n">
-        <v>6373378</v>
+        <v>6373250</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8597,28 +8585,29 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128815117</v>
+        <v>128813077</v>
       </c>
       <c r="B81" t="n">
-        <v>86999</v>
+        <v>86806</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8626,34 +8615,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717416</v>
+        <v>717116</v>
       </c>
       <c r="R81" t="n">
-        <v>6373167</v>
+        <v>6373207</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8683,9 +8672,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8700,57 +8699,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128806067</v>
+        <v>128815128</v>
       </c>
       <c r="B82" t="n">
-        <v>86917</v>
+        <v>91035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717298</v>
+        <v>717418</v>
       </c>
       <c r="R82" t="n">
-        <v>6373345</v>
+        <v>6373171</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8791,18 +8790,19 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8812,7 +8812,7 @@
         <v>128813055</v>
       </c>
       <c r="B83" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8916,10 +8916,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128806031</v>
+        <v>128806026</v>
       </c>
       <c r="B84" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717071</v>
+        <v>717211</v>
       </c>
       <c r="R84" t="n">
-        <v>6373294</v>
+        <v>6373375</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9014,10 +9014,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128806026</v>
+        <v>128806031</v>
       </c>
       <c r="B85" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9049,10 +9049,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717211</v>
+        <v>717071</v>
       </c>
       <c r="R85" t="n">
-        <v>6373375</v>
+        <v>6373294</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128815130</v>
+        <v>128813078</v>
       </c>
       <c r="B86" t="n">
-        <v>91030</v>
+        <v>86806</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9123,34 +9123,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717326</v>
+        <v>717243</v>
       </c>
       <c r="R86" t="n">
-        <v>6373267</v>
+        <v>6373192</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,75 +9180,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128813078</v>
+        <v>128815156</v>
       </c>
       <c r="B87" t="n">
-        <v>86802</v>
+        <v>86921</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717243</v>
+        <v>717444</v>
       </c>
       <c r="R87" t="n">
-        <v>6373192</v>
+        <v>6373273</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9278,19 +9287,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9305,44 +9304,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815156</v>
+        <v>128815120</v>
       </c>
       <c r="B88" t="n">
-        <v>86917</v>
+        <v>87003</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9352,10 +9351,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717444</v>
+        <v>717479</v>
       </c>
       <c r="R88" t="n">
-        <v>6373273</v>
+        <v>6373226</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9414,10 +9413,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815120</v>
+        <v>128815130</v>
       </c>
       <c r="B89" t="n">
-        <v>86999</v>
+        <v>91035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9425,21 +9424,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9449,10 +9448,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717479</v>
+        <v>717326</v>
       </c>
       <c r="R89" t="n">
-        <v>6373226</v>
+        <v>6373267</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9493,6 +9492,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9619,7 +9619,7 @@
         <v>128813061</v>
       </c>
       <c r="B91" t="n">
-        <v>86870</v>
+        <v>86874</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>128806318</v>
       </c>
       <c r="B92" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>128813069</v>
       </c>
       <c r="B93" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>128813074</v>
       </c>
       <c r="B94" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>128815109</v>
       </c>
       <c r="B95" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>128815112</v>
       </c>
       <c r="B96" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>128806071</v>
       </c>
       <c r="B97" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>128815123</v>
       </c>
       <c r="B98" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>128815118</v>
       </c>
       <c r="B99" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>128813076</v>
       </c>
       <c r="B100" t="n">
-        <v>90261</v>
+        <v>90266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>128815137</v>
       </c>
       <c r="B101" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>128813052</v>
       </c>
       <c r="B102" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>128815151</v>
       </c>
       <c r="B103" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>128815149</v>
       </c>
       <c r="B104" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>128815110</v>
       </c>
       <c r="B105" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>128815129</v>
       </c>
       <c r="B106" t="n">
-        <v>91030</v>
+        <v>91035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11225,48 +11225,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128813073</v>
+        <v>128806323</v>
       </c>
       <c r="B107" t="n">
-        <v>92818</v>
+        <v>86958</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717453</v>
+        <v>717241</v>
       </c>
       <c r="R107" t="n">
-        <v>6373125</v>
+        <v>6373264</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11296,19 +11293,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11324,22 +11311,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806323</v>
+        <v>128806028</v>
       </c>
       <c r="B108" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11371,10 +11358,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717241</v>
+        <v>717179</v>
       </c>
       <c r="R108" t="n">
-        <v>6373264</v>
+        <v>6373374</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11422,22 +11409,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806028</v>
+        <v>128806320</v>
       </c>
       <c r="B109" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11469,10 +11456,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717179</v>
+        <v>717131</v>
       </c>
       <c r="R109" t="n">
-        <v>6373374</v>
+        <v>6373249</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11520,57 +11507,60 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806320</v>
+        <v>128813073</v>
       </c>
       <c r="B110" t="n">
-        <v>86954</v>
+        <v>92823</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717131</v>
+        <v>717453</v>
       </c>
       <c r="R110" t="n">
-        <v>6373249</v>
+        <v>6373125</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11600,9 +11590,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,12 +11618,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11633,7 +11633,7 @@
         <v>128815121</v>
       </c>
       <c r="B111" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>128806313</v>
       </c>
       <c r="B112" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>128813568</v>
       </c>
       <c r="B113" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>128806055</v>
       </c>
       <c r="B114" t="n">
-        <v>86709</v>
+        <v>86713</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815139</v>
+        <v>128813063</v>
       </c>
       <c r="B115" t="n">
-        <v>86870</v>
+        <v>92253</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12048,34 +12048,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>248956</v>
+        <v>232138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717313</v>
+        <v>717511</v>
       </c>
       <c r="R115" t="n">
-        <v>6373361</v>
+        <v>6373145</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12105,9 +12105,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12122,22 +12132,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128813063</v>
+        <v>128815139</v>
       </c>
       <c r="B116" t="n">
-        <v>92248</v>
+        <v>86874</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12145,34 +12155,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>232138</v>
+        <v>248956</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717511</v>
+        <v>717313</v>
       </c>
       <c r="R116" t="n">
-        <v>6373145</v>
+        <v>6373361</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12202,19 +12212,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12229,12 +12229,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Via Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12244,7 +12244,7 @@
         <v>128813048</v>
       </c>
       <c r="B117" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12348,32 +12348,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128813030</v>
+        <v>128806315</v>
       </c>
       <c r="B118" t="n">
-        <v>86930</v>
+        <v>86806</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717079</v>
+        <v>717165</v>
       </c>
       <c r="R118" t="n">
-        <v>6373300</v>
+        <v>6373195</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,19 +12416,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12443,22 +12433,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806315</v>
+        <v>128806312</v>
       </c>
       <c r="B119" t="n">
-        <v>86802</v>
+        <v>87003</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12456,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717165</v>
+        <v>717332</v>
       </c>
       <c r="R119" t="n">
-        <v>6373195</v>
+        <v>6373350</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12552,10 +12542,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806312</v>
+        <v>128815111</v>
       </c>
       <c r="B120" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12583,14 +12573,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717332</v>
+        <v>717318</v>
       </c>
       <c r="R120" t="n">
-        <v>6373350</v>
+        <v>6373242</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12637,57 +12627,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128815111</v>
+        <v>128806347</v>
       </c>
       <c r="B121" t="n">
-        <v>86999</v>
+        <v>86921</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717318</v>
+        <v>717092</v>
       </c>
       <c r="R121" t="n">
-        <v>6373242</v>
+        <v>6373322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12734,44 +12724,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128806347</v>
+        <v>128813014</v>
       </c>
       <c r="B122" t="n">
-        <v>86917</v>
+        <v>87003</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12781,10 +12771,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717092</v>
+        <v>717462</v>
       </c>
       <c r="R122" t="n">
-        <v>6373322</v>
+        <v>6373231</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12814,9 +12804,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12831,44 +12831,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128813014</v>
+        <v>128806340</v>
       </c>
       <c r="B123" t="n">
-        <v>86999</v>
+        <v>86784</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717462</v>
+        <v>717314</v>
       </c>
       <c r="R123" t="n">
-        <v>6373231</v>
+        <v>6373345</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12911,19 +12911,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12938,22 +12928,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806340</v>
+        <v>128813030</v>
       </c>
       <c r="B124" t="n">
-        <v>86780</v>
+        <v>86934</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12961,16 +12951,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3712</v>
+        <v>1988</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -12985,10 +12975,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717314</v>
+        <v>717079</v>
       </c>
       <c r="R124" t="n">
-        <v>6373345</v>
+        <v>6373300</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13018,9 +13008,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13035,12 +13035,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13050,7 +13050,7 @@
         <v>128806331</v>
       </c>
       <c r="B125" t="n">
-        <v>90330</v>
+        <v>90335</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>128813056</v>
       </c>
       <c r="B126" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>128806032</v>
       </c>
       <c r="B127" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13349,45 +13349,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128813049</v>
+        <v>128815115</v>
       </c>
       <c r="B128" t="n">
-        <v>86954</v>
+        <v>87003</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717330</v>
+        <v>717424</v>
       </c>
       <c r="R128" t="n">
-        <v>6373178</v>
+        <v>6373147</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13417,19 +13417,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13444,46 +13434,42 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128815115</v>
+        <v>128815126</v>
       </c>
       <c r="B129" t="n">
-        <v>86999</v>
+        <v>87024</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3767</v>
+        <v>3624</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13491,10 +13477,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717424</v>
+        <v>717337</v>
       </c>
       <c r="R129" t="n">
-        <v>6373147</v>
+        <v>6373382</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13553,10 +13539,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128815126</v>
+        <v>128813080</v>
       </c>
       <c r="B130" t="n">
-        <v>87020</v>
+        <v>86921</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13564,30 +13550,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717337</v>
+        <v>717456</v>
       </c>
       <c r="R130" t="n">
-        <v>6373382</v>
+        <v>6373273</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13617,9 +13607,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13634,22 +13634,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813080</v>
+        <v>128813018</v>
       </c>
       <c r="B131" t="n">
-        <v>86917</v>
+        <v>110752</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13657,21 +13657,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3674</v>
+        <v>219711</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13681,10 +13681,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717456</v>
+        <v>717512</v>
       </c>
       <c r="R131" t="n">
-        <v>6373273</v>
+        <v>6373149</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13753,45 +13753,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813018</v>
+        <v>128813075</v>
       </c>
       <c r="B132" t="n">
-        <v>110746</v>
+        <v>86874</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219711</v>
+        <v>248956</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717512</v>
+        <v>717344</v>
       </c>
       <c r="R132" t="n">
-        <v>6373149</v>
+        <v>6373206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13823,7 +13826,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13833,7 +13836,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13842,6 +13850,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13860,48 +13869,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813075</v>
+        <v>128813049</v>
       </c>
       <c r="B133" t="n">
-        <v>86870</v>
+        <v>86958</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717344</v>
+        <v>717330</v>
       </c>
       <c r="R133" t="n">
-        <v>6373206</v>
+        <v>6373178</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13933,7 +13939,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13943,12 +13949,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13957,7 +13958,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>128806319</v>
       </c>
       <c r="B134" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>128815155</v>
       </c>
       <c r="B135" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>128806000</v>
       </c>
       <c r="B136" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>128815133</v>
       </c>
       <c r="B137" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>128813027</v>
       </c>
       <c r="B138" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>128806066</v>
       </c>
       <c r="B139" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>128806070</v>
       </c>
       <c r="B140" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>128806008</v>
       </c>
       <c r="B141" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>128813081</v>
       </c>
       <c r="B142" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>128815147</v>
       </c>
       <c r="B143" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>128815124</v>
       </c>
       <c r="B144" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>128815150</v>
       </c>
       <c r="B145" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128813064</v>
       </c>
       <c r="B146" t="n">
-        <v>91492</v>
+        <v>91497</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128813071</v>
+        <v>128806006</v>
       </c>
       <c r="B2" t="n">
-        <v>86980</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717455</v>
+        <v>717370</v>
       </c>
       <c r="R2" t="n">
-        <v>6373115</v>
+        <v>6373322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,57 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128815135</v>
+        <v>128805999</v>
       </c>
       <c r="B3" t="n">
-        <v>86760</v>
+        <v>87004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717476</v>
+        <v>717287</v>
       </c>
       <c r="R3" t="n">
-        <v>6373242</v>
+        <v>6373354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128805999</v>
+        <v>128806048</v>
       </c>
       <c r="B4" t="n">
-        <v>87003</v>
+        <v>90926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3767</v>
+        <v>4188</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717287</v>
+        <v>717322</v>
       </c>
       <c r="R4" t="n">
-        <v>6373354</v>
+        <v>6373213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806048</v>
+        <v>128815113</v>
       </c>
       <c r="B5" t="n">
-        <v>90921</v>
+        <v>87004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717322</v>
+        <v>717317</v>
       </c>
       <c r="R5" t="n">
-        <v>6373213</v>
+        <v>6373308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128806348</v>
+        <v>128813022</v>
       </c>
       <c r="B6" t="n">
-        <v>86921</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717239</v>
+        <v>717130</v>
       </c>
       <c r="R6" t="n">
-        <v>6373234</v>
+        <v>6373194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,9 +1131,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1158,44 +1158,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128815113</v>
+        <v>128815136</v>
       </c>
       <c r="B7" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717317</v>
+        <v>717412</v>
       </c>
       <c r="R7" t="n">
-        <v>6373308</v>
+        <v>6373217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1249,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1268,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806072</v>
+        <v>128806033</v>
       </c>
       <c r="B8" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717289</v>
+        <v>717315</v>
       </c>
       <c r="R8" t="n">
-        <v>6373288</v>
+        <v>6373232</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1357,39 +1359,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128813022</v>
+        <v>128813034</v>
       </c>
       <c r="B9" t="n">
-        <v>92801</v>
+        <v>86959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717130</v>
+        <v>717425</v>
       </c>
       <c r="R9" t="n">
-        <v>6373194</v>
+        <v>6373083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1436,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1444,7 +1446,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,32 +1473,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128806006</v>
+        <v>128813071</v>
       </c>
       <c r="B10" t="n">
-        <v>92434</v>
+        <v>86981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717370</v>
+        <v>717455</v>
       </c>
       <c r="R10" t="n">
-        <v>6373322</v>
+        <v>6373115</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,9 +1541,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,44 +1568,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128815136</v>
+        <v>128815135</v>
       </c>
       <c r="B11" t="n">
-        <v>86958</v>
+        <v>86760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717412</v>
+        <v>717476</v>
       </c>
       <c r="R11" t="n">
-        <v>6373217</v>
+        <v>6373242</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,7 +1659,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1666,32 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128806033</v>
+        <v>128806348</v>
       </c>
       <c r="B12" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1701,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717315</v>
+        <v>717239</v>
       </c>
       <c r="R12" t="n">
-        <v>6373232</v>
+        <v>6373234</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,51 +1756,50 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128813034</v>
+        <v>128806072</v>
       </c>
       <c r="B13" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717425</v>
+        <v>717289</v>
       </c>
       <c r="R13" t="n">
-        <v>6373083</v>
+        <v>6373288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,19 +1842,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,44 +1859,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128815145</v>
+        <v>128815153</v>
       </c>
       <c r="B14" t="n">
-        <v>86924</v>
+        <v>86922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037417</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717299</v>
+        <v>717341</v>
       </c>
       <c r="R14" t="n">
-        <v>6373241</v>
+        <v>6373251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,7 +1950,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1969,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128813050</v>
+        <v>128805997</v>
       </c>
       <c r="B15" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717330</v>
+        <v>717416</v>
       </c>
       <c r="R15" t="n">
-        <v>6373140</v>
+        <v>6373282</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,19 +2036,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2064,44 +2053,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128813054</v>
+        <v>128806003</v>
       </c>
       <c r="B16" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2111,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717402</v>
+        <v>717431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373098</v>
+        <v>6373255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,19 +2133,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,57 +2150,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128805997</v>
+        <v>128815145</v>
       </c>
       <c r="B17" t="n">
-        <v>87003</v>
+        <v>86925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>6037417</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717416</v>
+        <v>717299</v>
       </c>
       <c r="R17" t="n">
-        <v>6373282</v>
+        <v>6373241</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,50 +2241,51 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128806003</v>
+        <v>128813050</v>
       </c>
       <c r="B18" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717431</v>
+        <v>717330</v>
       </c>
       <c r="R18" t="n">
-        <v>6373255</v>
+        <v>6373140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,9 +2328,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2365,57 +2355,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128815153</v>
+        <v>128813054</v>
       </c>
       <c r="B19" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717341</v>
+        <v>717402</v>
       </c>
       <c r="R19" t="n">
-        <v>6373251</v>
+        <v>6373098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,9 +2435,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2462,12 +2462,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2580,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128806311</v>
+        <v>128813032</v>
       </c>
       <c r="B21" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717316</v>
+        <v>717409</v>
       </c>
       <c r="R21" t="n">
-        <v>6373307</v>
+        <v>6373057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,9 +2648,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2665,57 +2675,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815134</v>
+        <v>128806324</v>
       </c>
       <c r="B22" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717316</v>
+        <v>717408</v>
       </c>
       <c r="R22" t="n">
-        <v>6373365</v>
+        <v>6373296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,28 +2766,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128813032</v>
+        <v>128806027</v>
       </c>
       <c r="B23" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2820,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717409</v>
+        <v>717195</v>
       </c>
       <c r="R23" t="n">
-        <v>6373057</v>
+        <v>6373376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,49 +2853,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128806324</v>
+        <v>128806029</v>
       </c>
       <c r="B24" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717408</v>
+        <v>717149</v>
       </c>
       <c r="R24" t="n">
-        <v>6373296</v>
+        <v>6373385</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,44 +2969,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128806027</v>
+        <v>128806311</v>
       </c>
       <c r="B25" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3014,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717195</v>
+        <v>717316</v>
       </c>
       <c r="R25" t="n">
-        <v>6373376</v>
+        <v>6373307</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3058,64 +3060,63 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128806029</v>
+        <v>128815134</v>
       </c>
       <c r="B26" t="n">
-        <v>86958</v>
+        <v>86760</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717149</v>
+        <v>717316</v>
       </c>
       <c r="R26" t="n">
-        <v>6373385</v>
+        <v>6373365</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,19 +3157,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3178,7 +3178,7 @@
         <v>128815122</v>
       </c>
       <c r="B27" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128805998</v>
       </c>
       <c r="B28" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128813028</v>
       </c>
       <c r="B29" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>128813051</v>
       </c>
       <c r="B31" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,45 +3690,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128815154</v>
+        <v>128813070</v>
       </c>
       <c r="B32" t="n">
-        <v>86921</v>
+        <v>86981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717416</v>
+        <v>717323</v>
       </c>
       <c r="R32" t="n">
-        <v>6373159</v>
+        <v>6373241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,9 +3758,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,44 +3785,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128806349</v>
+        <v>128813068</v>
       </c>
       <c r="B33" t="n">
-        <v>86921</v>
+        <v>86981</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3822,10 +3832,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717337</v>
+        <v>717085</v>
       </c>
       <c r="R33" t="n">
-        <v>6373337</v>
+        <v>6373275</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3855,9 +3865,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3872,44 +3892,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128806351</v>
+        <v>128806002</v>
       </c>
       <c r="B34" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3919,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717390</v>
+        <v>717297</v>
       </c>
       <c r="R34" t="n">
-        <v>6373317</v>
+        <v>6373295</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,44 +3989,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806002</v>
+        <v>128806025</v>
       </c>
       <c r="B35" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4016,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717297</v>
+        <v>717284</v>
       </c>
       <c r="R35" t="n">
-        <v>6373295</v>
+        <v>6373347</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4060,6 +4080,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4071,41 +4092,37 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128813070</v>
+        <v>128806317</v>
       </c>
       <c r="B36" t="n">
-        <v>86980</v>
+        <v>92808</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>6047725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4113,10 +4130,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717323</v>
+        <v>717367</v>
       </c>
       <c r="R36" t="n">
-        <v>6373241</v>
+        <v>6373322</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4146,84 +4163,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128813068</v>
+        <v>128815154</v>
       </c>
       <c r="B37" t="n">
-        <v>86980</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717085</v>
+        <v>717416</v>
       </c>
       <c r="R37" t="n">
-        <v>6373275</v>
+        <v>6373159</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,19 +4261,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,44 +4278,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128806025</v>
+        <v>128806349</v>
       </c>
       <c r="B38" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4327,10 +4325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717284</v>
+        <v>717337</v>
       </c>
       <c r="R38" t="n">
-        <v>6373347</v>
+        <v>6373337</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,29 +4369,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128806317</v>
+        <v>128806351</v>
       </c>
       <c r="B39" t="n">
-        <v>92803</v>
+        <v>86922</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4401,19 +4398,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6047725</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4421,10 +4422,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717367</v>
+        <v>717390</v>
       </c>
       <c r="R39" t="n">
-        <v>6373322</v>
+        <v>6373317</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4465,7 +4466,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4484,45 +4484,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128813065</v>
+        <v>128815143</v>
       </c>
       <c r="B40" t="n">
-        <v>86980</v>
+        <v>90965</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>449</v>
+        <v>3286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717407</v>
+        <v>717335</v>
       </c>
       <c r="R40" t="n">
-        <v>6373048</v>
+        <v>6373383</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4552,19 +4552,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4579,22 +4569,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128815140</v>
+        <v>128813065</v>
       </c>
       <c r="B41" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,14 +4612,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717460</v>
+        <v>717407</v>
       </c>
       <c r="R41" t="n">
-        <v>6373180</v>
+        <v>6373048</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4659,9 +4649,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4676,22 +4676,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815114</v>
+        <v>128815140</v>
       </c>
       <c r="B42" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,21 +4699,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717431</v>
+        <v>717460</v>
       </c>
       <c r="R42" t="n">
-        <v>6373147</v>
+        <v>6373180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4785,32 +4785,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128815143</v>
+        <v>128815114</v>
       </c>
       <c r="B43" t="n">
-        <v>90960</v>
+        <v>87004</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3286</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717335</v>
+        <v>717431</v>
       </c>
       <c r="R43" t="n">
-        <v>6373383</v>
+        <v>6373147</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4885,7 +4885,7 @@
         <v>128813036</v>
       </c>
       <c r="B44" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>128806035</v>
       </c>
       <c r="B45" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5087,32 +5087,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128813046</v>
+        <v>128806053</v>
       </c>
       <c r="B46" t="n">
-        <v>86958</v>
+        <v>86784</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717216</v>
+        <v>717382</v>
       </c>
       <c r="R46" t="n">
-        <v>6373176</v>
+        <v>6373309</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,19 +5155,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5182,44 +5172,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128813040</v>
+        <v>128806345</v>
       </c>
       <c r="B47" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5229,10 +5219,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717487</v>
+        <v>717170</v>
       </c>
       <c r="R47" t="n">
-        <v>6373202</v>
+        <v>6373195</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5262,19 +5252,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5289,44 +5269,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128813067</v>
+        <v>128813046</v>
       </c>
       <c r="B48" t="n">
-        <v>86980</v>
+        <v>86959</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5336,10 +5316,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717325</v>
+        <v>717216</v>
       </c>
       <c r="R48" t="n">
-        <v>6373229</v>
+        <v>6373176</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,7 +5351,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5381,7 +5361,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5408,32 +5388,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128806053</v>
+        <v>128813040</v>
       </c>
       <c r="B49" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5443,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717382</v>
+        <v>717487</v>
       </c>
       <c r="R49" t="n">
-        <v>6373309</v>
+        <v>6373202</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5476,9 +5456,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5493,44 +5483,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128806345</v>
+        <v>128813067</v>
       </c>
       <c r="B50" t="n">
-        <v>86921</v>
+        <v>86981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5540,10 +5530,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717170</v>
+        <v>717325</v>
       </c>
       <c r="R50" t="n">
-        <v>6373195</v>
+        <v>6373229</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,9 +5563,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5590,44 +5590,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128806334</v>
+        <v>128806069</v>
       </c>
       <c r="B51" t="n">
-        <v>90960</v>
+        <v>86922</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717324</v>
+        <v>717117</v>
       </c>
       <c r="R51" t="n">
-        <v>6373355</v>
+        <v>6373208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,57 +5687,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128815141</v>
+        <v>128806334</v>
       </c>
       <c r="B52" t="n">
-        <v>86980</v>
+        <v>90965</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>449</v>
+        <v>3286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717505</v>
+        <v>717324</v>
       </c>
       <c r="R52" t="n">
-        <v>6373241</v>
+        <v>6373355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,22 +5784,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128806069</v>
+        <v>128806074</v>
       </c>
       <c r="B53" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717117</v>
+        <v>717445</v>
       </c>
       <c r="R53" t="n">
-        <v>6373208</v>
+        <v>6373269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5893,32 +5893,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128806074</v>
+        <v>128813042</v>
       </c>
       <c r="B54" t="n">
-        <v>86921</v>
+        <v>86959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717445</v>
+        <v>717084</v>
       </c>
       <c r="R54" t="n">
-        <v>6373269</v>
+        <v>6373295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5961,9 +5961,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5978,57 +5988,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128815131</v>
+        <v>128806034</v>
       </c>
       <c r="B55" t="n">
-        <v>91035</v>
+        <v>86959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717416</v>
+        <v>717303</v>
       </c>
       <c r="R55" t="n">
-        <v>6373162</v>
+        <v>6373236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6063,11 +6073,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6081,57 +6086,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128813042</v>
+        <v>128815141</v>
       </c>
       <c r="B56" t="n">
-        <v>86958</v>
+        <v>86981</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717084</v>
+        <v>717505</v>
       </c>
       <c r="R56" t="n">
-        <v>6373295</v>
+        <v>6373241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6161,19 +6166,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6188,57 +6183,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128806034</v>
+        <v>128815131</v>
       </c>
       <c r="B57" t="n">
-        <v>86958</v>
+        <v>91040</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717303</v>
+        <v>717416</v>
       </c>
       <c r="R57" t="n">
-        <v>6373236</v>
+        <v>6373162</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,6 +6268,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6286,12 +6286,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
         <v>128815116</v>
       </c>
       <c r="B58" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6395,45 +6395,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128815152</v>
+        <v>128806330</v>
       </c>
       <c r="B59" t="n">
-        <v>86921</v>
+        <v>107546</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717329</v>
+        <v>717069</v>
       </c>
       <c r="R59" t="n">
-        <v>6373260</v>
+        <v>6373282</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,44 +6480,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128806054</v>
+        <v>128806322</v>
       </c>
       <c r="B60" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717273</v>
+        <v>717234</v>
       </c>
       <c r="R60" t="n">
-        <v>6373345</v>
+        <v>6373222</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,28 +6571,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128815148</v>
+        <v>128815152</v>
       </c>
       <c r="B61" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,10 +6625,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717239</v>
+        <v>717329</v>
       </c>
       <c r="R61" t="n">
-        <v>6373262</v>
+        <v>6373260</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6686,32 +6687,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128806330</v>
+        <v>128806054</v>
       </c>
       <c r="B62" t="n">
-        <v>107539</v>
+        <v>86784</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6721,10 +6722,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717069</v>
+        <v>717273</v>
       </c>
       <c r="R62" t="n">
-        <v>6373282</v>
+        <v>6373345</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,57 +6772,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128806322</v>
+        <v>128815148</v>
       </c>
       <c r="B63" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717234</v>
+        <v>717239</v>
       </c>
       <c r="R63" t="n">
-        <v>6373222</v>
+        <v>6373262</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6862,19 +6863,18 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6884,7 +6884,7 @@
         <v>128813066</v>
       </c>
       <c r="B64" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>128806333</v>
       </c>
       <c r="B65" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>128813079</v>
       </c>
       <c r="B66" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128806350</v>
       </c>
       <c r="B67" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128813012</v>
       </c>
       <c r="B68" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7396,45 +7396,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128806326</v>
+        <v>128806342</v>
       </c>
       <c r="B69" t="n">
-        <v>86934</v>
+        <v>86713</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717084</v>
+        <v>717179</v>
       </c>
       <c r="R69" t="n">
-        <v>6373294</v>
+        <v>6373227</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7469,12 +7472,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7493,48 +7502,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806342</v>
+        <v>128806326</v>
       </c>
       <c r="B70" t="n">
-        <v>86713</v>
+        <v>86935</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717179</v>
+        <v>717084</v>
       </c>
       <c r="R70" t="n">
-        <v>6373227</v>
+        <v>6373294</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7569,18 +7575,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>128813044</v>
       </c>
       <c r="B71" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128806036</v>
       </c>
       <c r="B72" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7804,57 +7804,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128806041</v>
+        <v>128813020</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717150</v>
+        <v>717395</v>
       </c>
       <c r="R73" t="n">
-        <v>6373384</v>
+        <v>6373086</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,75 +7872,93 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128806046</v>
+        <v>128806041</v>
       </c>
       <c r="B74" t="n">
-        <v>86980</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>449</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717129</v>
+        <v>717150</v>
       </c>
       <c r="R74" t="n">
-        <v>6373201</v>
+        <v>6373384</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7990,6 +7999,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8008,32 +8018,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128813020</v>
+        <v>128806046</v>
       </c>
       <c r="B75" t="n">
-        <v>57713</v>
+        <v>86981</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8043,13 +8053,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717395</v>
+        <v>717129</v>
       </c>
       <c r="R75" t="n">
-        <v>6373086</v>
+        <v>6373201</v>
       </c>
       <c r="S75" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8076,19 +8086,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8103,44 +8103,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128806001</v>
+        <v>128806067</v>
       </c>
       <c r="B76" t="n">
-        <v>87003</v>
+        <v>86922</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717159</v>
+        <v>717298</v>
       </c>
       <c r="R76" t="n">
-        <v>6373378</v>
+        <v>6373345</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8212,10 +8212,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128815117</v>
+        <v>128806001</v>
       </c>
       <c r="B77" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8243,14 +8243,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717416</v>
+        <v>717159</v>
       </c>
       <c r="R77" t="n">
-        <v>6373167</v>
+        <v>6373378</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8297,57 +8297,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128806067</v>
+        <v>128815117</v>
       </c>
       <c r="B78" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717298</v>
+        <v>717416</v>
       </c>
       <c r="R78" t="n">
-        <v>6373345</v>
+        <v>6373167</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,12 +8394,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
         <v>128806047</v>
       </c>
       <c r="B79" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>128815128</v>
       </c>
       <c r="B82" t="n">
-        <v>91035</v>
+        <v>91040</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>128813055</v>
       </c>
       <c r="B83" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>128806026</v>
       </c>
       <c r="B84" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>128806031</v>
       </c>
       <c r="B85" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9112,32 +9112,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128813078</v>
+        <v>128806318</v>
       </c>
       <c r="B86" t="n">
-        <v>86806</v>
+        <v>86959</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717243</v>
+        <v>717062</v>
       </c>
       <c r="R86" t="n">
-        <v>6373192</v>
+        <v>6373304</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,84 +9180,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128815156</v>
+        <v>128813061</v>
       </c>
       <c r="B87" t="n">
-        <v>86921</v>
+        <v>86875</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717444</v>
+        <v>717085</v>
       </c>
       <c r="R87" t="n">
-        <v>6373273</v>
+        <v>6373261</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9287,9 +9278,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9304,22 +9305,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815120</v>
+        <v>128813078</v>
       </c>
       <c r="B88" t="n">
-        <v>87003</v>
+        <v>86806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9327,34 +9328,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717479</v>
+        <v>717243</v>
       </c>
       <c r="R88" t="n">
-        <v>6373226</v>
+        <v>6373192</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9384,9 +9385,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9401,44 +9412,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815130</v>
+        <v>128815156</v>
       </c>
       <c r="B89" t="n">
-        <v>91035</v>
+        <v>86922</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9448,10 +9459,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717326</v>
+        <v>717444</v>
       </c>
       <c r="R89" t="n">
-        <v>6373267</v>
+        <v>6373273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9492,7 +9503,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9511,53 +9521,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128806007</v>
+        <v>128815120</v>
       </c>
       <c r="B90" t="n">
-        <v>57713</v>
+        <v>87004</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>3767</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717083</v>
+        <v>717479</v>
       </c>
       <c r="R90" t="n">
-        <v>6373260</v>
+        <v>6373226</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9604,22 +9606,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128813061</v>
+        <v>128815130</v>
       </c>
       <c r="B91" t="n">
-        <v>86874</v>
+        <v>91040</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9627,34 +9629,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>1357</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717085</v>
+        <v>717326</v>
       </c>
       <c r="R91" t="n">
-        <v>6373261</v>
+        <v>6373267</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9684,49 +9686,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806318</v>
+        <v>128806007</v>
       </c>
       <c r="B92" t="n">
-        <v>86958</v>
+        <v>57713</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9734,34 +9727,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717062</v>
+        <v>717083</v>
       </c>
       <c r="R92" t="n">
-        <v>6373304</v>
+        <v>6373260</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9802,51 +9803,50 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128813069</v>
+        <v>128806071</v>
       </c>
       <c r="B93" t="n">
-        <v>86980</v>
+        <v>86922</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717134</v>
+        <v>717287</v>
       </c>
       <c r="R93" t="n">
-        <v>6373192</v>
+        <v>6373292</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9889,19 +9889,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9916,22 +9906,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128813074</v>
+        <v>128815112</v>
       </c>
       <c r="B94" t="n">
-        <v>87015</v>
+        <v>87004</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,30 +9929,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717185</v>
+        <v>717270</v>
       </c>
       <c r="R94" t="n">
-        <v>6373128</v>
+        <v>6373304</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9992,24 +9986,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10024,44 +10003,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815109</v>
+        <v>128815123</v>
       </c>
       <c r="B95" t="n">
-        <v>86901</v>
+        <v>87004</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10071,10 +10050,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717314</v>
+        <v>717500</v>
       </c>
       <c r="R95" t="n">
-        <v>6373229</v>
+        <v>6373237</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10133,10 +10112,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815112</v>
+        <v>128815118</v>
       </c>
       <c r="B96" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10168,10 +10147,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717270</v>
+        <v>717431</v>
       </c>
       <c r="R96" t="n">
-        <v>6373304</v>
+        <v>6373173</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,10 +10209,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128806071</v>
+        <v>128813076</v>
       </c>
       <c r="B97" t="n">
-        <v>86921</v>
+        <v>90271</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10241,34 +10220,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3674</v>
+        <v>245042</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717287</v>
+        <v>717322</v>
       </c>
       <c r="R97" t="n">
-        <v>6373292</v>
+        <v>6373147</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10298,39 +10280,50 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815123</v>
+        <v>128813069</v>
       </c>
       <c r="B98" t="n">
-        <v>87003</v>
+        <v>86981</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10338,34 +10331,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717500</v>
+        <v>717134</v>
       </c>
       <c r="R98" t="n">
-        <v>6373237</v>
+        <v>6373192</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10395,9 +10388,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10412,22 +10415,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128815118</v>
+        <v>128813074</v>
       </c>
       <c r="B99" t="n">
-        <v>87003</v>
+        <v>87016</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10435,34 +10438,30 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717431</v>
+        <v>717185</v>
       </c>
       <c r="R99" t="n">
-        <v>6373173</v>
+        <v>6373128</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,9 +10491,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10509,60 +10523,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128813076</v>
+        <v>128815109</v>
       </c>
       <c r="B100" t="n">
-        <v>90266</v>
+        <v>86902</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>245042</v>
+        <v>473</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717322</v>
+        <v>717314</v>
       </c>
       <c r="R100" t="n">
-        <v>6373147</v>
+        <v>6373229</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10592,40 +10603,29 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10635,7 +10635,7 @@
         <v>128815137</v>
       </c>
       <c r="B101" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>128813052</v>
       </c>
       <c r="B102" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>128815151</v>
       </c>
       <c r="B103" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>128815149</v>
       </c>
       <c r="B104" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11031,10 +11031,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815110</v>
+        <v>128815129</v>
       </c>
       <c r="B105" t="n">
-        <v>87003</v>
+        <v>91040</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11042,21 +11042,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717281</v>
+        <v>717424</v>
       </c>
       <c r="R105" t="n">
-        <v>6373300</v>
+        <v>6373165</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11128,45 +11128,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128815129</v>
+        <v>128813073</v>
       </c>
       <c r="B106" t="n">
-        <v>91035</v>
+        <v>92830</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1357</v>
+        <v>5964</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717424</v>
+        <v>717453</v>
       </c>
       <c r="R106" t="n">
-        <v>6373165</v>
+        <v>6373125</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11196,74 +11199,85 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806323</v>
+        <v>128815110</v>
       </c>
       <c r="B107" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717241</v>
+        <v>717281</v>
       </c>
       <c r="R107" t="n">
-        <v>6373264</v>
+        <v>6373300</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11304,29 +11318,28 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806028</v>
+        <v>128806323</v>
       </c>
       <c r="B108" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11358,10 +11371,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717179</v>
+        <v>717241</v>
       </c>
       <c r="R108" t="n">
-        <v>6373374</v>
+        <v>6373264</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11409,22 +11422,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806320</v>
+        <v>128806028</v>
       </c>
       <c r="B109" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11456,10 +11469,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717131</v>
+        <v>717179</v>
       </c>
       <c r="R109" t="n">
-        <v>6373249</v>
+        <v>6373374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11507,60 +11520,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128813073</v>
+        <v>128806320</v>
       </c>
       <c r="B110" t="n">
-        <v>92823</v>
+        <v>86959</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717453</v>
+        <v>717131</v>
       </c>
       <c r="R110" t="n">
-        <v>6373125</v>
+        <v>6373249</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11590,19 +11600,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,57 +11618,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128815121</v>
+        <v>128813568</v>
       </c>
       <c r="B111" t="n">
-        <v>87003</v>
+        <v>86902</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717499</v>
+        <v>717322</v>
       </c>
       <c r="R111" t="n">
-        <v>6373239</v>
+        <v>6373203</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,9 +11698,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11715,22 +11725,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806313</v>
+        <v>128813063</v>
       </c>
       <c r="B112" t="n">
-        <v>87003</v>
+        <v>92258</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11738,21 +11748,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3767</v>
+        <v>232138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11762,10 +11772,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717369</v>
+        <v>717511</v>
       </c>
       <c r="R112" t="n">
-        <v>6373319</v>
+        <v>6373145</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11795,9 +11805,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11812,22 +11832,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128813568</v>
+        <v>128813048</v>
       </c>
       <c r="B113" t="n">
-        <v>86901</v>
+        <v>86959</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11835,21 +11855,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11859,10 +11879,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717322</v>
+        <v>717248</v>
       </c>
       <c r="R113" t="n">
-        <v>6373203</v>
+        <v>6373196</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11894,7 +11914,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11904,7 +11924,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12037,10 +12057,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128813063</v>
+        <v>128815139</v>
       </c>
       <c r="B115" t="n">
-        <v>92253</v>
+        <v>86875</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12048,34 +12068,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>232138</v>
+        <v>248956</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717511</v>
+        <v>717313</v>
       </c>
       <c r="R115" t="n">
-        <v>6373145</v>
+        <v>6373361</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12105,19 +12125,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12132,22 +12142,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128815139</v>
+        <v>128815121</v>
       </c>
       <c r="B116" t="n">
-        <v>86874</v>
+        <v>87004</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12155,21 +12165,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12179,10 +12189,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717313</v>
+        <v>717499</v>
       </c>
       <c r="R116" t="n">
-        <v>6373361</v>
+        <v>6373239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12241,32 +12251,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128813048</v>
+        <v>128806313</v>
       </c>
       <c r="B117" t="n">
-        <v>86958</v>
+        <v>87004</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12276,10 +12286,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717248</v>
+        <v>717369</v>
       </c>
       <c r="R117" t="n">
-        <v>6373196</v>
+        <v>6373319</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12309,19 +12319,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12336,44 +12336,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806315</v>
+        <v>128813056</v>
       </c>
       <c r="B118" t="n">
-        <v>86806</v>
+        <v>98666</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>424</v>
+        <v>219874</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717165</v>
+        <v>717484</v>
       </c>
       <c r="R118" t="n">
-        <v>6373195</v>
+        <v>6373174</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,9 +12416,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12433,44 +12443,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806312</v>
+        <v>128806032</v>
       </c>
       <c r="B119" t="n">
-        <v>87003</v>
+        <v>86959</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12480,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717332</v>
+        <v>717081</v>
       </c>
       <c r="R119" t="n">
-        <v>6373350</v>
+        <v>6373276</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12524,28 +12534,29 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128815111</v>
+        <v>128806315</v>
       </c>
       <c r="B120" t="n">
-        <v>87003</v>
+        <v>86806</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12553,34 +12564,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717318</v>
+        <v>717165</v>
       </c>
       <c r="R120" t="n">
-        <v>6373242</v>
+        <v>6373195</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12627,12 +12638,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12642,7 +12653,7 @@
         <v>128806347</v>
       </c>
       <c r="B121" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12736,32 +12747,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128813014</v>
+        <v>128806340</v>
       </c>
       <c r="B122" t="n">
-        <v>87003</v>
+        <v>86784</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12771,10 +12782,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717462</v>
+        <v>717314</v>
       </c>
       <c r="R122" t="n">
-        <v>6373231</v>
+        <v>6373345</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12804,19 +12815,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12831,44 +12832,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806340</v>
+        <v>128806312</v>
       </c>
       <c r="B123" t="n">
-        <v>86784</v>
+        <v>87004</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12878,10 +12879,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717314</v>
+        <v>717332</v>
       </c>
       <c r="R123" t="n">
-        <v>6373345</v>
+        <v>6373350</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12940,45 +12941,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128813030</v>
+        <v>128815111</v>
       </c>
       <c r="B124" t="n">
-        <v>86934</v>
+        <v>87004</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717079</v>
+        <v>717318</v>
       </c>
       <c r="R124" t="n">
-        <v>6373300</v>
+        <v>6373242</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13008,19 +13009,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13035,44 +13026,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806331</v>
+        <v>128813014</v>
       </c>
       <c r="B125" t="n">
-        <v>90335</v>
+        <v>87004</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6292</v>
+        <v>3767</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13082,10 +13073,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717106</v>
+        <v>717462</v>
       </c>
       <c r="R125" t="n">
-        <v>6373238</v>
+        <v>6373231</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13115,9 +13106,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13132,22 +13133,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128813056</v>
+        <v>128813030</v>
       </c>
       <c r="B126" t="n">
-        <v>98659</v>
+        <v>86935</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13155,21 +13156,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>1988</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13179,10 +13180,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717484</v>
+        <v>717079</v>
       </c>
       <c r="R126" t="n">
-        <v>6373174</v>
+        <v>6373300</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13214,7 +13215,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13224,7 +13225,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13251,32 +13252,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806032</v>
+        <v>128806331</v>
       </c>
       <c r="B127" t="n">
-        <v>86958</v>
+        <v>90340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>6292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13286,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717081</v>
+        <v>717106</v>
       </c>
       <c r="R127" t="n">
-        <v>6373276</v>
+        <v>6373238</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13330,64 +13331,63 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128815115</v>
+        <v>128813018</v>
       </c>
       <c r="B128" t="n">
-        <v>87003</v>
+        <v>110759</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3767</v>
+        <v>219711</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717424</v>
+        <v>717512</v>
       </c>
       <c r="R128" t="n">
-        <v>6373147</v>
+        <v>6373149</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13417,9 +13417,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13434,53 +13444,57 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128815126</v>
+        <v>128813049</v>
       </c>
       <c r="B129" t="n">
-        <v>87024</v>
+        <v>86959</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3624</v>
+        <v>6003295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717337</v>
+        <v>717330</v>
       </c>
       <c r="R129" t="n">
-        <v>6373382</v>
+        <v>6373178</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13510,9 +13524,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13527,57 +13551,60 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128813080</v>
+        <v>128813075</v>
       </c>
       <c r="B130" t="n">
-        <v>86921</v>
+        <v>86875</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717456</v>
+        <v>717344</v>
       </c>
       <c r="R130" t="n">
-        <v>6373273</v>
+        <v>6373206</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13609,7 +13636,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13619,7 +13646,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13628,6 +13660,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13646,45 +13679,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813018</v>
+        <v>128815115</v>
       </c>
       <c r="B131" t="n">
-        <v>110752</v>
+        <v>87004</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219711</v>
+        <v>3767</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717512</v>
+        <v>717424</v>
       </c>
       <c r="R131" t="n">
-        <v>6373149</v>
+        <v>6373147</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13714,19 +13747,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13741,60 +13764,53 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813075</v>
+        <v>128815126</v>
       </c>
       <c r="B132" t="n">
-        <v>86874</v>
+        <v>87025</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>248956</v>
+        <v>3624</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717344</v>
+        <v>717337</v>
       </c>
       <c r="R132" t="n">
-        <v>6373206</v>
+        <v>6373382</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13824,77 +13840,61 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813049</v>
+        <v>128813080</v>
       </c>
       <c r="B133" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717330</v>
+        <v>717456</v>
       </c>
       <c r="R133" t="n">
-        <v>6373178</v>
+        <v>6373273</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13976,45 +13976,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806319</v>
+        <v>128815155</v>
       </c>
       <c r="B134" t="n">
-        <v>86958</v>
+        <v>86922</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717087</v>
+        <v>717498</v>
       </c>
       <c r="R134" t="n">
-        <v>6373291</v>
+        <v>6373233</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14055,29 +14055,28 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128815155</v>
+        <v>128815133</v>
       </c>
       <c r="B135" t="n">
-        <v>86921</v>
+        <v>86760</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14085,21 +14084,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14109,10 +14108,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717498</v>
+        <v>717314</v>
       </c>
       <c r="R135" t="n">
-        <v>6373233</v>
+        <v>6373361</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14174,7 +14173,7 @@
         <v>128806000</v>
       </c>
       <c r="B136" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14268,10 +14267,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128815133</v>
+        <v>128813027</v>
       </c>
       <c r="B137" t="n">
-        <v>86760</v>
+        <v>91013</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14279,34 +14278,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3762</v>
+        <v>5741</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717314</v>
+        <v>717343</v>
       </c>
       <c r="R137" t="n">
-        <v>6373361</v>
+        <v>6373129</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14336,9 +14335,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14353,44 +14362,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128813027</v>
+        <v>128806319</v>
       </c>
       <c r="B138" t="n">
-        <v>91008</v>
+        <v>86959</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14400,10 +14409,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717343</v>
+        <v>717087</v>
       </c>
       <c r="R138" t="n">
-        <v>6373129</v>
+        <v>6373291</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14433,39 +14442,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14475,7 +14475,7 @@
         <v>128806066</v>
       </c>
       <c r="B139" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>128806070</v>
       </c>
       <c r="B140" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>128813081</v>
       </c>
       <c r="B142" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>128815147</v>
       </c>
       <c r="B143" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14967,32 +14967,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128815124</v>
+        <v>128815150</v>
       </c>
       <c r="B144" t="n">
-        <v>87003</v>
+        <v>86922</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717467</v>
+        <v>717305</v>
       </c>
       <c r="R144" t="n">
-        <v>6373240</v>
+        <v>6373217</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15064,32 +15064,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128815150</v>
+        <v>128815124</v>
       </c>
       <c r="B145" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>717305</v>
+        <v>717467</v>
       </c>
       <c r="R145" t="n">
-        <v>6373217</v>
+        <v>6373240</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15164,7 +15164,7 @@
         <v>128813064</v>
       </c>
       <c r="B146" t="n">
-        <v>91497</v>
+        <v>91502</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128806006</v>
+        <v>128815135</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>86760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717370</v>
+        <v>717476</v>
       </c>
       <c r="R2" t="n">
-        <v>6373322</v>
+        <v>6373242</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -966,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128815113</v>
+        <v>128806348</v>
       </c>
       <c r="B5" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717317</v>
+        <v>717239</v>
       </c>
       <c r="R5" t="n">
-        <v>6373308</v>
+        <v>6373234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,57 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128813022</v>
+        <v>128815113</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>87004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717130</v>
+        <v>717317</v>
       </c>
       <c r="R6" t="n">
-        <v>6373194</v>
+        <v>6373308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1131,19 +1131,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1158,57 +1148,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128815136</v>
+        <v>128806072</v>
       </c>
       <c r="B7" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717412</v>
+        <v>717289</v>
       </c>
       <c r="R7" t="n">
-        <v>6373217</v>
+        <v>6373288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,51 +1239,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806033</v>
+        <v>128813022</v>
       </c>
       <c r="B8" t="n">
-        <v>86959</v>
+        <v>92806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717315</v>
+        <v>717130</v>
       </c>
       <c r="R8" t="n">
-        <v>6373232</v>
+        <v>6373194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1336,62 +1325,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128813034</v>
+        <v>128813071</v>
       </c>
       <c r="B9" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717425</v>
+        <v>717455</v>
       </c>
       <c r="R9" t="n">
-        <v>6373083</v>
+        <v>6373115</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,7 +1434,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1446,7 +1444,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128813071</v>
+        <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>86981</v>
+        <v>92439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>449</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1508,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717455</v>
+        <v>717370</v>
       </c>
       <c r="R10" t="n">
-        <v>6373115</v>
+        <v>6373322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,19 +1539,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,44 +1556,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128815135</v>
+        <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717476</v>
+        <v>717412</v>
       </c>
       <c r="R11" t="n">
-        <v>6373242</v>
+        <v>6373217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,6 +1647,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1677,32 +1666,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128806348</v>
+        <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717239</v>
+        <v>717315</v>
       </c>
       <c r="R12" t="n">
-        <v>6373234</v>
+        <v>6373232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,50 +1745,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128806072</v>
+        <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717289</v>
+        <v>717425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373288</v>
+        <v>6373083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,9 +1832,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,57 +1859,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128815153</v>
+        <v>128805997</v>
       </c>
       <c r="B14" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717341</v>
+        <v>717416</v>
       </c>
       <c r="R14" t="n">
-        <v>6373251</v>
+        <v>6373282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,19 +1956,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128805997</v>
+        <v>128806003</v>
       </c>
       <c r="B15" t="n">
         <v>87004</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717416</v>
+        <v>717431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373282</v>
+        <v>6373255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,45 +2065,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128806003</v>
+        <v>128815153</v>
       </c>
       <c r="B16" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717431</v>
+        <v>717341</v>
       </c>
       <c r="R16" t="n">
-        <v>6373255</v>
+        <v>6373251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,22 +2150,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128815145</v>
+        <v>128806343</v>
       </c>
       <c r="B17" t="n">
-        <v>86925</v>
+        <v>86713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,34 +2173,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037417</v>
+        <v>249278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717299</v>
+        <v>717258</v>
       </c>
       <c r="R17" t="n">
-        <v>6373241</v>
+        <v>6373299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,6 +2238,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2248,22 +2256,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128813050</v>
+        <v>128815145</v>
       </c>
       <c r="B18" t="n">
-        <v>86959</v>
+        <v>86925</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,34 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717330</v>
+        <v>717299</v>
       </c>
       <c r="R18" t="n">
-        <v>6373140</v>
+        <v>6373241</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,46 +2336,37 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813054</v>
+        <v>128813050</v>
       </c>
       <c r="B19" t="n">
         <v>86959</v>
@@ -2402,10 +2401,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717402</v>
+        <v>717330</v>
       </c>
       <c r="R19" t="n">
-        <v>6373098</v>
+        <v>6373140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,7 +2436,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2447,7 +2446,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2474,10 +2473,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128806343</v>
+        <v>128813054</v>
       </c>
       <c r="B20" t="n">
-        <v>86713</v>
+        <v>86959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2485,37 +2484,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717258</v>
+        <v>717402</v>
       </c>
       <c r="R20" t="n">
-        <v>6373299</v>
+        <v>6373098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,14 +2541,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2561,51 +2562,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813032</v>
+        <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717409</v>
+        <v>717316</v>
       </c>
       <c r="R21" t="n">
-        <v>6373057</v>
+        <v>6373307</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,19 +2648,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,57 +2665,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128806324</v>
+        <v>128815134</v>
       </c>
       <c r="B22" t="n">
-        <v>86959</v>
+        <v>86760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717408</v>
+        <v>717316</v>
       </c>
       <c r="R22" t="n">
-        <v>6373296</v>
+        <v>6373365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,26 +2756,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128806027</v>
+        <v>128813032</v>
       </c>
       <c r="B23" t="n">
         <v>86959</v>
@@ -2820,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717195</v>
+        <v>717409</v>
       </c>
       <c r="R23" t="n">
-        <v>6373376</v>
+        <v>6373057</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,37 +2842,46 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128806029</v>
+        <v>128806324</v>
       </c>
       <c r="B24" t="n">
         <v>86959</v>
@@ -2918,10 +2916,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717149</v>
+        <v>717408</v>
       </c>
       <c r="R24" t="n">
-        <v>6373385</v>
+        <v>6373296</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,44 +2967,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128806311</v>
+        <v>128806027</v>
       </c>
       <c r="B25" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3014,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717316</v>
+        <v>717195</v>
       </c>
       <c r="R25" t="n">
-        <v>6373307</v>
+        <v>6373376</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3060,63 +3058,64 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128815134</v>
+        <v>128806029</v>
       </c>
       <c r="B26" t="n">
-        <v>86760</v>
+        <v>86959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717316</v>
+        <v>717149</v>
       </c>
       <c r="R26" t="n">
-        <v>6373365</v>
+        <v>6373385</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,63 +3156,64 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128815122</v>
+        <v>128813028</v>
       </c>
       <c r="B27" t="n">
-        <v>87004</v>
+        <v>91013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717534</v>
+        <v>717490</v>
       </c>
       <c r="R27" t="n">
-        <v>6373182</v>
+        <v>6373178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3243,9 +3243,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3260,19 +3270,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128805998</v>
+        <v>128815122</v>
       </c>
       <c r="B28" t="n">
         <v>87004</v>
@@ -3303,14 +3313,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717299</v>
+        <v>717534</v>
       </c>
       <c r="R28" t="n">
-        <v>6373359</v>
+        <v>6373182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,44 +3367,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128813028</v>
+        <v>128805998</v>
       </c>
       <c r="B29" t="n">
-        <v>91013</v>
+        <v>87004</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717490</v>
+        <v>717299</v>
       </c>
       <c r="R29" t="n">
-        <v>6373178</v>
+        <v>6373359</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3437,19 +3447,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3464,12 +3464,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3690,45 +3690,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128813070</v>
+        <v>128815154</v>
       </c>
       <c r="B32" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717323</v>
+        <v>717416</v>
       </c>
       <c r="R32" t="n">
-        <v>6373241</v>
+        <v>6373159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,19 +3758,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3785,44 +3775,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128813068</v>
+        <v>128806349</v>
       </c>
       <c r="B33" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3832,10 +3822,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717085</v>
+        <v>717337</v>
       </c>
       <c r="R33" t="n">
-        <v>6373275</v>
+        <v>6373337</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,19 +3855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3892,44 +3872,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128806002</v>
+        <v>128806351</v>
       </c>
       <c r="B34" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3919,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717297</v>
+        <v>717390</v>
       </c>
       <c r="R34" t="n">
-        <v>6373295</v>
+        <v>6373317</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3989,44 +3969,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806025</v>
+        <v>128806002</v>
       </c>
       <c r="B35" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4016,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717284</v>
+        <v>717297</v>
       </c>
       <c r="R35" t="n">
-        <v>6373347</v>
+        <v>6373295</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,7 +4060,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4092,37 +4071,41 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128806317</v>
+        <v>128813068</v>
       </c>
       <c r="B36" t="n">
-        <v>92808</v>
+        <v>86981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6047725</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4130,10 +4113,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717367</v>
+        <v>717085</v>
       </c>
       <c r="R36" t="n">
-        <v>6373322</v>
+        <v>6373275</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,75 +4146,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128815154</v>
+        <v>128813070</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717416</v>
+        <v>717323</v>
       </c>
       <c r="R37" t="n">
-        <v>6373159</v>
+        <v>6373241</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4261,9 +4253,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4278,44 +4280,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128806349</v>
+        <v>128806025</v>
       </c>
       <c r="B38" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4325,10 +4327,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717337</v>
+        <v>717284</v>
       </c>
       <c r="R38" t="n">
-        <v>6373337</v>
+        <v>6373347</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,28 +4371,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128806351</v>
+        <v>128806317</v>
       </c>
       <c r="B39" t="n">
-        <v>86922</v>
+        <v>92808</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4398,23 +4401,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>6047725</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4422,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717390</v>
+        <v>717367</v>
       </c>
       <c r="R39" t="n">
-        <v>6373317</v>
+        <v>6373322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,6 +4465,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128813065</v>
+        <v>128815114</v>
       </c>
       <c r="B41" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4592,34 +4592,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717407</v>
+        <v>717431</v>
       </c>
       <c r="R41" t="n">
-        <v>6373048</v>
+        <v>6373147</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,19 +4649,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4676,19 +4666,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815140</v>
+        <v>128813065</v>
       </c>
       <c r="B42" t="n">
         <v>86981</v>
@@ -4719,14 +4709,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717460</v>
+        <v>717407</v>
       </c>
       <c r="R42" t="n">
-        <v>6373180</v>
+        <v>6373048</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4756,9 +4746,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4773,22 +4773,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128815114</v>
+        <v>128815140</v>
       </c>
       <c r="B43" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717431</v>
+        <v>717460</v>
       </c>
       <c r="R43" t="n">
-        <v>6373147</v>
+        <v>6373180</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5087,32 +5087,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128806053</v>
+        <v>128813067</v>
       </c>
       <c r="B46" t="n">
-        <v>86784</v>
+        <v>86981</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717382</v>
+        <v>717325</v>
       </c>
       <c r="R46" t="n">
-        <v>6373309</v>
+        <v>6373229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,9 +5155,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,22 +5182,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128806345</v>
+        <v>128806053</v>
       </c>
       <c r="B47" t="n">
-        <v>86922</v>
+        <v>86784</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5195,21 +5205,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5219,10 +5229,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717170</v>
+        <v>717382</v>
       </c>
       <c r="R47" t="n">
-        <v>6373195</v>
+        <v>6373309</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,44 +5279,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128813046</v>
+        <v>128806345</v>
       </c>
       <c r="B48" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5316,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717216</v>
+        <v>717170</v>
       </c>
       <c r="R48" t="n">
-        <v>6373176</v>
+        <v>6373195</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,19 +5359,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5376,19 +5376,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128813040</v>
+        <v>128813046</v>
       </c>
       <c r="B49" t="n">
         <v>86959</v>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717487</v>
+        <v>717216</v>
       </c>
       <c r="R49" t="n">
-        <v>6373202</v>
+        <v>6373176</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5495,32 +5495,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128813067</v>
+        <v>128813040</v>
       </c>
       <c r="B50" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717325</v>
+        <v>717487</v>
       </c>
       <c r="R50" t="n">
-        <v>6373229</v>
+        <v>6373202</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5602,45 +5602,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128806069</v>
+        <v>128815141</v>
       </c>
       <c r="B51" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717117</v>
+        <v>717505</v>
       </c>
       <c r="R51" t="n">
-        <v>6373208</v>
+        <v>6373241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,22 +5687,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128806334</v>
+        <v>128813042</v>
       </c>
       <c r="B52" t="n">
-        <v>90965</v>
+        <v>86959</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717324</v>
+        <v>717084</v>
       </c>
       <c r="R52" t="n">
-        <v>6373355</v>
+        <v>6373295</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5767,9 +5767,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5784,44 +5794,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128806074</v>
+        <v>128806034</v>
       </c>
       <c r="B53" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5831,10 +5841,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717445</v>
+        <v>717303</v>
       </c>
       <c r="R53" t="n">
-        <v>6373269</v>
+        <v>6373236</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5875,6 +5885,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5886,52 +5897,52 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128813042</v>
+        <v>128815131</v>
       </c>
       <c r="B54" t="n">
-        <v>86959</v>
+        <v>91040</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717084</v>
+        <v>717416</v>
       </c>
       <c r="R54" t="n">
-        <v>6373295</v>
+        <v>6373162</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5961,19 +5972,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:53</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5982,28 +5988,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806034</v>
+        <v>128806334</v>
       </c>
       <c r="B55" t="n">
-        <v>86959</v>
+        <v>90965</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6011,21 +6018,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6035,10 +6042,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717303</v>
+        <v>717324</v>
       </c>
       <c r="R55" t="n">
-        <v>6373236</v>
+        <v>6373355</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6079,64 +6086,63 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128815141</v>
+        <v>128806069</v>
       </c>
       <c r="B56" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717505</v>
+        <v>717117</v>
       </c>
       <c r="R56" t="n">
-        <v>6373241</v>
+        <v>6373208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6183,57 +6189,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128815131</v>
+        <v>128806074</v>
       </c>
       <c r="B57" t="n">
-        <v>91040</v>
+        <v>86922</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717416</v>
+        <v>717445</v>
       </c>
       <c r="R57" t="n">
-        <v>6373162</v>
+        <v>6373269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6268,75 +6274,69 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128815116</v>
+        <v>128806322</v>
       </c>
       <c r="B58" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717420</v>
+        <v>717234</v>
       </c>
       <c r="R58" t="n">
-        <v>6373147</v>
+        <v>6373222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6377,63 +6377,64 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128806330</v>
+        <v>128815116</v>
       </c>
       <c r="B59" t="n">
-        <v>107546</v>
+        <v>87004</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>3767</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717069</v>
+        <v>717420</v>
       </c>
       <c r="R59" t="n">
-        <v>6373282</v>
+        <v>6373147</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,57 +6481,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128806322</v>
+        <v>128815152</v>
       </c>
       <c r="B60" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717234</v>
+        <v>717329</v>
       </c>
       <c r="R60" t="n">
-        <v>6373222</v>
+        <v>6373260</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,29 +6572,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128815152</v>
+        <v>128806054</v>
       </c>
       <c r="B61" t="n">
-        <v>86922</v>
+        <v>86784</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6601,34 +6601,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717329</v>
+        <v>717273</v>
       </c>
       <c r="R61" t="n">
-        <v>6373260</v>
+        <v>6373345</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,22 +6675,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128806054</v>
+        <v>128815148</v>
       </c>
       <c r="B62" t="n">
-        <v>86784</v>
+        <v>86922</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6698,34 +6698,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717273</v>
+        <v>717239</v>
       </c>
       <c r="R62" t="n">
-        <v>6373345</v>
+        <v>6373262</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,57 +6772,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128815148</v>
+        <v>128806330</v>
       </c>
       <c r="B63" t="n">
-        <v>86922</v>
+        <v>107546</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3674</v>
+        <v>220079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717239</v>
+        <v>717069</v>
       </c>
       <c r="R63" t="n">
-        <v>6373262</v>
+        <v>6373282</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6869,44 +6869,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128813066</v>
+        <v>128806326</v>
       </c>
       <c r="B64" t="n">
-        <v>86981</v>
+        <v>86935</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717515</v>
+        <v>717084</v>
       </c>
       <c r="R64" t="n">
-        <v>6373166</v>
+        <v>6373294</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,19 +6949,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6976,44 +6966,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128806333</v>
+        <v>128813079</v>
       </c>
       <c r="B65" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7023,10 +7013,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717331</v>
+        <v>717315</v>
       </c>
       <c r="R65" t="n">
-        <v>6373327</v>
+        <v>6373221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7056,9 +7046,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,19 +7073,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128813079</v>
+        <v>128806350</v>
       </c>
       <c r="B66" t="n">
         <v>86922</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717315</v>
+        <v>717330</v>
       </c>
       <c r="R66" t="n">
-        <v>6373221</v>
+        <v>6373328</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7153,19 +7153,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7180,44 +7170,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128806350</v>
+        <v>128813012</v>
       </c>
       <c r="B67" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7227,10 +7217,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717330</v>
+        <v>717435</v>
       </c>
       <c r="R67" t="n">
-        <v>6373328</v>
+        <v>6373156</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7260,9 +7250,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7277,22 +7277,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128813012</v>
+        <v>128813066</v>
       </c>
       <c r="B68" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717435</v>
+        <v>717515</v>
       </c>
       <c r="R68" t="n">
-        <v>6373156</v>
+        <v>6373166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7396,48 +7396,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128806342</v>
+        <v>128806333</v>
       </c>
       <c r="B69" t="n">
-        <v>86713</v>
+        <v>86981</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>249278</v>
+        <v>449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717179</v>
+        <v>717331</v>
       </c>
       <c r="R69" t="n">
-        <v>6373227</v>
+        <v>6373327</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7472,18 +7469,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7502,45 +7493,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806326</v>
+        <v>128806342</v>
       </c>
       <c r="B70" t="n">
-        <v>86935</v>
+        <v>86713</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717084</v>
+        <v>717179</v>
       </c>
       <c r="R70" t="n">
-        <v>6373294</v>
+        <v>6373227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7575,12 +7569,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7804,48 +7804,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128813020</v>
+        <v>128806041</v>
       </c>
       <c r="B73" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717395</v>
+        <v>717150</v>
       </c>
       <c r="R73" t="n">
-        <v>6373086</v>
+        <v>6373384</v>
       </c>
       <c r="S73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7872,93 +7881,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128806041</v>
+        <v>128806046</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>86981</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717150</v>
+        <v>717129</v>
       </c>
       <c r="R74" t="n">
-        <v>6373384</v>
+        <v>6373201</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7999,7 +7990,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8018,32 +8008,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128806046</v>
+        <v>128813020</v>
       </c>
       <c r="B75" t="n">
-        <v>86981</v>
+        <v>57713</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8053,13 +8043,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717129</v>
+        <v>717395</v>
       </c>
       <c r="R75" t="n">
-        <v>6373201</v>
+        <v>6373086</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8086,9 +8076,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8103,44 +8103,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128806067</v>
+        <v>128806047</v>
       </c>
       <c r="B76" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717298</v>
+        <v>717290</v>
       </c>
       <c r="R76" t="n">
-        <v>6373345</v>
+        <v>6373221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8212,10 +8212,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806001</v>
+        <v>128815128</v>
       </c>
       <c r="B77" t="n">
-        <v>87004</v>
+        <v>91040</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,34 +8223,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717159</v>
+        <v>717418</v>
       </c>
       <c r="R77" t="n">
-        <v>6373378</v>
+        <v>6373171</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8291,25 +8291,26 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128815117</v>
+        <v>128806001</v>
       </c>
       <c r="B78" t="n">
         <v>87004</v>
@@ -8340,14 +8341,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717416</v>
+        <v>717159</v>
       </c>
       <c r="R78" t="n">
-        <v>6373167</v>
+        <v>6373378</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,22 +8395,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128806047</v>
+        <v>128815117</v>
       </c>
       <c r="B79" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8417,34 +8418,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717290</v>
+        <v>717416</v>
       </c>
       <c r="R79" t="n">
-        <v>6373221</v>
+        <v>6373167</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8491,60 +8492,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128806316</v>
+        <v>128806067</v>
       </c>
       <c r="B80" t="n">
-        <v>86806</v>
+        <v>86922</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717125</v>
+        <v>717298</v>
       </c>
       <c r="R80" t="n">
-        <v>6373250</v>
+        <v>6373345</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,26 +8583,25 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128813077</v>
+        <v>128806316</v>
       </c>
       <c r="B81" t="n">
         <v>86806</v>
@@ -8633,16 +8630,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717116</v>
+        <v>717125</v>
       </c>
       <c r="R81" t="n">
-        <v>6373207</v>
+        <v>6373250</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8672,49 +8672,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128815128</v>
+        <v>128813077</v>
       </c>
       <c r="B82" t="n">
-        <v>91040</v>
+        <v>86806</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8722,34 +8713,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717418</v>
+        <v>717116</v>
       </c>
       <c r="R82" t="n">
-        <v>6373171</v>
+        <v>6373207</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8779,30 +8770,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128806318</v>
+        <v>128806007</v>
       </c>
       <c r="B86" t="n">
-        <v>86959</v>
+        <v>57713</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9123,34 +9123,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717062</v>
+        <v>717083</v>
       </c>
       <c r="R86" t="n">
-        <v>6373304</v>
+        <v>6373260</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9191,19 +9199,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9317,10 +9324,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128813078</v>
+        <v>128815130</v>
       </c>
       <c r="B88" t="n">
-        <v>86806</v>
+        <v>91040</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9328,34 +9335,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>1357</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717243</v>
+        <v>717326</v>
       </c>
       <c r="R88" t="n">
-        <v>6373192</v>
+        <v>6373267</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9385,39 +9392,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9618,10 +9616,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128815130</v>
+        <v>128813078</v>
       </c>
       <c r="B91" t="n">
-        <v>91040</v>
+        <v>86806</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9629,34 +9627,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717326</v>
+        <v>717243</v>
       </c>
       <c r="R91" t="n">
-        <v>6373267</v>
+        <v>6373192</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9686,40 +9684,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806007</v>
+        <v>128806318</v>
       </c>
       <c r="B92" t="n">
-        <v>57713</v>
+        <v>86959</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9727,42 +9734,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717083</v>
+        <v>717062</v>
       </c>
       <c r="R92" t="n">
-        <v>6373260</v>
+        <v>6373304</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9803,63 +9802,64 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806071</v>
+        <v>128815118</v>
       </c>
       <c r="B93" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717287</v>
+        <v>717431</v>
       </c>
       <c r="R93" t="n">
-        <v>6373292</v>
+        <v>6373173</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9906,12 +9906,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10015,45 +10015,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815123</v>
+        <v>128806071</v>
       </c>
       <c r="B95" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717500</v>
+        <v>717287</v>
       </c>
       <c r="R95" t="n">
-        <v>6373237</v>
+        <v>6373292</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10100,19 +10100,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815118</v>
+        <v>128815123</v>
       </c>
       <c r="B96" t="n">
         <v>87004</v>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717431</v>
+        <v>717500</v>
       </c>
       <c r="R96" t="n">
-        <v>6373173</v>
+        <v>6373237</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10209,48 +10209,41 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128813076</v>
+        <v>128813074</v>
       </c>
       <c r="B97" t="n">
-        <v>90271</v>
+        <v>87016</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>245042</v>
+        <v>433</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717322</v>
+        <v>717185</v>
       </c>
       <c r="R97" t="n">
-        <v>6373147</v>
+        <v>6373128</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10282,7 +10275,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10292,7 +10285,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10301,7 +10299,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10320,45 +10317,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128813069</v>
+        <v>128815109</v>
       </c>
       <c r="B98" t="n">
-        <v>86981</v>
+        <v>86902</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717134</v>
+        <v>717314</v>
       </c>
       <c r="R98" t="n">
-        <v>6373192</v>
+        <v>6373229</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10388,19 +10385,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10415,22 +10402,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128813074</v>
+        <v>128813069</v>
       </c>
       <c r="B99" t="n">
-        <v>87016</v>
+        <v>86981</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10438,19 +10425,23 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -10458,10 +10449,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717185</v>
+        <v>717134</v>
       </c>
       <c r="R99" t="n">
-        <v>6373128</v>
+        <v>6373192</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10493,7 +10484,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10503,12 +10494,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10535,45 +10521,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128815109</v>
+        <v>128813076</v>
       </c>
       <c r="B100" t="n">
-        <v>86902</v>
+        <v>90271</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>473</v>
+        <v>245042</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717314</v>
+        <v>717322</v>
       </c>
       <c r="R100" t="n">
-        <v>6373229</v>
+        <v>6373147</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10603,29 +10592,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10837,32 +10837,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128815151</v>
+        <v>128815129</v>
       </c>
       <c r="B103" t="n">
-        <v>86922</v>
+        <v>91040</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717270</v>
+        <v>717424</v>
       </c>
       <c r="R103" t="n">
-        <v>6373304</v>
+        <v>6373165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10934,7 +10934,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128815149</v>
+        <v>128815151</v>
       </c>
       <c r="B104" t="n">
         <v>86922</v>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717269</v>
+        <v>717270</v>
       </c>
       <c r="R104" t="n">
-        <v>6373207</v>
+        <v>6373304</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815129</v>
+        <v>128815149</v>
       </c>
       <c r="B105" t="n">
-        <v>91040</v>
+        <v>86922</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717424</v>
+        <v>717269</v>
       </c>
       <c r="R105" t="n">
-        <v>6373165</v>
+        <v>6373207</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11128,48 +11128,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128813073</v>
+        <v>128815110</v>
       </c>
       <c r="B106" t="n">
-        <v>92830</v>
+        <v>87004</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5964</v>
+        <v>3767</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717453</v>
+        <v>717281</v>
       </c>
       <c r="R106" t="n">
-        <v>6373125</v>
+        <v>6373300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11199,85 +11196,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128815110</v>
+        <v>128813073</v>
       </c>
       <c r="B107" t="n">
-        <v>87004</v>
+        <v>92830</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3767</v>
+        <v>5964</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717281</v>
+        <v>717453</v>
       </c>
       <c r="R107" t="n">
-        <v>6373300</v>
+        <v>6373125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11307,29 +11296,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11630,45 +11630,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813568</v>
+        <v>128815121</v>
       </c>
       <c r="B111" t="n">
-        <v>86902</v>
+        <v>87004</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717322</v>
+        <v>717499</v>
       </c>
       <c r="R111" t="n">
-        <v>6373203</v>
+        <v>6373239</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,19 +11698,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11725,22 +11715,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128813063</v>
+        <v>128806313</v>
       </c>
       <c r="B112" t="n">
-        <v>92258</v>
+        <v>87004</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11748,21 +11738,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>232138</v>
+        <v>3767</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11772,10 +11762,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717511</v>
+        <v>717369</v>
       </c>
       <c r="R112" t="n">
-        <v>6373145</v>
+        <v>6373319</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11805,19 +11795,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11832,22 +11812,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128813048</v>
+        <v>128813568</v>
       </c>
       <c r="B113" t="n">
-        <v>86959</v>
+        <v>86902</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11855,21 +11835,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6003295</v>
+        <v>473</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11879,10 +11859,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717248</v>
+        <v>717322</v>
       </c>
       <c r="R113" t="n">
-        <v>6373196</v>
+        <v>6373203</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11914,7 +11894,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -11924,7 +11904,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11951,48 +11931,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128806055</v>
+        <v>128813063</v>
       </c>
       <c r="B114" t="n">
-        <v>86713</v>
+        <v>92258</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>249278</v>
+        <v>232138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717283</v>
+        <v>717511</v>
       </c>
       <c r="R114" t="n">
-        <v>6373299</v>
+        <v>6373145</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12022,14 +11999,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12038,64 +12020,66 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815139</v>
+        <v>128806055</v>
       </c>
       <c r="B115" t="n">
-        <v>86875</v>
+        <v>86713</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717313</v>
+        <v>717283</v>
       </c>
       <c r="R115" t="n">
-        <v>6373361</v>
+        <v>6373299</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12130,34 +12114,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128815121</v>
+        <v>128815139</v>
       </c>
       <c r="B116" t="n">
-        <v>87004</v>
+        <v>86875</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12165,21 +12155,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12189,10 +12179,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717499</v>
+        <v>717313</v>
       </c>
       <c r="R116" t="n">
-        <v>6373239</v>
+        <v>6373361</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12251,32 +12241,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806313</v>
+        <v>128813048</v>
       </c>
       <c r="B117" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12286,10 +12276,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717369</v>
+        <v>717248</v>
       </c>
       <c r="R117" t="n">
-        <v>6373319</v>
+        <v>6373196</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12319,9 +12309,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12336,44 +12336,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128813056</v>
+        <v>128806032</v>
       </c>
       <c r="B118" t="n">
-        <v>98666</v>
+        <v>86959</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717484</v>
+        <v>717081</v>
       </c>
       <c r="R118" t="n">
-        <v>6373174</v>
+        <v>6373276</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,71 +12416,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806032</v>
+        <v>128813030</v>
       </c>
       <c r="B119" t="n">
-        <v>86959</v>
+        <v>86935</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12481,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717081</v>
+        <v>717079</v>
       </c>
       <c r="R119" t="n">
-        <v>6373276</v>
+        <v>6373300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12523,30 +12514,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806347</v>
+        <v>128806331</v>
       </c>
       <c r="B121" t="n">
-        <v>86922</v>
+        <v>90340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12661,21 +12661,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3674</v>
+        <v>6292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12685,10 +12685,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717092</v>
+        <v>717106</v>
       </c>
       <c r="R121" t="n">
-        <v>6373322</v>
+        <v>6373238</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12747,10 +12747,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128806340</v>
+        <v>128813056</v>
       </c>
       <c r="B122" t="n">
-        <v>86784</v>
+        <v>98666</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12758,21 +12758,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3712</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12782,10 +12782,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717314</v>
+        <v>717484</v>
       </c>
       <c r="R122" t="n">
-        <v>6373345</v>
+        <v>6373174</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12815,9 +12815,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12832,12 +12842,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13038,32 +13048,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128813014</v>
+        <v>128806347</v>
       </c>
       <c r="B125" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13073,10 +13083,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717462</v>
+        <v>717092</v>
       </c>
       <c r="R125" t="n">
-        <v>6373231</v>
+        <v>6373322</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13106,19 +13116,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13133,44 +13133,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128813030</v>
+        <v>128813014</v>
       </c>
       <c r="B126" t="n">
-        <v>86935</v>
+        <v>87004</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13180,10 +13180,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717079</v>
+        <v>717462</v>
       </c>
       <c r="R126" t="n">
-        <v>6373300</v>
+        <v>6373231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13252,10 +13252,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806331</v>
+        <v>128806340</v>
       </c>
       <c r="B127" t="n">
-        <v>90340</v>
+        <v>86784</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13263,21 +13263,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6292</v>
+        <v>3712</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717106</v>
+        <v>717314</v>
       </c>
       <c r="R127" t="n">
-        <v>6373238</v>
+        <v>6373345</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13349,45 +13349,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128813018</v>
+        <v>128815115</v>
       </c>
       <c r="B128" t="n">
-        <v>110759</v>
+        <v>87004</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219711</v>
+        <v>3767</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717512</v>
+        <v>717424</v>
       </c>
       <c r="R128" t="n">
-        <v>6373149</v>
+        <v>6373147</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13417,19 +13417,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13444,44 +13434,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128813049</v>
+        <v>128813080</v>
       </c>
       <c r="B129" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13491,10 +13481,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717330</v>
+        <v>717456</v>
       </c>
       <c r="R129" t="n">
-        <v>6373178</v>
+        <v>6373273</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13526,7 +13516,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13536,7 +13526,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13563,48 +13553,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128813075</v>
+        <v>128813049</v>
       </c>
       <c r="B130" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717344</v>
+        <v>717330</v>
       </c>
       <c r="R130" t="n">
-        <v>6373206</v>
+        <v>6373178</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13636,7 +13623,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13646,12 +13633,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13660,7 +13642,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13679,45 +13660,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128815115</v>
+        <v>128813018</v>
       </c>
       <c r="B131" t="n">
-        <v>87004</v>
+        <v>110759</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3767</v>
+        <v>219711</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717424</v>
+        <v>717512</v>
       </c>
       <c r="R131" t="n">
-        <v>6373147</v>
+        <v>6373149</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13747,9 +13728,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13764,53 +13755,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128815126</v>
+        <v>128813075</v>
       </c>
       <c r="B132" t="n">
-        <v>87025</v>
+        <v>86875</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3624</v>
+        <v>248956</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717337</v>
+        <v>717344</v>
       </c>
       <c r="R132" t="n">
-        <v>6373382</v>
+        <v>6373206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13840,39 +13838,55 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813080</v>
+        <v>128815126</v>
       </c>
       <c r="B133" t="n">
-        <v>86922</v>
+        <v>87025</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13880,34 +13894,30 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717456</v>
+        <v>717337</v>
       </c>
       <c r="R133" t="n">
-        <v>6373273</v>
+        <v>6373382</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13937,19 +13947,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>08:59</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13964,22 +13964,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128815155</v>
+        <v>128813027</v>
       </c>
       <c r="B134" t="n">
-        <v>86922</v>
+        <v>91013</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13987,34 +13987,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717498</v>
+        <v>717343</v>
       </c>
       <c r="R134" t="n">
-        <v>6373233</v>
+        <v>6373129</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14044,9 +14044,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14061,22 +14071,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128815133</v>
+        <v>128815155</v>
       </c>
       <c r="B135" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14084,21 +14094,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14108,10 +14118,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717314</v>
+        <v>717498</v>
       </c>
       <c r="R135" t="n">
-        <v>6373361</v>
+        <v>6373233</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14267,10 +14277,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128813027</v>
+        <v>128815133</v>
       </c>
       <c r="B137" t="n">
-        <v>91013</v>
+        <v>86760</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14278,34 +14288,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5741</v>
+        <v>3762</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717343</v>
+        <v>717314</v>
       </c>
       <c r="R137" t="n">
-        <v>6373129</v>
+        <v>6373361</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14335,19 +14345,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>10:05</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14362,12 +14362,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -14967,32 +14967,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128815150</v>
+        <v>128815124</v>
       </c>
       <c r="B144" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717305</v>
+        <v>717467</v>
       </c>
       <c r="R144" t="n">
-        <v>6373217</v>
+        <v>6373240</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15064,32 +15064,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128815124</v>
+        <v>128815150</v>
       </c>
       <c r="B145" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>717467</v>
+        <v>717305</v>
       </c>
       <c r="R145" t="n">
-        <v>6373240</v>
+        <v>6373217</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128815135</v>
+        <v>128806006</v>
       </c>
       <c r="B2" t="n">
-        <v>86760</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717476</v>
+        <v>717370</v>
       </c>
       <c r="R2" t="n">
-        <v>6373242</v>
+        <v>6373322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128805999</v>
+        <v>128813071</v>
       </c>
       <c r="B3" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717287</v>
+        <v>717455</v>
       </c>
       <c r="R3" t="n">
-        <v>6373354</v>
+        <v>6373115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,9 +840,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128806048</v>
+        <v>128806348</v>
       </c>
       <c r="B4" t="n">
-        <v>90926</v>
+        <v>86922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717322</v>
+        <v>717239</v>
       </c>
       <c r="R4" t="n">
-        <v>6373213</v>
+        <v>6373234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806348</v>
+        <v>128806072</v>
       </c>
       <c r="B5" t="n">
         <v>86922</v>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717239</v>
+        <v>717289</v>
       </c>
       <c r="R5" t="n">
-        <v>6373234</v>
+        <v>6373288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,57 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128815113</v>
+        <v>128813022</v>
       </c>
       <c r="B6" t="n">
-        <v>87004</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717317</v>
+        <v>717130</v>
       </c>
       <c r="R6" t="n">
-        <v>6373308</v>
+        <v>6373194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1131,9 +1141,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128806072</v>
+        <v>128815135</v>
       </c>
       <c r="B7" t="n">
-        <v>86922</v>
+        <v>86760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717289</v>
+        <v>717476</v>
       </c>
       <c r="R7" t="n">
-        <v>6373288</v>
+        <v>6373242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,44 +1265,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128813022</v>
+        <v>128805999</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>87004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717130</v>
+        <v>717287</v>
       </c>
       <c r="R8" t="n">
-        <v>6373194</v>
+        <v>6373354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1325,19 +1345,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1352,22 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128813071</v>
+        <v>128815113</v>
       </c>
       <c r="B9" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,34 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717455</v>
+        <v>717317</v>
       </c>
       <c r="R9" t="n">
-        <v>6373115</v>
+        <v>6373308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1432,19 +1442,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,22 +1459,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128806006</v>
+        <v>128806048</v>
       </c>
       <c r="B10" t="n">
-        <v>92439</v>
+        <v>90926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>4188</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717370</v>
+        <v>717322</v>
       </c>
       <c r="R10" t="n">
-        <v>6373322</v>
+        <v>6373213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1871,45 +1871,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128805997</v>
+        <v>128815145</v>
       </c>
       <c r="B14" t="n">
-        <v>87004</v>
+        <v>86925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>6037417</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717416</v>
+        <v>717299</v>
       </c>
       <c r="R14" t="n">
-        <v>6373282</v>
+        <v>6373241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,63 +1950,64 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128806003</v>
+        <v>128815153</v>
       </c>
       <c r="B15" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717431</v>
+        <v>717341</v>
       </c>
       <c r="R15" t="n">
-        <v>6373255</v>
+        <v>6373251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,57 +2054,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815153</v>
+        <v>128806343</v>
       </c>
       <c r="B16" t="n">
-        <v>86922</v>
+        <v>86713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717341</v>
+        <v>717258</v>
       </c>
       <c r="R16" t="n">
-        <v>6373251</v>
+        <v>6373299</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,34 +2142,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128806343</v>
+        <v>128813050</v>
       </c>
       <c r="B17" t="n">
-        <v>86713</v>
+        <v>86959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,37 +2183,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717258</v>
+        <v>717330</v>
       </c>
       <c r="R17" t="n">
-        <v>6373299</v>
+        <v>6373140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,14 +2240,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2249,29 +2261,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128815145</v>
+        <v>128813054</v>
       </c>
       <c r="B18" t="n">
-        <v>86925</v>
+        <v>86959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2290,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717299</v>
+        <v>717402</v>
       </c>
       <c r="R18" t="n">
-        <v>6373241</v>
+        <v>6373098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,62 +2347,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813050</v>
+        <v>128805997</v>
       </c>
       <c r="B19" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2401,10 +2421,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717330</v>
+        <v>717416</v>
       </c>
       <c r="R19" t="n">
-        <v>6373140</v>
+        <v>6373282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,19 +2454,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2461,44 +2471,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128813054</v>
+        <v>128806003</v>
       </c>
       <c r="B20" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2508,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717402</v>
+        <v>717431</v>
       </c>
       <c r="R20" t="n">
-        <v>6373098</v>
+        <v>6373255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,19 +2551,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2568,12 +2568,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3175,45 +3175,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128813028</v>
+        <v>128815122</v>
       </c>
       <c r="B27" t="n">
-        <v>91013</v>
+        <v>87004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717490</v>
+        <v>717534</v>
       </c>
       <c r="R27" t="n">
-        <v>6373178</v>
+        <v>6373182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3243,19 +3243,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3270,19 +3260,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128815122</v>
+        <v>128805998</v>
       </c>
       <c r="B28" t="n">
         <v>87004</v>
@@ -3313,14 +3303,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717534</v>
+        <v>717299</v>
       </c>
       <c r="R28" t="n">
-        <v>6373182</v>
+        <v>6373359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,44 +3357,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128805998</v>
+        <v>128813028</v>
       </c>
       <c r="B29" t="n">
-        <v>87004</v>
+        <v>91013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717299</v>
+        <v>717490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373359</v>
+        <v>6373178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,9 +3437,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3464,12 +3464,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3690,45 +3690,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128815154</v>
+        <v>128806025</v>
       </c>
       <c r="B32" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717416</v>
+        <v>717284</v>
       </c>
       <c r="R32" t="n">
-        <v>6373159</v>
+        <v>6373347</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3769,28 +3769,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128806349</v>
+        <v>128806317</v>
       </c>
       <c r="B33" t="n">
-        <v>86922</v>
+        <v>92808</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3798,23 +3799,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>6047725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3822,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717337</v>
+        <v>717367</v>
       </c>
       <c r="R33" t="n">
-        <v>6373337</v>
+        <v>6373322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3866,6 +3863,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3884,32 +3882,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128806351</v>
+        <v>128813070</v>
       </c>
       <c r="B34" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3919,10 +3917,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717390</v>
+        <v>717323</v>
       </c>
       <c r="R34" t="n">
-        <v>6373317</v>
+        <v>6373241</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3952,9 +3950,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3969,22 +3977,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806002</v>
+        <v>128813068</v>
       </c>
       <c r="B35" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3992,21 +4000,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4016,10 +4024,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717297</v>
+        <v>717085</v>
       </c>
       <c r="R35" t="n">
-        <v>6373295</v>
+        <v>6373275</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4049,9 +4057,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4066,57 +4084,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128813068</v>
+        <v>128815154</v>
       </c>
       <c r="B36" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717085</v>
+        <v>717416</v>
       </c>
       <c r="R36" t="n">
-        <v>6373275</v>
+        <v>6373159</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4146,19 +4164,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4173,44 +4181,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128813070</v>
+        <v>128806349</v>
       </c>
       <c r="B37" t="n">
-        <v>86981</v>
+        <v>86922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4220,10 +4228,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717323</v>
+        <v>717337</v>
       </c>
       <c r="R37" t="n">
-        <v>6373241</v>
+        <v>6373337</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,19 +4261,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,44 +4278,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128806025</v>
+        <v>128806351</v>
       </c>
       <c r="B38" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4327,10 +4325,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717284</v>
+        <v>717390</v>
       </c>
       <c r="R38" t="n">
-        <v>6373347</v>
+        <v>6373317</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,49 +4369,52 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128806317</v>
+        <v>128806002</v>
       </c>
       <c r="B39" t="n">
-        <v>92808</v>
+        <v>87004</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6047725</v>
+        <v>3767</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4421,10 +4422,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717367</v>
+        <v>717297</v>
       </c>
       <c r="R39" t="n">
-        <v>6373322</v>
+        <v>6373295</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4465,19 +4466,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4581,45 +4581,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128815114</v>
+        <v>128813036</v>
       </c>
       <c r="B41" t="n">
-        <v>87004</v>
+        <v>86959</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717431</v>
+        <v>717436</v>
       </c>
       <c r="R41" t="n">
-        <v>6373147</v>
+        <v>6373168</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,9 +4649,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4666,44 +4676,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128813065</v>
+        <v>128806035</v>
       </c>
       <c r="B42" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4713,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717407</v>
+        <v>717263</v>
       </c>
       <c r="R42" t="n">
-        <v>6373048</v>
+        <v>6373307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4746,46 +4756,37 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128815140</v>
+        <v>128813065</v>
       </c>
       <c r="B43" t="n">
         <v>86981</v>
@@ -4816,14 +4817,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717460</v>
+        <v>717407</v>
       </c>
       <c r="R43" t="n">
-        <v>6373180</v>
+        <v>6373048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,9 +4854,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4870,57 +4881,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128813036</v>
+        <v>128815140</v>
       </c>
       <c r="B44" t="n">
-        <v>86959</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717436</v>
+        <v>717460</v>
       </c>
       <c r="R44" t="n">
-        <v>6373168</v>
+        <v>6373180</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4950,19 +4961,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4977,57 +4978,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128806035</v>
+        <v>128815114</v>
       </c>
       <c r="B45" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717263</v>
+        <v>717431</v>
       </c>
       <c r="R45" t="n">
-        <v>6373307</v>
+        <v>6373147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5068,19 +5069,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5602,45 +5602,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128815141</v>
+        <v>128806334</v>
       </c>
       <c r="B51" t="n">
-        <v>86981</v>
+        <v>90965</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>449</v>
+        <v>3286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717505</v>
+        <v>717324</v>
       </c>
       <c r="R51" t="n">
-        <v>6373241</v>
+        <v>6373355</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,44 +5687,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128813042</v>
+        <v>128806069</v>
       </c>
       <c r="B52" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717084</v>
+        <v>717117</v>
       </c>
       <c r="R52" t="n">
-        <v>6373295</v>
+        <v>6373208</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5767,19 +5767,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5794,44 +5784,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128806034</v>
+        <v>128806074</v>
       </c>
       <c r="B53" t="n">
-        <v>86959</v>
+        <v>86922</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5841,10 +5831,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717303</v>
+        <v>717445</v>
       </c>
       <c r="R53" t="n">
-        <v>6373236</v>
+        <v>6373269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5885,7 +5875,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5897,52 +5886,52 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128815131</v>
+        <v>128813042</v>
       </c>
       <c r="B54" t="n">
-        <v>91040</v>
+        <v>86959</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717416</v>
+        <v>717084</v>
       </c>
       <c r="R54" t="n">
-        <v>6373162</v>
+        <v>6373295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5972,14 +5961,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5988,29 +5982,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806334</v>
+        <v>128806034</v>
       </c>
       <c r="B55" t="n">
-        <v>90965</v>
+        <v>86959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6018,21 +6011,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6042,10 +6035,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717324</v>
+        <v>717303</v>
       </c>
       <c r="R55" t="n">
-        <v>6373355</v>
+        <v>6373236</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6086,63 +6079,64 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128806069</v>
+        <v>128815141</v>
       </c>
       <c r="B56" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717117</v>
+        <v>717505</v>
       </c>
       <c r="R56" t="n">
-        <v>6373208</v>
+        <v>6373241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6189,57 +6183,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128806074</v>
+        <v>128815131</v>
       </c>
       <c r="B57" t="n">
-        <v>86922</v>
+        <v>91040</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717445</v>
+        <v>717416</v>
       </c>
       <c r="R57" t="n">
-        <v>6373269</v>
+        <v>6373162</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,69 +6268,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128806322</v>
+        <v>128815116</v>
       </c>
       <c r="B58" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717234</v>
+        <v>717420</v>
       </c>
       <c r="R58" t="n">
-        <v>6373222</v>
+        <v>6373147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6377,64 +6377,63 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128815116</v>
+        <v>128806330</v>
       </c>
       <c r="B59" t="n">
-        <v>87004</v>
+        <v>107546</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3767</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717420</v>
+        <v>717069</v>
       </c>
       <c r="R59" t="n">
-        <v>6373147</v>
+        <v>6373282</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6481,57 +6480,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128815152</v>
+        <v>128806322</v>
       </c>
       <c r="B60" t="n">
-        <v>86922</v>
+        <v>86959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717329</v>
+        <v>717234</v>
       </c>
       <c r="R60" t="n">
-        <v>6373260</v>
+        <v>6373222</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6572,28 +6571,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128806054</v>
+        <v>128815152</v>
       </c>
       <c r="B61" t="n">
-        <v>86784</v>
+        <v>86922</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6601,34 +6601,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717273</v>
+        <v>717329</v>
       </c>
       <c r="R61" t="n">
-        <v>6373345</v>
+        <v>6373260</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,22 +6675,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128815148</v>
+        <v>128806054</v>
       </c>
       <c r="B62" t="n">
-        <v>86922</v>
+        <v>86784</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6698,34 +6698,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717239</v>
+        <v>717273</v>
       </c>
       <c r="R62" t="n">
-        <v>6373262</v>
+        <v>6373345</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,57 +6772,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128806330</v>
+        <v>128815148</v>
       </c>
       <c r="B63" t="n">
-        <v>107546</v>
+        <v>86922</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>3674</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717069</v>
+        <v>717239</v>
       </c>
       <c r="R63" t="n">
-        <v>6373282</v>
+        <v>6373262</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6869,44 +6869,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128806326</v>
+        <v>128813066</v>
       </c>
       <c r="B64" t="n">
-        <v>86935</v>
+        <v>86981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1988</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717084</v>
+        <v>717515</v>
       </c>
       <c r="R64" t="n">
-        <v>6373294</v>
+        <v>6373166</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,9 +6949,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6966,44 +6976,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128813079</v>
+        <v>128806333</v>
       </c>
       <c r="B65" t="n">
-        <v>86922</v>
+        <v>86981</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7013,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717315</v>
+        <v>717331</v>
       </c>
       <c r="R65" t="n">
-        <v>6373221</v>
+        <v>6373327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7046,19 +7056,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,19 +7073,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128806350</v>
+        <v>128813079</v>
       </c>
       <c r="B66" t="n">
         <v>86922</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717330</v>
+        <v>717315</v>
       </c>
       <c r="R66" t="n">
-        <v>6373328</v>
+        <v>6373221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7153,9 +7153,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7170,44 +7180,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813012</v>
+        <v>128806350</v>
       </c>
       <c r="B67" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7217,10 +7227,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717435</v>
+        <v>717330</v>
       </c>
       <c r="R67" t="n">
-        <v>6373156</v>
+        <v>6373328</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7250,19 +7260,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7277,22 +7277,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128813066</v>
+        <v>128813012</v>
       </c>
       <c r="B68" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717515</v>
+        <v>717435</v>
       </c>
       <c r="R68" t="n">
-        <v>6373166</v>
+        <v>6373156</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7396,32 +7396,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128806333</v>
+        <v>128806036</v>
       </c>
       <c r="B69" t="n">
-        <v>86981</v>
+        <v>86959</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717331</v>
+        <v>717449</v>
       </c>
       <c r="R69" t="n">
-        <v>6373327</v>
+        <v>6373281</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7475,66 +7475,64 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806342</v>
+        <v>128806326</v>
       </c>
       <c r="B70" t="n">
-        <v>86713</v>
+        <v>86935</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717179</v>
+        <v>717084</v>
       </c>
       <c r="R70" t="n">
-        <v>6373227</v>
+        <v>6373294</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7569,18 +7567,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7599,10 +7591,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128813044</v>
+        <v>128806342</v>
       </c>
       <c r="B71" t="n">
-        <v>86959</v>
+        <v>86713</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7610,34 +7602,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717135</v>
+        <v>717179</v>
       </c>
       <c r="R71" t="n">
-        <v>6373174</v>
+        <v>6373227</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7667,19 +7662,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7688,25 +7678,26 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806036</v>
+        <v>128813044</v>
       </c>
       <c r="B72" t="n">
         <v>86959</v>
@@ -7741,10 +7732,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717449</v>
+        <v>717135</v>
       </c>
       <c r="R72" t="n">
-        <v>6373281</v>
+        <v>6373174</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7774,84 +7765,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128806041</v>
+        <v>128806046</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>86981</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717150</v>
+        <v>717129</v>
       </c>
       <c r="R73" t="n">
-        <v>6373384</v>
+        <v>6373201</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7892,7 +7883,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7911,32 +7901,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128806046</v>
+        <v>128813020</v>
       </c>
       <c r="B74" t="n">
-        <v>86981</v>
+        <v>57713</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7946,13 +7936,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717129</v>
+        <v>717395</v>
       </c>
       <c r="R74" t="n">
-        <v>6373201</v>
+        <v>6373086</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7979,9 +7969,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,60 +7996,69 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128813020</v>
+        <v>128806041</v>
       </c>
       <c r="B75" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717395</v>
+        <v>717150</v>
       </c>
       <c r="R75" t="n">
-        <v>6373086</v>
+        <v>6373384</v>
       </c>
       <c r="S75" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8076,39 +8085,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8212,10 +8212,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128815128</v>
+        <v>128806316</v>
       </c>
       <c r="B77" t="n">
-        <v>91040</v>
+        <v>86806</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,34 +8223,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717418</v>
+        <v>717125</v>
       </c>
       <c r="R77" t="n">
-        <v>6373171</v>
+        <v>6373250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8298,22 +8301,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128806001</v>
+        <v>128813077</v>
       </c>
       <c r="B78" t="n">
-        <v>87004</v>
+        <v>86806</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8321,21 +8324,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8345,10 +8348,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717159</v>
+        <v>717116</v>
       </c>
       <c r="R78" t="n">
-        <v>6373378</v>
+        <v>6373207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8378,9 +8381,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8395,22 +8408,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128815117</v>
+        <v>128815128</v>
       </c>
       <c r="B79" t="n">
-        <v>87004</v>
+        <v>91040</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8418,21 +8431,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8442,10 +8455,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717416</v>
+        <v>717418</v>
       </c>
       <c r="R79" t="n">
-        <v>6373167</v>
+        <v>6373171</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8486,6 +8499,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8601,10 +8615,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128806316</v>
+        <v>128806001</v>
       </c>
       <c r="B81" t="n">
-        <v>86806</v>
+        <v>87004</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8612,37 +8626,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717125</v>
+        <v>717159</v>
       </c>
       <c r="R81" t="n">
-        <v>6373250</v>
+        <v>6373378</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8683,29 +8694,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128813077</v>
+        <v>128815117</v>
       </c>
       <c r="B82" t="n">
-        <v>86806</v>
+        <v>87004</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8713,34 +8723,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717116</v>
+        <v>717416</v>
       </c>
       <c r="R82" t="n">
-        <v>6373207</v>
+        <v>6373167</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8770,19 +8780,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8797,44 +8797,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128813055</v>
+        <v>128806026</v>
       </c>
       <c r="B83" t="n">
-        <v>98666</v>
+        <v>86959</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717326</v>
+        <v>717211</v>
       </c>
       <c r="R83" t="n">
-        <v>6373144</v>
+        <v>6373375</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8877,46 +8877,37 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128806026</v>
+        <v>128806031</v>
       </c>
       <c r="B84" t="n">
         <v>86959</v>
@@ -8951,10 +8942,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717211</v>
+        <v>717071</v>
       </c>
       <c r="R84" t="n">
-        <v>6373375</v>
+        <v>6373294</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9014,32 +9005,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128806031</v>
+        <v>128813055</v>
       </c>
       <c r="B85" t="n">
-        <v>86959</v>
+        <v>98666</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>219874</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9049,10 +9040,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717071</v>
+        <v>717326</v>
       </c>
       <c r="R85" t="n">
-        <v>6373294</v>
+        <v>6373144</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9082,83 +9073,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128806007</v>
+        <v>128813061</v>
       </c>
       <c r="B86" t="n">
-        <v>57713</v>
+        <v>86875</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>248956</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717083</v>
+        <v>717085</v>
       </c>
       <c r="R86" t="n">
-        <v>6373260</v>
+        <v>6373261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9188,9 +9180,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9205,44 +9207,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128813061</v>
+        <v>128806318</v>
       </c>
       <c r="B87" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9252,10 +9254,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717085</v>
+        <v>717062</v>
       </c>
       <c r="R87" t="n">
-        <v>6373261</v>
+        <v>6373304</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9285,49 +9287,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815130</v>
+        <v>128813078</v>
       </c>
       <c r="B88" t="n">
-        <v>91040</v>
+        <v>86806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9335,34 +9328,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717326</v>
+        <v>717243</v>
       </c>
       <c r="R88" t="n">
-        <v>6373267</v>
+        <v>6373192</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9392,62 +9385,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815156</v>
+        <v>128815130</v>
       </c>
       <c r="B89" t="n">
-        <v>86922</v>
+        <v>91040</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9457,10 +9459,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717444</v>
+        <v>717326</v>
       </c>
       <c r="R89" t="n">
-        <v>6373273</v>
+        <v>6373267</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9501,6 +9503,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9519,32 +9522,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128815120</v>
+        <v>128815156</v>
       </c>
       <c r="B90" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9554,10 +9557,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717479</v>
+        <v>717444</v>
       </c>
       <c r="R90" t="n">
-        <v>6373226</v>
+        <v>6373273</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9616,45 +9619,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128813078</v>
+        <v>128806007</v>
       </c>
       <c r="B91" t="n">
-        <v>86806</v>
+        <v>57713</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>424</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717243</v>
+        <v>717083</v>
       </c>
       <c r="R91" t="n">
-        <v>6373192</v>
+        <v>6373260</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9684,19 +9695,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9711,57 +9712,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806318</v>
+        <v>128815120</v>
       </c>
       <c r="B92" t="n">
-        <v>86959</v>
+        <v>87004</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717062</v>
+        <v>717479</v>
       </c>
       <c r="R92" t="n">
-        <v>6373304</v>
+        <v>6373226</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9802,64 +9803,63 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128815118</v>
+        <v>128806071</v>
       </c>
       <c r="B93" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717431</v>
+        <v>717287</v>
       </c>
       <c r="R93" t="n">
-        <v>6373173</v>
+        <v>6373292</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9906,22 +9906,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128815112</v>
+        <v>128813069</v>
       </c>
       <c r="B94" t="n">
-        <v>87004</v>
+        <v>86981</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9929,34 +9929,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717270</v>
+        <v>717134</v>
       </c>
       <c r="R94" t="n">
-        <v>6373304</v>
+        <v>6373192</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9986,9 +9986,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10003,46 +10013,42 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128806071</v>
+        <v>128813074</v>
       </c>
       <c r="B95" t="n">
-        <v>86922</v>
+        <v>87016</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3674</v>
+        <v>433</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10050,10 +10056,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717287</v>
+        <v>717185</v>
       </c>
       <c r="R95" t="n">
-        <v>6373292</v>
+        <v>6373128</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10083,9 +10089,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10100,44 +10121,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815123</v>
+        <v>128815109</v>
       </c>
       <c r="B96" t="n">
-        <v>87004</v>
+        <v>86902</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10147,10 +10168,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717500</v>
+        <v>717314</v>
       </c>
       <c r="R96" t="n">
-        <v>6373237</v>
+        <v>6373229</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10209,10 +10230,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128813074</v>
+        <v>128815112</v>
       </c>
       <c r="B97" t="n">
-        <v>87016</v>
+        <v>87004</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10220,30 +10241,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717185</v>
+        <v>717270</v>
       </c>
       <c r="R97" t="n">
-        <v>6373128</v>
+        <v>6373304</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,24 +10298,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10305,44 +10315,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815109</v>
+        <v>128815123</v>
       </c>
       <c r="B98" t="n">
-        <v>86902</v>
+        <v>87004</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10352,10 +10362,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717314</v>
+        <v>717500</v>
       </c>
       <c r="R98" t="n">
-        <v>6373229</v>
+        <v>6373237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10414,10 +10424,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128813069</v>
+        <v>128815118</v>
       </c>
       <c r="B99" t="n">
-        <v>86981</v>
+        <v>87004</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10425,34 +10435,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717134</v>
+        <v>717431</v>
       </c>
       <c r="R99" t="n">
-        <v>6373192</v>
+        <v>6373173</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10482,19 +10492,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10509,12 +10509,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10837,32 +10837,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128815129</v>
+        <v>128815151</v>
       </c>
       <c r="B103" t="n">
-        <v>91040</v>
+        <v>86922</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717424</v>
+        <v>717270</v>
       </c>
       <c r="R103" t="n">
-        <v>6373165</v>
+        <v>6373304</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10934,7 +10934,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128815151</v>
+        <v>128815149</v>
       </c>
       <c r="B104" t="n">
         <v>86922</v>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717270</v>
+        <v>717269</v>
       </c>
       <c r="R104" t="n">
-        <v>6373304</v>
+        <v>6373207</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815149</v>
+        <v>128815129</v>
       </c>
       <c r="B105" t="n">
-        <v>86922</v>
+        <v>91040</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717269</v>
+        <v>717424</v>
       </c>
       <c r="R105" t="n">
-        <v>6373207</v>
+        <v>6373165</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11630,45 +11630,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128815121</v>
+        <v>128813568</v>
       </c>
       <c r="B111" t="n">
-        <v>87004</v>
+        <v>86902</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717499</v>
+        <v>717322</v>
       </c>
       <c r="R111" t="n">
-        <v>6373239</v>
+        <v>6373203</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,9 +11698,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11715,19 +11725,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806313</v>
+        <v>128815121</v>
       </c>
       <c r="B112" t="n">
         <v>87004</v>
@@ -11758,14 +11768,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717369</v>
+        <v>717499</v>
       </c>
       <c r="R112" t="n">
-        <v>6373319</v>
+        <v>6373239</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11812,44 +11822,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128813568</v>
+        <v>128806313</v>
       </c>
       <c r="B113" t="n">
-        <v>86902</v>
+        <v>87004</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11859,10 +11869,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717322</v>
+        <v>717369</v>
       </c>
       <c r="R113" t="n">
-        <v>6373203</v>
+        <v>6373319</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11892,19 +11902,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11919,12 +11919,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12144,45 +12144,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128815139</v>
+        <v>128813048</v>
       </c>
       <c r="B116" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717313</v>
+        <v>717248</v>
       </c>
       <c r="R116" t="n">
-        <v>6373361</v>
+        <v>6373196</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12212,9 +12212,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12229,57 +12239,57 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128813048</v>
+        <v>128815139</v>
       </c>
       <c r="B117" t="n">
-        <v>86959</v>
+        <v>86875</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717248</v>
+        <v>717313</v>
       </c>
       <c r="R117" t="n">
-        <v>6373196</v>
+        <v>6373361</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12309,19 +12319,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12336,44 +12336,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806032</v>
+        <v>128813030</v>
       </c>
       <c r="B118" t="n">
-        <v>86959</v>
+        <v>86935</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717081</v>
+        <v>717079</v>
       </c>
       <c r="R118" t="n">
-        <v>6373276</v>
+        <v>6373300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,62 +12416,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128813030</v>
+        <v>128806312</v>
       </c>
       <c r="B119" t="n">
-        <v>86935</v>
+        <v>87004</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12481,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717079</v>
+        <v>717332</v>
       </c>
       <c r="R119" t="n">
-        <v>6373300</v>
+        <v>6373350</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12514,19 +12523,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12541,22 +12540,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806315</v>
+        <v>128815111</v>
       </c>
       <c r="B120" t="n">
-        <v>86806</v>
+        <v>87004</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12564,34 +12563,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717165</v>
+        <v>717318</v>
       </c>
       <c r="R120" t="n">
-        <v>6373195</v>
+        <v>6373242</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12638,44 +12637,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806331</v>
+        <v>128813014</v>
       </c>
       <c r="B121" t="n">
-        <v>90340</v>
+        <v>87004</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6292</v>
+        <v>3767</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12685,10 +12684,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717106</v>
+        <v>717462</v>
       </c>
       <c r="R121" t="n">
-        <v>6373238</v>
+        <v>6373231</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12718,9 +12717,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12735,22 +12744,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128813056</v>
+        <v>128806331</v>
       </c>
       <c r="B122" t="n">
-        <v>98666</v>
+        <v>90340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12758,21 +12767,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>6292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12782,10 +12791,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717484</v>
+        <v>717106</v>
       </c>
       <c r="R122" t="n">
-        <v>6373174</v>
+        <v>6373238</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12815,19 +12824,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>09:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12842,22 +12841,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806312</v>
+        <v>128806315</v>
       </c>
       <c r="B123" t="n">
-        <v>87004</v>
+        <v>86806</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12865,21 +12864,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12889,10 +12888,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717332</v>
+        <v>717165</v>
       </c>
       <c r="R123" t="n">
-        <v>6373350</v>
+        <v>6373195</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12951,45 +12950,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128815111</v>
+        <v>128806347</v>
       </c>
       <c r="B124" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717318</v>
+        <v>717092</v>
       </c>
       <c r="R124" t="n">
-        <v>6373242</v>
+        <v>6373322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13036,22 +13035,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806347</v>
+        <v>128806340</v>
       </c>
       <c r="B125" t="n">
-        <v>86922</v>
+        <v>86784</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13059,21 +13058,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13083,10 +13082,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717092</v>
+        <v>717314</v>
       </c>
       <c r="R125" t="n">
-        <v>6373322</v>
+        <v>6373345</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13145,32 +13144,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128813014</v>
+        <v>128813056</v>
       </c>
       <c r="B126" t="n">
-        <v>87004</v>
+        <v>98666</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3767</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13180,10 +13179,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717462</v>
+        <v>717484</v>
       </c>
       <c r="R126" t="n">
-        <v>6373231</v>
+        <v>6373174</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13215,7 +13214,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13225,7 +13224,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13252,32 +13251,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806340</v>
+        <v>128806032</v>
       </c>
       <c r="B127" t="n">
-        <v>86784</v>
+        <v>86959</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13286,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717314</v>
+        <v>717081</v>
       </c>
       <c r="R127" t="n">
-        <v>6373345</v>
+        <v>6373276</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13331,18 +13330,19 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13553,45 +13553,41 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128813049</v>
+        <v>128815126</v>
       </c>
       <c r="B130" t="n">
-        <v>86959</v>
+        <v>87025</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>3624</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717330</v>
+        <v>717337</v>
       </c>
       <c r="R130" t="n">
-        <v>6373178</v>
+        <v>6373382</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13621,19 +13617,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13648,12 +13634,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -13767,48 +13753,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813075</v>
+        <v>128813049</v>
       </c>
       <c r="B132" t="n">
-        <v>86875</v>
+        <v>86959</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717344</v>
+        <v>717330</v>
       </c>
       <c r="R132" t="n">
-        <v>6373206</v>
+        <v>6373178</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13840,7 +13823,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13850,12 +13833,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13864,7 +13842,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13883,41 +13860,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128815126</v>
+        <v>128813075</v>
       </c>
       <c r="B133" t="n">
-        <v>87025</v>
+        <v>86875</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3624</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717337</v>
+        <v>717344</v>
       </c>
       <c r="R133" t="n">
-        <v>6373382</v>
+        <v>6373206</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13947,61 +13931,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128813027</v>
+        <v>128806319</v>
       </c>
       <c r="B134" t="n">
-        <v>91013</v>
+        <v>86959</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717343</v>
+        <v>717087</v>
       </c>
       <c r="R134" t="n">
-        <v>6373129</v>
+        <v>6373291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14044,39 +14044,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14374,32 +14365,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806319</v>
+        <v>128813027</v>
       </c>
       <c r="B138" t="n">
-        <v>86959</v>
+        <v>91013</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14409,10 +14400,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717087</v>
+        <v>717343</v>
       </c>
       <c r="R138" t="n">
-        <v>6373291</v>
+        <v>6373129</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,30 +14433,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806008</v>
+        <v>128813081</v>
       </c>
       <c r="B141" t="n">
-        <v>86760</v>
+        <v>86922</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14677,21 +14677,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14701,10 +14701,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717255</v>
+        <v>717161</v>
       </c>
       <c r="R141" t="n">
-        <v>6373321</v>
+        <v>6373174</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14734,9 +14734,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14751,19 +14761,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128813081</v>
+        <v>128815147</v>
       </c>
       <c r="B142" t="n">
         <v>86922</v>
@@ -14794,14 +14804,14 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717161</v>
+        <v>717312</v>
       </c>
       <c r="R142" t="n">
-        <v>6373174</v>
+        <v>6373366</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14831,19 +14841,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14858,19 +14858,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128815147</v>
+        <v>128815150</v>
       </c>
       <c r="B143" t="n">
         <v>86922</v>
@@ -14905,10 +14905,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717312</v>
+        <v>717305</v>
       </c>
       <c r="R143" t="n">
-        <v>6373366</v>
+        <v>6373217</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14967,45 +14967,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128815124</v>
+        <v>128806008</v>
       </c>
       <c r="B144" t="n">
-        <v>87004</v>
+        <v>86760</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717467</v>
+        <v>717255</v>
       </c>
       <c r="R144" t="n">
-        <v>6373240</v>
+        <v>6373321</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15052,44 +15052,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128815150</v>
+        <v>128815124</v>
       </c>
       <c r="B145" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>717305</v>
+        <v>717467</v>
       </c>
       <c r="R145" t="n">
-        <v>6373217</v>
+        <v>6373240</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128806006</v>
+        <v>128815135</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>86764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717370</v>
+        <v>717476</v>
       </c>
       <c r="R2" t="n">
-        <v>6373322</v>
+        <v>6373242</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128813071</v>
+        <v>128805999</v>
       </c>
       <c r="B3" t="n">
-        <v>86981</v>
+        <v>87008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717455</v>
+        <v>717287</v>
       </c>
       <c r="R3" t="n">
-        <v>6373115</v>
+        <v>6373354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +840,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128806348</v>
+        <v>128806048</v>
       </c>
       <c r="B4" t="n">
-        <v>86922</v>
+        <v>90930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717239</v>
+        <v>717322</v>
       </c>
       <c r="R4" t="n">
-        <v>6373234</v>
+        <v>6373213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806072</v>
+        <v>128806348</v>
       </c>
       <c r="B5" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717289</v>
+        <v>717239</v>
       </c>
       <c r="R5" t="n">
-        <v>6373288</v>
+        <v>6373234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,57 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128813022</v>
+        <v>128815113</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>87008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717130</v>
+        <v>717317</v>
       </c>
       <c r="R6" t="n">
-        <v>6373194</v>
+        <v>6373308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,19 +1131,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128815135</v>
+        <v>128806072</v>
       </c>
       <c r="B7" t="n">
-        <v>86760</v>
+        <v>86926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717476</v>
+        <v>717289</v>
       </c>
       <c r="R7" t="n">
-        <v>6373242</v>
+        <v>6373288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128805999</v>
+        <v>128813022</v>
       </c>
       <c r="B8" t="n">
-        <v>87004</v>
+        <v>92810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3767</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717287</v>
+        <v>717130</v>
       </c>
       <c r="R8" t="n">
-        <v>6373354</v>
+        <v>6373194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,9 +1325,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128815113</v>
+        <v>128813071</v>
       </c>
       <c r="B9" t="n">
-        <v>87004</v>
+        <v>86985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1375,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717317</v>
+        <v>717455</v>
       </c>
       <c r="R9" t="n">
-        <v>6373308</v>
+        <v>6373115</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,9 +1432,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,22 +1459,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128806048</v>
+        <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>90926</v>
+        <v>92443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4188</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717322</v>
+        <v>717370</v>
       </c>
       <c r="R10" t="n">
-        <v>6373213</v>
+        <v>6373322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,45 +1871,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128815145</v>
+        <v>128805997</v>
       </c>
       <c r="B14" t="n">
-        <v>86925</v>
+        <v>87008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037417</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717299</v>
+        <v>717416</v>
       </c>
       <c r="R14" t="n">
-        <v>6373241</v>
+        <v>6373282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,64 +1950,63 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128815153</v>
+        <v>128806003</v>
       </c>
       <c r="B15" t="n">
-        <v>86922</v>
+        <v>87008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717341</v>
+        <v>717431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373251</v>
+        <v>6373255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,60 +2053,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128806343</v>
+        <v>128815153</v>
       </c>
       <c r="B16" t="n">
-        <v>86713</v>
+        <v>86926</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717258</v>
+        <v>717341</v>
       </c>
       <c r="R16" t="n">
-        <v>6373299</v>
+        <v>6373251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,40 +2138,34 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813050</v>
+        <v>128806343</v>
       </c>
       <c r="B17" t="n">
-        <v>86959</v>
+        <v>86717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,34 +2173,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717330</v>
+        <v>717258</v>
       </c>
       <c r="R17" t="n">
-        <v>6373140</v>
+        <v>6373299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,19 +2233,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:06</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2261,28 +2249,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128813054</v>
+        <v>128813050</v>
       </c>
       <c r="B18" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717402</v>
+        <v>717330</v>
       </c>
       <c r="R18" t="n">
-        <v>6373098</v>
+        <v>6373140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,7 +2338,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2359,7 +2348,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2386,32 +2375,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805997</v>
+        <v>128813054</v>
       </c>
       <c r="B19" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2421,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717416</v>
+        <v>717402</v>
       </c>
       <c r="R19" t="n">
-        <v>6373282</v>
+        <v>6373098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,9 +2443,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,57 +2470,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128806003</v>
+        <v>128815145</v>
       </c>
       <c r="B20" t="n">
-        <v>87004</v>
+        <v>86929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3767</v>
+        <v>6037417</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717431</v>
+        <v>717299</v>
       </c>
       <c r="R20" t="n">
-        <v>6373255</v>
+        <v>6373241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,18 +2561,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
         <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128815134</v>
       </c>
       <c r="B22" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>128813032</v>
       </c>
       <c r="B23" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>128806324</v>
       </c>
       <c r="B24" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>128806027</v>
       </c>
       <c r="B25" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>128806029</v>
       </c>
       <c r="B26" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,45 +3175,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128815122</v>
+        <v>128813028</v>
       </c>
       <c r="B27" t="n">
-        <v>87004</v>
+        <v>91017</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717534</v>
+        <v>717490</v>
       </c>
       <c r="R27" t="n">
-        <v>6373182</v>
+        <v>6373178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3243,9 +3243,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3260,22 +3270,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128805998</v>
+        <v>128815122</v>
       </c>
       <c r="B28" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,14 +3313,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717299</v>
+        <v>717534</v>
       </c>
       <c r="R28" t="n">
-        <v>6373359</v>
+        <v>6373182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,44 +3367,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128813028</v>
+        <v>128805998</v>
       </c>
       <c r="B29" t="n">
-        <v>91013</v>
+        <v>87008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717490</v>
+        <v>717299</v>
       </c>
       <c r="R29" t="n">
-        <v>6373178</v>
+        <v>6373359</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3437,19 +3447,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3464,66 +3464,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128806042</v>
+        <v>128813051</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>86963</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717134</v>
+        <v>717385</v>
       </c>
       <c r="R30" t="n">
-        <v>6373159</v>
+        <v>6373091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,75 +3544,93 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128813051</v>
+        <v>128806042</v>
       </c>
       <c r="B31" t="n">
-        <v>86959</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717385</v>
+        <v>717134</v>
       </c>
       <c r="R31" t="n">
-        <v>6373091</v>
+        <v>6373159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3651,71 +3660,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128806025</v>
+        <v>128813070</v>
       </c>
       <c r="B32" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717284</v>
+        <v>717323</v>
       </c>
       <c r="R32" t="n">
-        <v>6373347</v>
+        <v>6373241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,60 +3758,73 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128806317</v>
+        <v>128813068</v>
       </c>
       <c r="B33" t="n">
-        <v>92808</v>
+        <v>86985</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6047725</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3819,10 +3832,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717367</v>
+        <v>717085</v>
       </c>
       <c r="R33" t="n">
-        <v>6373322</v>
+        <v>6373275</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3852,62 +3865,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128813070</v>
+        <v>128806349</v>
       </c>
       <c r="B34" t="n">
-        <v>86981</v>
+        <v>86926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3917,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717323</v>
+        <v>717337</v>
       </c>
       <c r="R34" t="n">
-        <v>6373241</v>
+        <v>6373337</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3950,19 +3972,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3977,44 +3989,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128813068</v>
+        <v>128806351</v>
       </c>
       <c r="B35" t="n">
-        <v>86981</v>
+        <v>86926</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4024,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717085</v>
+        <v>717390</v>
       </c>
       <c r="R35" t="n">
-        <v>6373275</v>
+        <v>6373317</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4057,19 +4069,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4084,57 +4086,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128815154</v>
+        <v>128806002</v>
       </c>
       <c r="B36" t="n">
-        <v>86922</v>
+        <v>87008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717416</v>
+        <v>717297</v>
       </c>
       <c r="R36" t="n">
-        <v>6373159</v>
+        <v>6373295</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4181,44 +4183,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128806349</v>
+        <v>128806025</v>
       </c>
       <c r="B37" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4228,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717337</v>
+        <v>717284</v>
       </c>
       <c r="R37" t="n">
-        <v>6373337</v>
+        <v>6373347</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4272,28 +4274,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128806351</v>
+        <v>128806317</v>
       </c>
       <c r="B38" t="n">
-        <v>86922</v>
+        <v>92812</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4301,23 +4304,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>6047725</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4325,10 +4324,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717390</v>
+        <v>717367</v>
       </c>
       <c r="R38" t="n">
-        <v>6373317</v>
+        <v>6373322</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,6 +4368,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4387,45 +4387,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128806002</v>
+        <v>128815154</v>
       </c>
       <c r="B39" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717297</v>
+        <v>717416</v>
       </c>
       <c r="R39" t="n">
-        <v>6373295</v>
+        <v>6373159</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4472,12 +4472,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
         <v>128815143</v>
       </c>
       <c r="B40" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,32 +4581,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128813036</v>
+        <v>128813065</v>
       </c>
       <c r="B41" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717436</v>
+        <v>717407</v>
       </c>
       <c r="R41" t="n">
-        <v>6373168</v>
+        <v>6373048</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4688,45 +4688,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128806035</v>
+        <v>128815140</v>
       </c>
       <c r="B42" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717263</v>
+        <v>717460</v>
       </c>
       <c r="R42" t="n">
-        <v>6373307</v>
+        <v>6373180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4767,29 +4767,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128813065</v>
+        <v>128815114</v>
       </c>
       <c r="B43" t="n">
-        <v>86981</v>
+        <v>87008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,34 +4796,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717407</v>
+        <v>717431</v>
       </c>
       <c r="R43" t="n">
-        <v>6373048</v>
+        <v>6373147</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4854,19 +4853,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4881,57 +4870,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128815140</v>
+        <v>128813036</v>
       </c>
       <c r="B44" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717460</v>
+        <v>717436</v>
       </c>
       <c r="R44" t="n">
-        <v>6373180</v>
+        <v>6373168</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4961,9 +4950,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4978,57 +4977,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128815114</v>
+        <v>128806035</v>
       </c>
       <c r="B45" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717431</v>
+        <v>717263</v>
       </c>
       <c r="R45" t="n">
-        <v>6373147</v>
+        <v>6373307</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5069,50 +5068,51 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128813067</v>
+        <v>128806345</v>
       </c>
       <c r="B46" t="n">
-        <v>86981</v>
+        <v>86926</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717325</v>
+        <v>717170</v>
       </c>
       <c r="R46" t="n">
-        <v>6373229</v>
+        <v>6373195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,19 +5155,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5182,44 +5172,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128806053</v>
+        <v>128813046</v>
       </c>
       <c r="B47" t="n">
-        <v>86784</v>
+        <v>86963</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5229,10 +5219,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717382</v>
+        <v>717216</v>
       </c>
       <c r="R47" t="n">
-        <v>6373309</v>
+        <v>6373176</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5262,9 +5252,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5279,44 +5279,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128806345</v>
+        <v>128813040</v>
       </c>
       <c r="B48" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717170</v>
+        <v>717487</v>
       </c>
       <c r="R48" t="n">
-        <v>6373195</v>
+        <v>6373202</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5359,9 +5359,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5376,44 +5386,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128813046</v>
+        <v>128813067</v>
       </c>
       <c r="B49" t="n">
-        <v>86959</v>
+        <v>86985</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5423,10 +5433,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717216</v>
+        <v>717325</v>
       </c>
       <c r="R49" t="n">
-        <v>6373176</v>
+        <v>6373229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5458,7 +5468,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5468,7 +5478,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5495,32 +5505,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128813040</v>
+        <v>128806053</v>
       </c>
       <c r="B50" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5530,10 +5540,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717487</v>
+        <v>717382</v>
       </c>
       <c r="R50" t="n">
-        <v>6373202</v>
+        <v>6373309</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5563,19 +5573,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5590,57 +5590,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128806334</v>
+        <v>128815141</v>
       </c>
       <c r="B51" t="n">
-        <v>90965</v>
+        <v>86985</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3286</v>
+        <v>449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717324</v>
+        <v>717505</v>
       </c>
       <c r="R51" t="n">
-        <v>6373355</v>
+        <v>6373241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,44 +5687,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128806069</v>
+        <v>128806334</v>
       </c>
       <c r="B52" t="n">
-        <v>86922</v>
+        <v>90969</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>3286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717117</v>
+        <v>717324</v>
       </c>
       <c r="R52" t="n">
-        <v>6373208</v>
+        <v>6373355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,57 +5784,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128806074</v>
+        <v>128815131</v>
       </c>
       <c r="B53" t="n">
-        <v>86922</v>
+        <v>91044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717445</v>
+        <v>717416</v>
       </c>
       <c r="R53" t="n">
-        <v>6373269</v>
+        <v>6373162</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5869,56 +5869,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128813042</v>
+        <v>128806069</v>
       </c>
       <c r="B54" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5928,10 +5934,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717084</v>
+        <v>717117</v>
       </c>
       <c r="R54" t="n">
-        <v>6373295</v>
+        <v>6373208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5961,19 +5967,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5988,44 +5984,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806034</v>
+        <v>128806074</v>
       </c>
       <c r="B55" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6035,10 +6031,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717303</v>
+        <v>717445</v>
       </c>
       <c r="R55" t="n">
-        <v>6373236</v>
+        <v>6373269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6079,7 +6075,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6091,52 +6086,52 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128815141</v>
+        <v>128813042</v>
       </c>
       <c r="B56" t="n">
-        <v>86981</v>
+        <v>86963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717505</v>
+        <v>717084</v>
       </c>
       <c r="R56" t="n">
-        <v>6373241</v>
+        <v>6373295</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6166,9 +6161,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6183,57 +6188,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128815131</v>
+        <v>128806034</v>
       </c>
       <c r="B57" t="n">
-        <v>91040</v>
+        <v>86963</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717416</v>
+        <v>717303</v>
       </c>
       <c r="R57" t="n">
-        <v>6373162</v>
+        <v>6373236</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6268,11 +6273,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6286,12 +6286,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
         <v>128815116</v>
       </c>
       <c r="B58" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6395,45 +6395,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128806330</v>
+        <v>128815152</v>
       </c>
       <c r="B59" t="n">
-        <v>107546</v>
+        <v>86926</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717069</v>
+        <v>717329</v>
       </c>
       <c r="R59" t="n">
-        <v>6373282</v>
+        <v>6373260</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6480,44 +6480,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128806322</v>
+        <v>128806054</v>
       </c>
       <c r="B60" t="n">
-        <v>86959</v>
+        <v>86788</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717234</v>
+        <v>717273</v>
       </c>
       <c r="R60" t="n">
-        <v>6373222</v>
+        <v>6373345</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,29 +6571,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128815152</v>
+        <v>128815148</v>
       </c>
       <c r="B61" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6625,10 +6624,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717329</v>
+        <v>717239</v>
       </c>
       <c r="R61" t="n">
-        <v>6373260</v>
+        <v>6373262</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6687,32 +6686,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128806054</v>
+        <v>128806330</v>
       </c>
       <c r="B62" t="n">
-        <v>86784</v>
+        <v>107550</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6722,10 +6721,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717273</v>
+        <v>717069</v>
       </c>
       <c r="R62" t="n">
-        <v>6373345</v>
+        <v>6373282</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,57 +6771,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128815148</v>
+        <v>128806322</v>
       </c>
       <c r="B63" t="n">
-        <v>86922</v>
+        <v>86963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717239</v>
+        <v>717234</v>
       </c>
       <c r="R63" t="n">
-        <v>6373262</v>
+        <v>6373222</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6863,50 +6862,51 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128813066</v>
+        <v>128806326</v>
       </c>
       <c r="B64" t="n">
-        <v>86981</v>
+        <v>86939</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717515</v>
+        <v>717084</v>
       </c>
       <c r="R64" t="n">
-        <v>6373166</v>
+        <v>6373294</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,19 +6949,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6976,22 +6966,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128806333</v>
+        <v>128813066</v>
       </c>
       <c r="B65" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7023,10 +7013,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717331</v>
+        <v>717515</v>
       </c>
       <c r="R65" t="n">
-        <v>6373327</v>
+        <v>6373166</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7056,9 +7046,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,44 +7073,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128813079</v>
+        <v>128806333</v>
       </c>
       <c r="B66" t="n">
-        <v>86922</v>
+        <v>86985</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717315</v>
+        <v>717331</v>
       </c>
       <c r="R66" t="n">
-        <v>6373221</v>
+        <v>6373327</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7153,19 +7153,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7180,22 +7170,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128806350</v>
+        <v>128813079</v>
       </c>
       <c r="B67" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7227,10 +7217,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717330</v>
+        <v>717315</v>
       </c>
       <c r="R67" t="n">
-        <v>6373328</v>
+        <v>6373221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7260,9 +7250,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7277,44 +7277,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128813012</v>
+        <v>128806350</v>
       </c>
       <c r="B68" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717435</v>
+        <v>717330</v>
       </c>
       <c r="R68" t="n">
-        <v>6373156</v>
+        <v>6373328</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7357,19 +7357,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7384,44 +7374,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128806036</v>
+        <v>128813012</v>
       </c>
       <c r="B69" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7431,10 +7421,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717449</v>
+        <v>717435</v>
       </c>
       <c r="R69" t="n">
-        <v>6373281</v>
+        <v>6373156</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7464,75 +7454,87 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806326</v>
+        <v>128806342</v>
       </c>
       <c r="B70" t="n">
-        <v>86935</v>
+        <v>86717</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1988</v>
+        <v>249278</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717084</v>
+        <v>717179</v>
       </c>
       <c r="R70" t="n">
-        <v>6373294</v>
+        <v>6373227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7567,12 +7569,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7591,10 +7599,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128806342</v>
+        <v>128813044</v>
       </c>
       <c r="B71" t="n">
-        <v>86713</v>
+        <v>86963</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7602,37 +7610,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717179</v>
+        <v>717135</v>
       </c>
       <c r="R71" t="n">
-        <v>6373227</v>
+        <v>6373174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7662,14 +7667,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7678,29 +7688,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128813044</v>
+        <v>128806036</v>
       </c>
       <c r="B72" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7732,10 +7741,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717135</v>
+        <v>717449</v>
       </c>
       <c r="R72" t="n">
-        <v>6373174</v>
+        <v>6373281</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7765,84 +7774,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128806046</v>
+        <v>128806041</v>
       </c>
       <c r="B73" t="n">
-        <v>86981</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717129</v>
+        <v>717150</v>
       </c>
       <c r="R73" t="n">
-        <v>6373201</v>
+        <v>6373384</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7883,6 +7892,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7901,32 +7911,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128813020</v>
+        <v>128806046</v>
       </c>
       <c r="B74" t="n">
-        <v>57713</v>
+        <v>86985</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7936,13 +7946,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717395</v>
+        <v>717129</v>
       </c>
       <c r="R74" t="n">
-        <v>6373086</v>
+        <v>6373201</v>
       </c>
       <c r="S74" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7969,19 +7979,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,69 +7996,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128806041</v>
+        <v>128813020</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717150</v>
+        <v>717395</v>
       </c>
       <c r="R75" t="n">
-        <v>6373384</v>
+        <v>6373086</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8085,62 +8076,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128806047</v>
+        <v>128813055</v>
       </c>
       <c r="B76" t="n">
-        <v>86981</v>
+        <v>98670</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>449</v>
+        <v>219874</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717290</v>
+        <v>717326</v>
       </c>
       <c r="R76" t="n">
-        <v>6373221</v>
+        <v>6373144</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8183,9 +8183,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8200,22 +8210,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806316</v>
+        <v>128806047</v>
       </c>
       <c r="B77" t="n">
-        <v>86806</v>
+        <v>86985</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,37 +8233,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717125</v>
+        <v>717290</v>
       </c>
       <c r="R77" t="n">
-        <v>6373250</v>
+        <v>6373221</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,29 +8301,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128813077</v>
+        <v>128806316</v>
       </c>
       <c r="B78" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8342,16 +8348,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717116</v>
+        <v>717125</v>
       </c>
       <c r="R78" t="n">
-        <v>6373207</v>
+        <v>6373250</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,49 +8390,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128815128</v>
+        <v>128813077</v>
       </c>
       <c r="B79" t="n">
-        <v>91040</v>
+        <v>86810</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8431,34 +8431,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717418</v>
+        <v>717116</v>
       </c>
       <c r="R79" t="n">
-        <v>6373171</v>
+        <v>6373207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8488,75 +8488,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128806067</v>
+        <v>128815128</v>
       </c>
       <c r="B80" t="n">
-        <v>86922</v>
+        <v>91044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717298</v>
+        <v>717418</v>
       </c>
       <c r="R80" t="n">
-        <v>6373345</v>
+        <v>6373171</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8597,18 +8606,19 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8618,7 +8628,7 @@
         <v>128806001</v>
       </c>
       <c r="B81" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8715,7 +8725,7 @@
         <v>128815117</v>
       </c>
       <c r="B82" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8809,32 +8819,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128806026</v>
+        <v>128806067</v>
       </c>
       <c r="B83" t="n">
-        <v>86959</v>
+        <v>86926</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8844,10 +8854,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717211</v>
+        <v>717298</v>
       </c>
       <c r="R83" t="n">
-        <v>6373375</v>
+        <v>6373345</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8888,7 +8898,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8900,17 +8909,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128806031</v>
+        <v>128806026</v>
       </c>
       <c r="B84" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8942,10 +8951,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717071</v>
+        <v>717211</v>
       </c>
       <c r="R84" t="n">
-        <v>6373294</v>
+        <v>6373375</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9005,32 +9014,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128813055</v>
+        <v>128806031</v>
       </c>
       <c r="B85" t="n">
-        <v>98666</v>
+        <v>86963</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219874</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9040,10 +9049,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717326</v>
+        <v>717071</v>
       </c>
       <c r="R85" t="n">
-        <v>6373144</v>
+        <v>6373294</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9073,84 +9082,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128813061</v>
+        <v>128815156</v>
       </c>
       <c r="B86" t="n">
-        <v>86875</v>
+        <v>86926</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717085</v>
+        <v>717444</v>
       </c>
       <c r="R86" t="n">
-        <v>6373261</v>
+        <v>6373273</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,19 +9180,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9207,57 +9197,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806318</v>
+        <v>128815120</v>
       </c>
       <c r="B87" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717062</v>
+        <v>717479</v>
       </c>
       <c r="R87" t="n">
-        <v>6373304</v>
+        <v>6373226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9298,19 +9288,18 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9320,7 +9309,7 @@
         <v>128813078</v>
       </c>
       <c r="B88" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9427,7 +9416,7 @@
         <v>128815130</v>
       </c>
       <c r="B89" t="n">
-        <v>91040</v>
+        <v>91044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9522,45 +9511,53 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128815156</v>
+        <v>128806007</v>
       </c>
       <c r="B90" t="n">
-        <v>86922</v>
+        <v>57717</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3674</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717444</v>
+        <v>717083</v>
       </c>
       <c r="R90" t="n">
-        <v>6373273</v>
+        <v>6373260</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9607,22 +9604,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806007</v>
+        <v>128806318</v>
       </c>
       <c r="B91" t="n">
-        <v>57713</v>
+        <v>86963</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9630,42 +9627,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717083</v>
+        <v>717062</v>
       </c>
       <c r="R91" t="n">
-        <v>6373260</v>
+        <v>6373304</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9706,28 +9695,29 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128815120</v>
+        <v>128813061</v>
       </c>
       <c r="B92" t="n">
-        <v>87004</v>
+        <v>86879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9735,34 +9725,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717479</v>
+        <v>717085</v>
       </c>
       <c r="R92" t="n">
-        <v>6373226</v>
+        <v>6373261</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9792,9 +9782,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9809,12 +9809,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
         <v>128806071</v>
       </c>
       <c r="B93" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9918,10 +9918,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128813069</v>
+        <v>128815123</v>
       </c>
       <c r="B94" t="n">
-        <v>86981</v>
+        <v>87008</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9929,34 +9929,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717134</v>
+        <v>717500</v>
       </c>
       <c r="R94" t="n">
-        <v>6373192</v>
+        <v>6373237</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9986,19 +9986,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10013,22 +10003,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128813074</v>
+        <v>128815118</v>
       </c>
       <c r="B95" t="n">
-        <v>87016</v>
+        <v>87008</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10036,30 +10026,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717185</v>
+        <v>717431</v>
       </c>
       <c r="R95" t="n">
-        <v>6373128</v>
+        <v>6373173</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10089,24 +10083,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10121,22 +10100,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815109</v>
+        <v>128815137</v>
       </c>
       <c r="B96" t="n">
-        <v>86902</v>
+        <v>86963</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10144,21 +10123,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10168,10 +10147,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717314</v>
+        <v>717433</v>
       </c>
       <c r="R96" t="n">
-        <v>6373229</v>
+        <v>6373170</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10212,6 +10191,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10230,45 +10210,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128815112</v>
+        <v>128813052</v>
       </c>
       <c r="B97" t="n">
-        <v>87004</v>
+        <v>86963</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717270</v>
+        <v>717411</v>
       </c>
       <c r="R97" t="n">
-        <v>6373304</v>
+        <v>6373077</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10298,9 +10278,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10315,22 +10305,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815123</v>
+        <v>128815112</v>
       </c>
       <c r="B98" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10362,10 +10352,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717500</v>
+        <v>717270</v>
       </c>
       <c r="R98" t="n">
-        <v>6373237</v>
+        <v>6373304</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10424,45 +10414,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128815118</v>
+        <v>128813076</v>
       </c>
       <c r="B99" t="n">
-        <v>87004</v>
+        <v>90275</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>245042</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717431</v>
+        <v>717322</v>
       </c>
       <c r="R99" t="n">
-        <v>6373173</v>
+        <v>6373147</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,77 +10485,85 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128813076</v>
+        <v>128813069</v>
       </c>
       <c r="B100" t="n">
-        <v>90271</v>
+        <v>86985</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>245042</v>
+        <v>449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717322</v>
+        <v>717134</v>
       </c>
       <c r="R100" t="n">
-        <v>6373147</v>
+        <v>6373192</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10594,7 +10595,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10604,7 +10605,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10613,7 +10614,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10632,45 +10632,41 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128815137</v>
+        <v>128813074</v>
       </c>
       <c r="B101" t="n">
-        <v>86959</v>
+        <v>87020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717433</v>
+        <v>717185</v>
       </c>
       <c r="R101" t="n">
-        <v>6373170</v>
+        <v>6373128</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10700,40 +10696,54 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128813052</v>
+        <v>128815109</v>
       </c>
       <c r="B102" t="n">
-        <v>86959</v>
+        <v>86906</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10741,34 +10751,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>473</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717411</v>
+        <v>717314</v>
       </c>
       <c r="R102" t="n">
-        <v>6373077</v>
+        <v>6373229</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10798,19 +10808,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10825,44 +10825,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128815151</v>
+        <v>128815129</v>
       </c>
       <c r="B103" t="n">
-        <v>86922</v>
+        <v>91044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717270</v>
+        <v>717424</v>
       </c>
       <c r="R103" t="n">
-        <v>6373304</v>
+        <v>6373165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10934,10 +10934,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128815149</v>
+        <v>128815151</v>
       </c>
       <c r="B104" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717269</v>
+        <v>717270</v>
       </c>
       <c r="R104" t="n">
-        <v>6373207</v>
+        <v>6373304</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815129</v>
+        <v>128815149</v>
       </c>
       <c r="B105" t="n">
-        <v>91040</v>
+        <v>86926</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717424</v>
+        <v>717269</v>
       </c>
       <c r="R105" t="n">
-        <v>6373165</v>
+        <v>6373207</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11131,7 +11131,7 @@
         <v>128815110</v>
       </c>
       <c r="B106" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>128813073</v>
       </c>
       <c r="B107" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>128806323</v>
       </c>
       <c r="B108" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>128806028</v>
       </c>
       <c r="B109" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>128806320</v>
       </c>
       <c r="B110" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11630,10 +11630,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813568</v>
+        <v>128813048</v>
       </c>
       <c r="B111" t="n">
-        <v>86902</v>
+        <v>86963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11641,21 +11641,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11665,10 +11665,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717322</v>
+        <v>717248</v>
       </c>
       <c r="R111" t="n">
-        <v>6373203</v>
+        <v>6373196</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11737,45 +11737,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128815121</v>
+        <v>128806055</v>
       </c>
       <c r="B112" t="n">
-        <v>87004</v>
+        <v>86717</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3767</v>
+        <v>249278</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717499</v>
+        <v>717283</v>
       </c>
       <c r="R112" t="n">
-        <v>6373239</v>
+        <v>6373299</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11810,34 +11813,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806313</v>
+        <v>128815139</v>
       </c>
       <c r="B113" t="n">
-        <v>87004</v>
+        <v>86879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11845,34 +11854,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717369</v>
+        <v>717313</v>
       </c>
       <c r="R113" t="n">
-        <v>6373319</v>
+        <v>6373361</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11919,44 +11928,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128813063</v>
+        <v>128813568</v>
       </c>
       <c r="B114" t="n">
-        <v>92258</v>
+        <v>86906</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>232138</v>
+        <v>473</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11966,10 +11975,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717511</v>
+        <v>717322</v>
       </c>
       <c r="R114" t="n">
-        <v>6373145</v>
+        <v>6373203</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12001,7 +12010,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12011,7 +12020,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12038,48 +12047,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128806055</v>
+        <v>128815121</v>
       </c>
       <c r="B115" t="n">
-        <v>86713</v>
+        <v>87008</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717283</v>
+        <v>717499</v>
       </c>
       <c r="R115" t="n">
-        <v>6373299</v>
+        <v>6373239</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12114,62 +12120,56 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128813048</v>
+        <v>128806313</v>
       </c>
       <c r="B116" t="n">
-        <v>86959</v>
+        <v>87008</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717248</v>
+        <v>717369</v>
       </c>
       <c r="R116" t="n">
-        <v>6373196</v>
+        <v>6373319</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12212,19 +12212,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12239,22 +12229,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128815139</v>
+        <v>128813063</v>
       </c>
       <c r="B117" t="n">
-        <v>86875</v>
+        <v>92262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12262,34 +12252,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>248956</v>
+        <v>232138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717313</v>
+        <v>717511</v>
       </c>
       <c r="R117" t="n">
-        <v>6373361</v>
+        <v>6373145</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12319,9 +12309,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12336,44 +12336,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128813030</v>
+        <v>128806312</v>
       </c>
       <c r="B118" t="n">
-        <v>86935</v>
+        <v>87008</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717079</v>
+        <v>717332</v>
       </c>
       <c r="R118" t="n">
-        <v>6373300</v>
+        <v>6373350</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,19 +12416,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12443,22 +12433,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806312</v>
+        <v>128806315</v>
       </c>
       <c r="B119" t="n">
-        <v>87004</v>
+        <v>86810</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12456,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717332</v>
+        <v>717165</v>
       </c>
       <c r="R119" t="n">
-        <v>6373350</v>
+        <v>6373195</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12555,7 +12545,7 @@
         <v>128815111</v>
       </c>
       <c r="B120" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12649,32 +12639,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128813014</v>
+        <v>128806347</v>
       </c>
       <c r="B121" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12684,10 +12674,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717462</v>
+        <v>717092</v>
       </c>
       <c r="R121" t="n">
-        <v>6373231</v>
+        <v>6373322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12717,19 +12707,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12744,44 +12724,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128806331</v>
+        <v>128813014</v>
       </c>
       <c r="B122" t="n">
-        <v>90340</v>
+        <v>87008</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6292</v>
+        <v>3767</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12791,10 +12771,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717106</v>
+        <v>717462</v>
       </c>
       <c r="R122" t="n">
-        <v>6373238</v>
+        <v>6373231</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12824,9 +12804,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12841,44 +12831,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806315</v>
+        <v>128806340</v>
       </c>
       <c r="B123" t="n">
-        <v>86806</v>
+        <v>86788</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12888,10 +12878,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717165</v>
+        <v>717314</v>
       </c>
       <c r="R123" t="n">
-        <v>6373195</v>
+        <v>6373345</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12950,10 +12940,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806347</v>
+        <v>128813030</v>
       </c>
       <c r="B124" t="n">
-        <v>86922</v>
+        <v>86939</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12961,21 +12951,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12985,10 +12975,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717092</v>
+        <v>717079</v>
       </c>
       <c r="R124" t="n">
-        <v>6373322</v>
+        <v>6373300</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13018,9 +13008,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13035,22 +13035,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806340</v>
+        <v>128806331</v>
       </c>
       <c r="B125" t="n">
-        <v>86784</v>
+        <v>90344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13058,21 +13058,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3712</v>
+        <v>6292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13082,10 +13082,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717314</v>
+        <v>717106</v>
       </c>
       <c r="R125" t="n">
-        <v>6373345</v>
+        <v>6373238</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13147,7 +13147,7 @@
         <v>128813056</v>
       </c>
       <c r="B126" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>128806032</v>
       </c>
       <c r="B127" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13349,34 +13349,30 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128815115</v>
+        <v>128815126</v>
       </c>
       <c r="B128" t="n">
-        <v>87004</v>
+        <v>87029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3767</v>
+        <v>3624</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13384,10 +13380,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717424</v>
+        <v>717337</v>
       </c>
       <c r="R128" t="n">
-        <v>6373147</v>
+        <v>6373382</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13446,10 +13442,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128813080</v>
+        <v>128813018</v>
       </c>
       <c r="B129" t="n">
-        <v>86922</v>
+        <v>110763</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13457,21 +13453,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3674</v>
+        <v>219711</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13481,10 +13477,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717456</v>
+        <v>717512</v>
       </c>
       <c r="R129" t="n">
-        <v>6373273</v>
+        <v>6373149</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13516,7 +13512,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13526,7 +13522,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13553,30 +13549,34 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128815126</v>
+        <v>128815115</v>
       </c>
       <c r="B130" t="n">
-        <v>87025</v>
+        <v>87008</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3624</v>
+        <v>3767</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717337</v>
+        <v>717424</v>
       </c>
       <c r="R130" t="n">
-        <v>6373382</v>
+        <v>6373147</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13646,10 +13646,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813018</v>
+        <v>128813080</v>
       </c>
       <c r="B131" t="n">
-        <v>110759</v>
+        <v>86926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13657,21 +13657,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219711</v>
+        <v>3674</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13681,10 +13681,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717512</v>
+        <v>717456</v>
       </c>
       <c r="R131" t="n">
-        <v>6373149</v>
+        <v>6373273</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13756,7 +13756,7 @@
         <v>128813049</v>
       </c>
       <c r="B132" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>128813075</v>
       </c>
       <c r="B133" t="n">
-        <v>86875</v>
+        <v>86879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>128806319</v>
       </c>
       <c r="B134" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14074,10 +14074,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128815155</v>
+        <v>128813027</v>
       </c>
       <c r="B135" t="n">
-        <v>86922</v>
+        <v>91017</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14085,34 +14085,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717498</v>
+        <v>717343</v>
       </c>
       <c r="R135" t="n">
-        <v>6373233</v>
+        <v>6373129</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14142,9 +14142,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14159,57 +14169,57 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128806000</v>
+        <v>128815155</v>
       </c>
       <c r="B136" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717298</v>
+        <v>717498</v>
       </c>
       <c r="R136" t="n">
-        <v>6373343</v>
+        <v>6373233</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14256,57 +14266,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128815133</v>
+        <v>128806000</v>
       </c>
       <c r="B137" t="n">
-        <v>86760</v>
+        <v>87008</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717314</v>
+        <v>717298</v>
       </c>
       <c r="R137" t="n">
-        <v>6373361</v>
+        <v>6373343</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14353,22 +14363,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128813027</v>
+        <v>128815133</v>
       </c>
       <c r="B138" t="n">
-        <v>91013</v>
+        <v>86764</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14376,34 +14386,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5741</v>
+        <v>3762</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717343</v>
+        <v>717314</v>
       </c>
       <c r="R138" t="n">
-        <v>6373129</v>
+        <v>6373361</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14433,19 +14443,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>10:05</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14460,12 +14460,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14475,7 +14475,7 @@
         <v>128806066</v>
       </c>
       <c r="B139" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>128806070</v>
       </c>
       <c r="B140" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128813081</v>
+        <v>128806008</v>
       </c>
       <c r="B141" t="n">
-        <v>86922</v>
+        <v>86764</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14677,21 +14677,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14701,10 +14701,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717161</v>
+        <v>717255</v>
       </c>
       <c r="R141" t="n">
-        <v>6373174</v>
+        <v>6373321</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14734,19 +14734,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14761,22 +14751,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128815147</v>
+        <v>128813081</v>
       </c>
       <c r="B142" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14804,14 +14794,14 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717312</v>
+        <v>717161</v>
       </c>
       <c r="R142" t="n">
-        <v>6373366</v>
+        <v>6373174</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14841,9 +14831,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14858,22 +14858,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128815150</v>
+        <v>128815147</v>
       </c>
       <c r="B143" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14905,10 +14905,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717305</v>
+        <v>717312</v>
       </c>
       <c r="R143" t="n">
-        <v>6373217</v>
+        <v>6373366</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14967,45 +14967,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128806008</v>
+        <v>128815124</v>
       </c>
       <c r="B144" t="n">
-        <v>86760</v>
+        <v>87008</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717255</v>
+        <v>717467</v>
       </c>
       <c r="R144" t="n">
-        <v>6373321</v>
+        <v>6373240</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15052,44 +15052,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128815124</v>
+        <v>128815150</v>
       </c>
       <c r="B145" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>717467</v>
+        <v>717305</v>
       </c>
       <c r="R145" t="n">
-        <v>6373240</v>
+        <v>6373217</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15164,7 +15164,7 @@
         <v>128813064</v>
       </c>
       <c r="B146" t="n">
-        <v>91502</v>
+        <v>91506</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128815135</v>
+        <v>128813071</v>
       </c>
       <c r="B2" t="n">
-        <v>86764</v>
+        <v>86985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717476</v>
+        <v>717455</v>
       </c>
       <c r="R2" t="n">
-        <v>6373242</v>
+        <v>6373115</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -966,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806348</v>
+        <v>128815113</v>
       </c>
       <c r="B5" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717239</v>
+        <v>717317</v>
       </c>
       <c r="R5" t="n">
-        <v>6373234</v>
+        <v>6373308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,57 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128815113</v>
+        <v>128813022</v>
       </c>
       <c r="B6" t="n">
-        <v>87008</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717317</v>
+        <v>717130</v>
       </c>
       <c r="R6" t="n">
-        <v>6373308</v>
+        <v>6373194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1131,9 +1141,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128806072</v>
+        <v>128815135</v>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>86764</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717289</v>
+        <v>717476</v>
       </c>
       <c r="R7" t="n">
-        <v>6373288</v>
+        <v>6373242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128813022</v>
+        <v>128806348</v>
       </c>
       <c r="B8" t="n">
-        <v>92810</v>
+        <v>86926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717130</v>
+        <v>717239</v>
       </c>
       <c r="R8" t="n">
-        <v>6373194</v>
+        <v>6373234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1325,19 +1345,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1352,44 +1362,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128813071</v>
+        <v>128806072</v>
       </c>
       <c r="B9" t="n">
-        <v>86985</v>
+        <v>86926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717455</v>
+        <v>717289</v>
       </c>
       <c r="R9" t="n">
-        <v>6373115</v>
+        <v>6373288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1432,19 +1442,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,57 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128806006</v>
+        <v>128815136</v>
       </c>
       <c r="B10" t="n">
-        <v>92443</v>
+        <v>86963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717370</v>
+        <v>717412</v>
       </c>
       <c r="R10" t="n">
-        <v>6373322</v>
+        <v>6373217</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,25 +1550,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128815136</v>
+        <v>128806033</v>
       </c>
       <c r="B11" t="n">
         <v>86963</v>
@@ -1599,14 +1600,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717412</v>
+        <v>717315</v>
       </c>
       <c r="R11" t="n">
-        <v>6373217</v>
+        <v>6373232</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,19 +1655,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128806033</v>
+        <v>128813034</v>
       </c>
       <c r="B12" t="n">
         <v>86963</v>
@@ -1701,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717315</v>
+        <v>717425</v>
       </c>
       <c r="R12" t="n">
-        <v>6373232</v>
+        <v>6373083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,62 +1735,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128813034</v>
+        <v>128806006</v>
       </c>
       <c r="B13" t="n">
-        <v>86963</v>
+        <v>92443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717425</v>
+        <v>717370</v>
       </c>
       <c r="R13" t="n">
-        <v>6373083</v>
+        <v>6373322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,19 +1842,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,12 +1859,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128806343</v>
+        <v>128815145</v>
       </c>
       <c r="B17" t="n">
-        <v>86717</v>
+        <v>86929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,37 +2173,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>249278</v>
+        <v>6037417</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717258</v>
+        <v>717299</v>
       </c>
       <c r="R17" t="n">
-        <v>6373299</v>
+        <v>6373241</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2238,11 +2235,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2256,12 +2248,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2482,10 +2474,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128815145</v>
+        <v>128806343</v>
       </c>
       <c r="B20" t="n">
-        <v>86929</v>
+        <v>86717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,34 +2485,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6037417</v>
+        <v>249278</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717299</v>
+        <v>717258</v>
       </c>
       <c r="R20" t="n">
-        <v>6373241</v>
+        <v>6373299</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,6 +2550,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2568,44 +2568,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128806311</v>
+        <v>128813032</v>
       </c>
       <c r="B21" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717316</v>
+        <v>717409</v>
       </c>
       <c r="R21" t="n">
-        <v>6373307</v>
+        <v>6373057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,9 +2648,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2665,57 +2675,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128815134</v>
+        <v>128806324</v>
       </c>
       <c r="B22" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717316</v>
+        <v>717408</v>
       </c>
       <c r="R22" t="n">
-        <v>6373365</v>
+        <v>6373296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,25 +2766,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128813032</v>
+        <v>128806027</v>
       </c>
       <c r="B23" t="n">
         <v>86963</v>
@@ -2809,10 +2820,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717409</v>
+        <v>717195</v>
       </c>
       <c r="R23" t="n">
-        <v>6373057</v>
+        <v>6373376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,46 +2853,37 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128806324</v>
+        <v>128806029</v>
       </c>
       <c r="B24" t="n">
         <v>86963</v>
@@ -2916,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717408</v>
+        <v>717149</v>
       </c>
       <c r="R24" t="n">
-        <v>6373296</v>
+        <v>6373385</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,44 +2969,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128806027</v>
+        <v>128806311</v>
       </c>
       <c r="B25" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3014,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717195</v>
+        <v>717316</v>
       </c>
       <c r="R25" t="n">
-        <v>6373376</v>
+        <v>6373307</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3058,64 +3060,63 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128806029</v>
+        <v>128815134</v>
       </c>
       <c r="B26" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717149</v>
+        <v>717316</v>
       </c>
       <c r="R26" t="n">
-        <v>6373385</v>
+        <v>6373365</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,64 +3157,63 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128813028</v>
+        <v>128815122</v>
       </c>
       <c r="B27" t="n">
-        <v>91017</v>
+        <v>87008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717490</v>
+        <v>717534</v>
       </c>
       <c r="R27" t="n">
-        <v>6373178</v>
+        <v>6373182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3243,19 +3243,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3270,19 +3260,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128815122</v>
+        <v>128805998</v>
       </c>
       <c r="B28" t="n">
         <v>87008</v>
@@ -3313,14 +3303,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717534</v>
+        <v>717299</v>
       </c>
       <c r="R28" t="n">
-        <v>6373182</v>
+        <v>6373359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,44 +3357,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128805998</v>
+        <v>128813028</v>
       </c>
       <c r="B29" t="n">
-        <v>87008</v>
+        <v>91017</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717299</v>
+        <v>717490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373359</v>
+        <v>6373178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,9 +3437,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3464,57 +3464,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128813051</v>
+        <v>128806042</v>
       </c>
       <c r="B30" t="n">
-        <v>86963</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717385</v>
+        <v>717134</v>
       </c>
       <c r="R30" t="n">
-        <v>6373091</v>
+        <v>6373159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3544,93 +3553,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128806042</v>
+        <v>128813051</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>86963</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717134</v>
+        <v>717385</v>
       </c>
       <c r="R31" t="n">
-        <v>6373159</v>
+        <v>6373091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,40 +3651,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128813070</v>
+        <v>128806002</v>
       </c>
       <c r="B32" t="n">
-        <v>86985</v>
+        <v>87008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717323</v>
+        <v>717297</v>
       </c>
       <c r="R32" t="n">
-        <v>6373241</v>
+        <v>6373295</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,19 +3758,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3785,19 +3775,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128813068</v>
+        <v>128813070</v>
       </c>
       <c r="B33" t="n">
         <v>86985</v>
@@ -3832,10 +3822,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717085</v>
+        <v>717323</v>
       </c>
       <c r="R33" t="n">
-        <v>6373275</v>
+        <v>6373241</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3867,7 +3857,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3877,7 +3867,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3904,32 +3894,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128806349</v>
+        <v>128813068</v>
       </c>
       <c r="B34" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3929,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717337</v>
+        <v>717085</v>
       </c>
       <c r="R34" t="n">
-        <v>6373337</v>
+        <v>6373275</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,9 +3962,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3989,19 +3989,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806351</v>
+        <v>128815154</v>
       </c>
       <c r="B35" t="n">
         <v>86926</v>
@@ -4032,14 +4032,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717390</v>
+        <v>717416</v>
       </c>
       <c r="R35" t="n">
-        <v>6373317</v>
+        <v>6373159</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4086,44 +4086,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128806002</v>
+        <v>128806349</v>
       </c>
       <c r="B36" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717297</v>
+        <v>717337</v>
       </c>
       <c r="R36" t="n">
-        <v>6373295</v>
+        <v>6373337</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4183,44 +4183,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128806025</v>
+        <v>128806351</v>
       </c>
       <c r="B37" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717284</v>
+        <v>717390</v>
       </c>
       <c r="R37" t="n">
-        <v>6373347</v>
+        <v>6373317</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4274,49 +4274,52 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128806317</v>
+        <v>128806025</v>
       </c>
       <c r="B38" t="n">
-        <v>92812</v>
+        <v>86963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6047725</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4324,10 +4327,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>717367</v>
+        <v>717284</v>
       </c>
       <c r="R38" t="n">
-        <v>6373322</v>
+        <v>6373347</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4375,22 +4378,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128815154</v>
+        <v>128806317</v>
       </c>
       <c r="B39" t="n">
-        <v>86926</v>
+        <v>92812</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4398,34 +4401,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3674</v>
+        <v>6047725</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>717416</v>
+        <v>717367</v>
       </c>
       <c r="R39" t="n">
-        <v>6373159</v>
+        <v>6373322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,63 +4465,64 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128815143</v>
+        <v>128813065</v>
       </c>
       <c r="B40" t="n">
-        <v>90969</v>
+        <v>86985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3286</v>
+        <v>449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717335</v>
+        <v>717407</v>
       </c>
       <c r="R40" t="n">
-        <v>6373383</v>
+        <v>6373048</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4552,9 +4552,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4569,19 +4579,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128813065</v>
+        <v>128815140</v>
       </c>
       <c r="B41" t="n">
         <v>86985</v>
@@ -4612,14 +4622,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717407</v>
+        <v>717460</v>
       </c>
       <c r="R41" t="n">
-        <v>6373048</v>
+        <v>6373180</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,19 +4659,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4676,44 +4676,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815140</v>
+        <v>128815143</v>
       </c>
       <c r="B42" t="n">
-        <v>86985</v>
+        <v>90969</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>3286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717460</v>
+        <v>717335</v>
       </c>
       <c r="R42" t="n">
-        <v>6373180</v>
+        <v>6373383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5080,39 +5080,39 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128806345</v>
+        <v>128813067</v>
       </c>
       <c r="B46" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717170</v>
+        <v>717325</v>
       </c>
       <c r="R46" t="n">
-        <v>6373195</v>
+        <v>6373229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,9 +5155,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,12 +5182,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5398,32 +5408,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128813067</v>
+        <v>128806053</v>
       </c>
       <c r="B49" t="n">
-        <v>86985</v>
+        <v>86788</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5433,10 +5443,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717325</v>
+        <v>717382</v>
       </c>
       <c r="R49" t="n">
-        <v>6373229</v>
+        <v>6373309</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5466,19 +5476,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5493,22 +5493,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128806053</v>
+        <v>128806345</v>
       </c>
       <c r="B50" t="n">
-        <v>86788</v>
+        <v>86926</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717382</v>
+        <v>717170</v>
       </c>
       <c r="R50" t="n">
-        <v>6373309</v>
+        <v>6373195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5590,57 +5590,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128815141</v>
+        <v>128813042</v>
       </c>
       <c r="B51" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717505</v>
+        <v>717084</v>
       </c>
       <c r="R51" t="n">
-        <v>6373241</v>
+        <v>6373295</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5670,9 +5670,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5687,22 +5697,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128806334</v>
+        <v>128806034</v>
       </c>
       <c r="B52" t="n">
-        <v>90969</v>
+        <v>86963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5710,21 +5720,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5734,10 +5744,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717324</v>
+        <v>717303</v>
       </c>
       <c r="R52" t="n">
-        <v>6373355</v>
+        <v>6373236</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5778,28 +5788,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128815131</v>
+        <v>128815141</v>
       </c>
       <c r="B53" t="n">
-        <v>91044</v>
+        <v>86985</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5807,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5831,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717416</v>
+        <v>717505</v>
       </c>
       <c r="R53" t="n">
-        <v>6373162</v>
+        <v>6373241</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5869,18 +5880,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5899,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128806069</v>
+        <v>128806334</v>
       </c>
       <c r="B54" t="n">
-        <v>86926</v>
+        <v>90969</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3674</v>
+        <v>3286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5934,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717117</v>
+        <v>717324</v>
       </c>
       <c r="R54" t="n">
-        <v>6373208</v>
+        <v>6373355</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5984,57 +5989,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806074</v>
+        <v>128815131</v>
       </c>
       <c r="B55" t="n">
-        <v>86926</v>
+        <v>91044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717445</v>
+        <v>717416</v>
       </c>
       <c r="R55" t="n">
-        <v>6373269</v>
+        <v>6373162</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,56 +6074,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128813042</v>
+        <v>128806069</v>
       </c>
       <c r="B56" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6128,10 +6139,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717084</v>
+        <v>717117</v>
       </c>
       <c r="R56" t="n">
-        <v>6373295</v>
+        <v>6373208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6161,19 +6172,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6188,44 +6189,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128806034</v>
+        <v>128806074</v>
       </c>
       <c r="B57" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6236,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717303</v>
+        <v>717445</v>
       </c>
       <c r="R57" t="n">
-        <v>6373236</v>
+        <v>6373269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6279,7 +6280,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6291,52 +6291,52 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128815116</v>
+        <v>128806330</v>
       </c>
       <c r="B58" t="n">
-        <v>87008</v>
+        <v>107550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3767</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717420</v>
+        <v>717069</v>
       </c>
       <c r="R58" t="n">
-        <v>6373147</v>
+        <v>6373282</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6383,57 +6383,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128815152</v>
+        <v>128806322</v>
       </c>
       <c r="B59" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717329</v>
+        <v>717234</v>
       </c>
       <c r="R59" t="n">
-        <v>6373260</v>
+        <v>6373222</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6474,63 +6474,64 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128806054</v>
+        <v>128815116</v>
       </c>
       <c r="B60" t="n">
-        <v>86788</v>
+        <v>87008</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717273</v>
+        <v>717420</v>
       </c>
       <c r="R60" t="n">
-        <v>6373345</v>
+        <v>6373147</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6577,19 +6578,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128815148</v>
+        <v>128815152</v>
       </c>
       <c r="B61" t="n">
         <v>86926</v>
@@ -6624,10 +6625,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717239</v>
+        <v>717329</v>
       </c>
       <c r="R61" t="n">
-        <v>6373262</v>
+        <v>6373260</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6686,32 +6687,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128806330</v>
+        <v>128806054</v>
       </c>
       <c r="B62" t="n">
-        <v>107550</v>
+        <v>86788</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6721,10 +6722,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717069</v>
+        <v>717273</v>
       </c>
       <c r="R62" t="n">
-        <v>6373282</v>
+        <v>6373345</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,57 +6772,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128806322</v>
+        <v>128815148</v>
       </c>
       <c r="B63" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717234</v>
+        <v>717239</v>
       </c>
       <c r="R63" t="n">
-        <v>6373222</v>
+        <v>6373262</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6862,51 +6863,50 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128806326</v>
+        <v>128813012</v>
       </c>
       <c r="B64" t="n">
-        <v>86939</v>
+        <v>87008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717084</v>
+        <v>717435</v>
       </c>
       <c r="R64" t="n">
-        <v>6373294</v>
+        <v>6373156</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,9 +6949,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6966,44 +6976,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128813066</v>
+        <v>128813044</v>
       </c>
       <c r="B65" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7013,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717515</v>
+        <v>717135</v>
       </c>
       <c r="R65" t="n">
-        <v>6373166</v>
+        <v>6373174</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7048,7 +7058,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7058,7 +7068,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7085,32 +7095,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128806333</v>
+        <v>128806036</v>
       </c>
       <c r="B66" t="n">
-        <v>86985</v>
+        <v>86963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7120,10 +7130,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717331</v>
+        <v>717449</v>
       </c>
       <c r="R66" t="n">
-        <v>6373327</v>
+        <v>6373281</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7164,50 +7174,51 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813079</v>
+        <v>128813066</v>
       </c>
       <c r="B67" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7217,10 +7228,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717315</v>
+        <v>717515</v>
       </c>
       <c r="R67" t="n">
-        <v>6373221</v>
+        <v>6373166</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7252,7 +7263,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7262,7 +7273,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7289,32 +7300,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128806350</v>
+        <v>128806333</v>
       </c>
       <c r="B68" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7335,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717330</v>
+        <v>717331</v>
       </c>
       <c r="R68" t="n">
-        <v>6373328</v>
+        <v>6373327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7386,32 +7397,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128813012</v>
+        <v>128806326</v>
       </c>
       <c r="B69" t="n">
-        <v>87008</v>
+        <v>86939</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>1988</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7421,10 +7432,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717435</v>
+        <v>717084</v>
       </c>
       <c r="R69" t="n">
-        <v>6373156</v>
+        <v>6373294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7454,19 +7465,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>09:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7481,60 +7482,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128806342</v>
+        <v>128813079</v>
       </c>
       <c r="B70" t="n">
-        <v>86717</v>
+        <v>86926</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>249278</v>
+        <v>3674</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717179</v>
+        <v>717315</v>
       </c>
       <c r="R70" t="n">
-        <v>6373227</v>
+        <v>6373221</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7564,14 +7562,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7580,51 +7583,50 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128813044</v>
+        <v>128806350</v>
       </c>
       <c r="B71" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7634,10 +7636,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717135</v>
+        <v>717330</v>
       </c>
       <c r="R71" t="n">
-        <v>6373174</v>
+        <v>6373328</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7667,19 +7669,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7694,22 +7686,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806036</v>
+        <v>128806342</v>
       </c>
       <c r="B72" t="n">
-        <v>86963</v>
+        <v>86717</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7717,34 +7709,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717449</v>
+        <v>717179</v>
       </c>
       <c r="R72" t="n">
-        <v>6373281</v>
+        <v>6373227</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7779,6 +7774,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7792,69 +7792,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128806041</v>
+        <v>128813020</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717150</v>
+        <v>717395</v>
       </c>
       <c r="R73" t="n">
-        <v>6373384</v>
+        <v>6373086</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7881,30 +7872,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8008,48 +8008,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128813020</v>
+        <v>128806041</v>
       </c>
       <c r="B75" t="n">
-        <v>57717</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717395</v>
+        <v>717150</v>
       </c>
       <c r="R75" t="n">
-        <v>6373086</v>
+        <v>6373384</v>
       </c>
       <c r="S75" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8076,71 +8085,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128813055</v>
+        <v>128806047</v>
       </c>
       <c r="B76" t="n">
-        <v>98670</v>
+        <v>86985</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219874</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717326</v>
+        <v>717290</v>
       </c>
       <c r="R76" t="n">
-        <v>6373144</v>
+        <v>6373221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8183,19 +8183,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8210,22 +8200,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806047</v>
+        <v>128806316</v>
       </c>
       <c r="B77" t="n">
-        <v>86985</v>
+        <v>86810</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,34 +8223,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717290</v>
+        <v>717125</v>
       </c>
       <c r="R77" t="n">
-        <v>6373221</v>
+        <v>6373250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8301,25 +8294,26 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128806316</v>
+        <v>128813077</v>
       </c>
       <c r="B78" t="n">
         <v>86810</v>
@@ -8348,19 +8342,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717125</v>
+        <v>717116</v>
       </c>
       <c r="R78" t="n">
-        <v>6373250</v>
+        <v>6373207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8390,62 +8381,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128813077</v>
+        <v>128806067</v>
       </c>
       <c r="B79" t="n">
-        <v>86810</v>
+        <v>86926</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8455,10 +8455,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717116</v>
+        <v>717298</v>
       </c>
       <c r="R79" t="n">
-        <v>6373207</v>
+        <v>6373345</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8488,19 +8488,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8515,12 +8505,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8819,10 +8809,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128806067</v>
+        <v>128813055</v>
       </c>
       <c r="B83" t="n">
-        <v>86926</v>
+        <v>98670</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8830,21 +8820,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8854,10 +8844,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717298</v>
+        <v>717326</v>
       </c>
       <c r="R83" t="n">
-        <v>6373345</v>
+        <v>6373144</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8887,9 +8877,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8904,12 +8904,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9209,45 +9209,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128815120</v>
+        <v>128806007</v>
       </c>
       <c r="B87" t="n">
-        <v>87008</v>
+        <v>57717</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3767</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717479</v>
+        <v>717083</v>
       </c>
       <c r="R87" t="n">
-        <v>6373226</v>
+        <v>6373260</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9294,44 +9302,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128813078</v>
+        <v>128806318</v>
       </c>
       <c r="B88" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9341,10 +9349,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717243</v>
+        <v>717062</v>
       </c>
       <c r="R88" t="n">
-        <v>6373192</v>
+        <v>6373304</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9374,49 +9382,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815130</v>
+        <v>128813078</v>
       </c>
       <c r="B89" t="n">
-        <v>91044</v>
+        <v>86810</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9424,34 +9423,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717326</v>
+        <v>717243</v>
       </c>
       <c r="R89" t="n">
-        <v>6373267</v>
+        <v>6373192</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9481,83 +9480,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128806007</v>
+        <v>128815130</v>
       </c>
       <c r="B90" t="n">
-        <v>57717</v>
+        <v>91044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717083</v>
+        <v>717326</v>
       </c>
       <c r="R90" t="n">
-        <v>6373260</v>
+        <v>6373267</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9598,63 +9598,64 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128806318</v>
+        <v>128815120</v>
       </c>
       <c r="B91" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717062</v>
+        <v>717479</v>
       </c>
       <c r="R91" t="n">
-        <v>6373304</v>
+        <v>6373226</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9695,19 +9696,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9821,32 +9821,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806071</v>
+        <v>128813069</v>
       </c>
       <c r="B93" t="n">
-        <v>86926</v>
+        <v>86985</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717287</v>
+        <v>717134</v>
       </c>
       <c r="R93" t="n">
-        <v>6373292</v>
+        <v>6373192</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9889,9 +9889,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9906,22 +9916,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128815123</v>
+        <v>128813074</v>
       </c>
       <c r="B94" t="n">
-        <v>87008</v>
+        <v>87020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9929,34 +9939,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717500</v>
+        <v>717185</v>
       </c>
       <c r="R94" t="n">
-        <v>6373237</v>
+        <v>6373128</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9986,9 +9992,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10003,44 +10024,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815118</v>
+        <v>128815109</v>
       </c>
       <c r="B95" t="n">
-        <v>87008</v>
+        <v>86906</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10050,10 +10071,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717431</v>
+        <v>717314</v>
       </c>
       <c r="R95" t="n">
-        <v>6373173</v>
+        <v>6373229</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10112,32 +10133,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815137</v>
+        <v>128815112</v>
       </c>
       <c r="B96" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10147,10 +10168,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717433</v>
+        <v>717270</v>
       </c>
       <c r="R96" t="n">
-        <v>6373170</v>
+        <v>6373304</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10191,7 +10212,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10210,45 +10230,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128813052</v>
+        <v>128815123</v>
       </c>
       <c r="B97" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717411</v>
+        <v>717500</v>
       </c>
       <c r="R97" t="n">
-        <v>6373077</v>
+        <v>6373237</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10278,19 +10298,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10305,19 +10315,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815112</v>
+        <v>128815118</v>
       </c>
       <c r="B98" t="n">
         <v>87008</v>
@@ -10352,10 +10362,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717270</v>
+        <v>717431</v>
       </c>
       <c r="R98" t="n">
-        <v>6373304</v>
+        <v>6373173</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10414,10 +10424,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128813076</v>
+        <v>128806071</v>
       </c>
       <c r="B99" t="n">
-        <v>90275</v>
+        <v>86926</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10425,37 +10435,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>245042</v>
+        <v>3674</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717322</v>
+        <v>717287</v>
       </c>
       <c r="R99" t="n">
-        <v>6373147</v>
+        <v>6373292</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10485,85 +10492,77 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128813069</v>
+        <v>128813076</v>
       </c>
       <c r="B100" t="n">
-        <v>86985</v>
+        <v>90275</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>449</v>
+        <v>245042</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717134</v>
+        <v>717322</v>
       </c>
       <c r="R100" t="n">
-        <v>6373192</v>
+        <v>6373147</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10595,7 +10594,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10605,7 +10604,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10614,6 +10613,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10632,41 +10632,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128813074</v>
+        <v>128815137</v>
       </c>
       <c r="B101" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717185</v>
+        <v>717433</v>
       </c>
       <c r="R101" t="n">
-        <v>6373128</v>
+        <v>6373170</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10696,54 +10700,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128815109</v>
+        <v>128813052</v>
       </c>
       <c r="B102" t="n">
-        <v>86906</v>
+        <v>86963</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10751,34 +10741,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717314</v>
+        <v>717411</v>
       </c>
       <c r="R102" t="n">
-        <v>6373229</v>
+        <v>6373077</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10808,9 +10798,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10825,57 +10825,57 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128815129</v>
+        <v>128806323</v>
       </c>
       <c r="B103" t="n">
-        <v>91044</v>
+        <v>86963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717424</v>
+        <v>717241</v>
       </c>
       <c r="R103" t="n">
-        <v>6373165</v>
+        <v>6373264</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10916,63 +10916,64 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128815151</v>
+        <v>128806028</v>
       </c>
       <c r="B104" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717270</v>
+        <v>717179</v>
       </c>
       <c r="R104" t="n">
-        <v>6373304</v>
+        <v>6373374</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11013,63 +11014,64 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815149</v>
+        <v>128806320</v>
       </c>
       <c r="B105" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717269</v>
+        <v>717131</v>
       </c>
       <c r="R105" t="n">
-        <v>6373207</v>
+        <v>6373249</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11110,28 +11112,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128815110</v>
+        <v>128815129</v>
       </c>
       <c r="B106" t="n">
-        <v>87008</v>
+        <v>91044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11139,21 +11142,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11163,10 +11166,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717281</v>
+        <v>717424</v>
       </c>
       <c r="R106" t="n">
-        <v>6373300</v>
+        <v>6373165</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11225,48 +11228,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128813073</v>
+        <v>128815110</v>
       </c>
       <c r="B107" t="n">
-        <v>92834</v>
+        <v>87008</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5964</v>
+        <v>3767</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717453</v>
+        <v>717281</v>
       </c>
       <c r="R107" t="n">
-        <v>6373125</v>
+        <v>6373300</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11296,85 +11296,74 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806323</v>
+        <v>128815151</v>
       </c>
       <c r="B108" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717241</v>
+        <v>717270</v>
       </c>
       <c r="R108" t="n">
-        <v>6373264</v>
+        <v>6373304</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11415,64 +11404,63 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806028</v>
+        <v>128815149</v>
       </c>
       <c r="B109" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717179</v>
+        <v>717269</v>
       </c>
       <c r="R109" t="n">
-        <v>6373374</v>
+        <v>6373207</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11513,64 +11501,66 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806320</v>
+        <v>128813073</v>
       </c>
       <c r="B110" t="n">
-        <v>86963</v>
+        <v>92834</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717131</v>
+        <v>717453</v>
       </c>
       <c r="R110" t="n">
-        <v>6373249</v>
+        <v>6373125</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11600,9 +11590,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,44 +11618,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813048</v>
+        <v>128813063</v>
       </c>
       <c r="B111" t="n">
-        <v>86963</v>
+        <v>92262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>232138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11665,10 +11665,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717248</v>
+        <v>717511</v>
       </c>
       <c r="R111" t="n">
-        <v>6373196</v>
+        <v>6373145</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11737,10 +11737,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806055</v>
+        <v>128813048</v>
       </c>
       <c r="B112" t="n">
-        <v>86717</v>
+        <v>86963</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11748,37 +11748,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717283</v>
+        <v>717248</v>
       </c>
       <c r="R112" t="n">
-        <v>6373299</v>
+        <v>6373196</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11808,14 +11805,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11824,64 +11826,66 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128815139</v>
+        <v>128806055</v>
       </c>
       <c r="B113" t="n">
-        <v>86879</v>
+        <v>86717</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717313</v>
+        <v>717283</v>
       </c>
       <c r="R113" t="n">
-        <v>6373361</v>
+        <v>6373299</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11916,69 +11920,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128813568</v>
+        <v>128815139</v>
       </c>
       <c r="B114" t="n">
-        <v>86906</v>
+        <v>86879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>473</v>
+        <v>248956</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717322</v>
+        <v>717313</v>
       </c>
       <c r="R114" t="n">
-        <v>6373203</v>
+        <v>6373361</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12008,19 +12018,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12035,57 +12035,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815121</v>
+        <v>128813568</v>
       </c>
       <c r="B115" t="n">
-        <v>87008</v>
+        <v>86906</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717499</v>
+        <v>717322</v>
       </c>
       <c r="R115" t="n">
-        <v>6373239</v>
+        <v>6373203</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12115,9 +12115,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12132,19 +12142,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806313</v>
+        <v>128815121</v>
       </c>
       <c r="B116" t="n">
         <v>87008</v>
@@ -12175,14 +12185,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717369</v>
+        <v>717499</v>
       </c>
       <c r="R116" t="n">
-        <v>6373319</v>
+        <v>6373239</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12229,22 +12239,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128813063</v>
+        <v>128806313</v>
       </c>
       <c r="B117" t="n">
-        <v>92262</v>
+        <v>87008</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12252,21 +12262,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>232138</v>
+        <v>3767</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12276,10 +12286,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717511</v>
+        <v>717369</v>
       </c>
       <c r="R117" t="n">
-        <v>6373145</v>
+        <v>6373319</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12309,19 +12319,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12336,44 +12336,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806312</v>
+        <v>128813030</v>
       </c>
       <c r="B118" t="n">
-        <v>87008</v>
+        <v>86939</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3767</v>
+        <v>1988</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717332</v>
+        <v>717079</v>
       </c>
       <c r="R118" t="n">
-        <v>6373350</v>
+        <v>6373300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,9 +12416,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12433,44 +12443,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806315</v>
+        <v>128806347</v>
       </c>
       <c r="B119" t="n">
-        <v>86810</v>
+        <v>86926</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12480,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717165</v>
+        <v>717092</v>
       </c>
       <c r="R119" t="n">
-        <v>6373195</v>
+        <v>6373322</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12542,45 +12552,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128815111</v>
+        <v>128806340</v>
       </c>
       <c r="B120" t="n">
-        <v>87008</v>
+        <v>86788</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717318</v>
+        <v>717314</v>
       </c>
       <c r="R120" t="n">
-        <v>6373242</v>
+        <v>6373345</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12627,44 +12637,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806347</v>
+        <v>128806032</v>
       </c>
       <c r="B121" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12674,10 +12684,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717092</v>
+        <v>717081</v>
       </c>
       <c r="R121" t="n">
-        <v>6373322</v>
+        <v>6373276</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12718,50 +12728,51 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128813014</v>
+        <v>128813056</v>
       </c>
       <c r="B122" t="n">
-        <v>87008</v>
+        <v>98670</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3767</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12771,10 +12782,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717462</v>
+        <v>717484</v>
       </c>
       <c r="R122" t="n">
-        <v>6373231</v>
+        <v>6373174</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12806,7 +12817,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12816,7 +12827,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12843,32 +12854,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806340</v>
+        <v>128806315</v>
       </c>
       <c r="B123" t="n">
-        <v>86788</v>
+        <v>86810</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12878,10 +12889,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717314</v>
+        <v>717165</v>
       </c>
       <c r="R123" t="n">
-        <v>6373345</v>
+        <v>6373195</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12940,32 +12951,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128813030</v>
+        <v>128806312</v>
       </c>
       <c r="B124" t="n">
-        <v>86939</v>
+        <v>87008</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,10 +12986,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717079</v>
+        <v>717332</v>
       </c>
       <c r="R124" t="n">
-        <v>6373300</v>
+        <v>6373350</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13008,19 +13019,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13035,57 +13036,57 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806331</v>
+        <v>128815111</v>
       </c>
       <c r="B125" t="n">
-        <v>90344</v>
+        <v>87008</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6292</v>
+        <v>3767</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717106</v>
+        <v>717318</v>
       </c>
       <c r="R125" t="n">
-        <v>6373238</v>
+        <v>6373242</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13132,44 +13133,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128813056</v>
+        <v>128813014</v>
       </c>
       <c r="B126" t="n">
-        <v>98670</v>
+        <v>87008</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13179,10 +13180,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717484</v>
+        <v>717462</v>
       </c>
       <c r="R126" t="n">
-        <v>6373174</v>
+        <v>6373231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13214,7 +13215,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13224,7 +13225,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13251,32 +13252,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806032</v>
+        <v>128806331</v>
       </c>
       <c r="B127" t="n">
-        <v>86963</v>
+        <v>90344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>6292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13286,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717081</v>
+        <v>717106</v>
       </c>
       <c r="R127" t="n">
-        <v>6373276</v>
+        <v>6373238</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13330,49 +13331,52 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128815126</v>
+        <v>128815115</v>
       </c>
       <c r="B128" t="n">
-        <v>87029</v>
+        <v>87008</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3624</v>
+        <v>3767</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -13380,10 +13384,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717337</v>
+        <v>717424</v>
       </c>
       <c r="R128" t="n">
-        <v>6373382</v>
+        <v>6373147</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13442,10 +13446,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128813018</v>
+        <v>128815126</v>
       </c>
       <c r="B129" t="n">
-        <v>110763</v>
+        <v>87029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13453,34 +13457,30 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219711</v>
+        <v>3624</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717512</v>
+        <v>717337</v>
       </c>
       <c r="R129" t="n">
-        <v>6373149</v>
+        <v>6373382</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13510,19 +13510,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13537,57 +13527,57 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128815115</v>
+        <v>128813080</v>
       </c>
       <c r="B130" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717424</v>
+        <v>717456</v>
       </c>
       <c r="R130" t="n">
-        <v>6373147</v>
+        <v>6373273</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13617,9 +13607,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13634,44 +13634,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813080</v>
+        <v>128813049</v>
       </c>
       <c r="B131" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13681,10 +13681,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717456</v>
+        <v>717330</v>
       </c>
       <c r="R131" t="n">
-        <v>6373273</v>
+        <v>6373178</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13753,45 +13753,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813049</v>
+        <v>128813075</v>
       </c>
       <c r="B132" t="n">
-        <v>86963</v>
+        <v>86879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717330</v>
+        <v>717344</v>
       </c>
       <c r="R132" t="n">
-        <v>6373178</v>
+        <v>6373206</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13823,7 +13826,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13833,7 +13836,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13842,6 +13850,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13860,48 +13869,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813075</v>
+        <v>128813018</v>
       </c>
       <c r="B133" t="n">
-        <v>86879</v>
+        <v>110763</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>248956</v>
+        <v>219711</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717344</v>
+        <v>717512</v>
       </c>
       <c r="R133" t="n">
-        <v>6373206</v>
+        <v>6373149</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13933,7 +13939,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13943,12 +13949,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13957,7 +13958,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13976,45 +13976,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128806319</v>
+        <v>128815155</v>
       </c>
       <c r="B134" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717087</v>
+        <v>717498</v>
       </c>
       <c r="R134" t="n">
-        <v>6373291</v>
+        <v>6373233</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14055,29 +14055,28 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128813027</v>
+        <v>128815133</v>
       </c>
       <c r="B135" t="n">
-        <v>91017</v>
+        <v>86764</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14085,34 +14084,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5741</v>
+        <v>3762</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717343</v>
+        <v>717314</v>
       </c>
       <c r="R135" t="n">
-        <v>6373129</v>
+        <v>6373361</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14142,19 +14141,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>10:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14169,22 +14158,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128815155</v>
+        <v>128813027</v>
       </c>
       <c r="B136" t="n">
-        <v>86926</v>
+        <v>91017</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14192,34 +14181,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717498</v>
+        <v>717343</v>
       </c>
       <c r="R136" t="n">
-        <v>6373233</v>
+        <v>6373129</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14249,9 +14238,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14266,12 +14265,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14375,45 +14374,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128815133</v>
+        <v>128806319</v>
       </c>
       <c r="B138" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717314</v>
+        <v>717087</v>
       </c>
       <c r="R138" t="n">
-        <v>6373361</v>
+        <v>6373291</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14454,63 +14453,64 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128806066</v>
+        <v>128815124</v>
       </c>
       <c r="B139" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717348</v>
+        <v>717467</v>
       </c>
       <c r="R139" t="n">
-        <v>6373330</v>
+        <v>6373240</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14557,19 +14557,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806070</v>
+        <v>128806066</v>
       </c>
       <c r="B140" t="n">
         <v>86926</v>
@@ -14604,10 +14604,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717289</v>
+        <v>717348</v>
       </c>
       <c r="R140" t="n">
-        <v>6373225</v>
+        <v>6373330</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806008</v>
+        <v>128806070</v>
       </c>
       <c r="B141" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14677,21 +14677,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14701,10 +14701,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717255</v>
+        <v>717289</v>
       </c>
       <c r="R141" t="n">
-        <v>6373321</v>
+        <v>6373225</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14763,10 +14763,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128813081</v>
+        <v>128806008</v>
       </c>
       <c r="B142" t="n">
-        <v>86926</v>
+        <v>86764</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14774,21 +14774,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14798,10 +14798,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717161</v>
+        <v>717255</v>
       </c>
       <c r="R142" t="n">
-        <v>6373174</v>
+        <v>6373321</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14831,19 +14831,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14858,19 +14848,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128815147</v>
+        <v>128813081</v>
       </c>
       <c r="B143" t="n">
         <v>86926</v>
@@ -14901,14 +14891,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717312</v>
+        <v>717161</v>
       </c>
       <c r="R143" t="n">
-        <v>6373366</v>
+        <v>6373174</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14938,9 +14928,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14955,44 +14955,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128815124</v>
+        <v>128815147</v>
       </c>
       <c r="B144" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717467</v>
+        <v>717312</v>
       </c>
       <c r="R144" t="n">
-        <v>6373240</v>
+        <v>6373366</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128805999</v>
+        <v>128815135</v>
       </c>
       <c r="B3" t="n">
-        <v>87008</v>
+        <v>86764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717287</v>
+        <v>717476</v>
       </c>
       <c r="R3" t="n">
-        <v>6373354</v>
+        <v>6373242</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128806048</v>
+        <v>128805999</v>
       </c>
       <c r="B4" t="n">
-        <v>90930</v>
+        <v>87008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717322</v>
+        <v>717287</v>
       </c>
       <c r="R4" t="n">
-        <v>6373213</v>
+        <v>6373354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128815113</v>
+        <v>128806348</v>
       </c>
       <c r="B5" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717317</v>
+        <v>717239</v>
       </c>
       <c r="R5" t="n">
-        <v>6373308</v>
+        <v>6373234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,57 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128813022</v>
+        <v>128815113</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>87008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717130</v>
+        <v>717317</v>
       </c>
       <c r="R6" t="n">
-        <v>6373194</v>
+        <v>6373308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,19 +1141,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128815135</v>
+        <v>128806072</v>
       </c>
       <c r="B7" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717476</v>
+        <v>717289</v>
       </c>
       <c r="R7" t="n">
-        <v>6373242</v>
+        <v>6373288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806348</v>
+        <v>128806048</v>
       </c>
       <c r="B8" t="n">
-        <v>86926</v>
+        <v>90930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717239</v>
+        <v>717322</v>
       </c>
       <c r="R8" t="n">
-        <v>6373234</v>
+        <v>6373213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128806072</v>
+        <v>128813022</v>
       </c>
       <c r="B9" t="n">
-        <v>86926</v>
+        <v>92810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717289</v>
+        <v>717130</v>
       </c>
       <c r="R9" t="n">
-        <v>6373288</v>
+        <v>6373194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,9 +1432,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,57 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128815136</v>
+        <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>86963</v>
+        <v>92443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717412</v>
+        <v>717370</v>
       </c>
       <c r="R10" t="n">
-        <v>6373217</v>
+        <v>6373322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,26 +1550,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128806033</v>
+        <v>128813034</v>
       </c>
       <c r="B11" t="n">
         <v>86963</v>
@@ -1604,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717315</v>
+        <v>717425</v>
       </c>
       <c r="R11" t="n">
-        <v>6373232</v>
+        <v>6373083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1637,37 +1636,46 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128813034</v>
+        <v>128806033</v>
       </c>
       <c r="B12" t="n">
         <v>86963</v>
@@ -1702,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717425</v>
+        <v>717315</v>
       </c>
       <c r="R12" t="n">
-        <v>6373083</v>
+        <v>6373232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1735,84 +1743,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128806006</v>
+        <v>128815136</v>
       </c>
       <c r="B13" t="n">
-        <v>92443</v>
+        <v>86963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717370</v>
+        <v>717412</v>
       </c>
       <c r="R13" t="n">
-        <v>6373322</v>
+        <v>6373217</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,18 +1852,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128815145</v>
+        <v>128813054</v>
       </c>
       <c r="B17" t="n">
-        <v>86929</v>
+        <v>86963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,34 +2173,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717299</v>
+        <v>717402</v>
       </c>
       <c r="R17" t="n">
-        <v>6373241</v>
+        <v>6373098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,30 +2230,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2367,10 +2376,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128813054</v>
+        <v>128815145</v>
       </c>
       <c r="B19" t="n">
-        <v>86963</v>
+        <v>86929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2378,34 +2387,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717402</v>
+        <v>717299</v>
       </c>
       <c r="R19" t="n">
-        <v>6373098</v>
+        <v>6373241</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,39 +2444,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2580,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813032</v>
+        <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717409</v>
+        <v>717316</v>
       </c>
       <c r="R21" t="n">
-        <v>6373057</v>
+        <v>6373307</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,19 +2648,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,57 +2665,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128806324</v>
+        <v>128815134</v>
       </c>
       <c r="B22" t="n">
-        <v>86963</v>
+        <v>86764</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717408</v>
+        <v>717316</v>
       </c>
       <c r="R22" t="n">
-        <v>6373296</v>
+        <v>6373365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,19 +2756,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2883,7 +2872,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128806029</v>
+        <v>128806324</v>
       </c>
       <c r="B24" t="n">
         <v>86963</v>
@@ -2918,10 +2907,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717149</v>
+        <v>717408</v>
       </c>
       <c r="R24" t="n">
-        <v>6373385</v>
+        <v>6373296</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,44 +2958,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128806311</v>
+        <v>128813032</v>
       </c>
       <c r="B25" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717316</v>
+        <v>717409</v>
       </c>
       <c r="R25" t="n">
-        <v>6373307</v>
+        <v>6373057</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3049,9 +3038,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3066,57 +3065,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128815134</v>
+        <v>128806029</v>
       </c>
       <c r="B26" t="n">
-        <v>86764</v>
+        <v>86963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717316</v>
+        <v>717149</v>
       </c>
       <c r="R26" t="n">
-        <v>6373365</v>
+        <v>6373385</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,18 +3156,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128813028</v>
+        <v>128806042</v>
       </c>
       <c r="B29" t="n">
-        <v>91017</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,34 +3380,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717490</v>
+        <v>717134</v>
       </c>
       <c r="R29" t="n">
-        <v>6373178</v>
+        <v>6373159</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3437,49 +3446,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128806042</v>
+        <v>128813028</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>91017</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3487,43 +3487,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>5741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717134</v>
+        <v>717490</v>
       </c>
       <c r="R30" t="n">
-        <v>6373159</v>
+        <v>6373178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,30 +3544,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128806002</v>
+        <v>128813070</v>
       </c>
       <c r="B32" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717297</v>
+        <v>717323</v>
       </c>
       <c r="R32" t="n">
-        <v>6373295</v>
+        <v>6373241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,9 +3758,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,19 +3785,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128813070</v>
+        <v>128813068</v>
       </c>
       <c r="B33" t="n">
         <v>86985</v>
@@ -3822,10 +3832,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717323</v>
+        <v>717085</v>
       </c>
       <c r="R33" t="n">
-        <v>6373241</v>
+        <v>6373275</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3857,7 +3867,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3867,7 +3877,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3894,45 +3904,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128813068</v>
+        <v>128815154</v>
       </c>
       <c r="B34" t="n">
-        <v>86985</v>
+        <v>86926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717085</v>
+        <v>717416</v>
       </c>
       <c r="R34" t="n">
-        <v>6373275</v>
+        <v>6373159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3962,19 +3972,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3989,19 +3989,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128815154</v>
+        <v>128806349</v>
       </c>
       <c r="B35" t="n">
         <v>86926</v>
@@ -4032,14 +4032,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717416</v>
+        <v>717337</v>
       </c>
       <c r="R35" t="n">
-        <v>6373159</v>
+        <v>6373337</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4086,19 +4086,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128806349</v>
+        <v>128806351</v>
       </c>
       <c r="B36" t="n">
         <v>86926</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717337</v>
+        <v>717390</v>
       </c>
       <c r="R36" t="n">
-        <v>6373337</v>
+        <v>6373317</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4195,32 +4195,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128806351</v>
+        <v>128806002</v>
       </c>
       <c r="B37" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717390</v>
+        <v>717297</v>
       </c>
       <c r="R37" t="n">
-        <v>6373317</v>
+        <v>6373295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4280,12 +4280,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4688,32 +4688,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815143</v>
+        <v>128815114</v>
       </c>
       <c r="B42" t="n">
-        <v>90969</v>
+        <v>87008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3286</v>
+        <v>3767</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717335</v>
+        <v>717431</v>
       </c>
       <c r="R42" t="n">
-        <v>6373383</v>
+        <v>6373147</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4785,32 +4785,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128815114</v>
+        <v>128815143</v>
       </c>
       <c r="B43" t="n">
-        <v>87008</v>
+        <v>90969</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3767</v>
+        <v>3286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717431</v>
+        <v>717335</v>
       </c>
       <c r="R43" t="n">
-        <v>6373147</v>
+        <v>6373383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128813036</v>
+        <v>128806035</v>
       </c>
       <c r="B44" t="n">
         <v>86963</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717436</v>
+        <v>717263</v>
       </c>
       <c r="R44" t="n">
-        <v>6373168</v>
+        <v>6373307</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4950,46 +4950,37 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128806035</v>
+        <v>128813036</v>
       </c>
       <c r="B45" t="n">
         <v>86963</v>
@@ -5024,10 +5015,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717263</v>
+        <v>717436</v>
       </c>
       <c r="R45" t="n">
-        <v>6373307</v>
+        <v>6373168</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5057,30 +5048,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5194,32 +5194,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128813046</v>
+        <v>128806053</v>
       </c>
       <c r="B47" t="n">
-        <v>86963</v>
+        <v>86788</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717216</v>
+        <v>717382</v>
       </c>
       <c r="R47" t="n">
-        <v>6373176</v>
+        <v>6373309</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5262,19 +5262,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5289,44 +5279,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128813040</v>
+        <v>128806345</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5336,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717487</v>
+        <v>717170</v>
       </c>
       <c r="R48" t="n">
-        <v>6373202</v>
+        <v>6373195</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5369,19 +5359,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5396,44 +5376,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128806053</v>
+        <v>128813040</v>
       </c>
       <c r="B49" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5443,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717382</v>
+        <v>717487</v>
       </c>
       <c r="R49" t="n">
-        <v>6373309</v>
+        <v>6373202</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5476,9 +5456,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5493,44 +5483,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128806345</v>
+        <v>128813046</v>
       </c>
       <c r="B50" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5540,10 +5530,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717170</v>
+        <v>717216</v>
       </c>
       <c r="R50" t="n">
-        <v>6373195</v>
+        <v>6373176</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,9 +5563,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5590,57 +5590,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128813042</v>
+        <v>128815141</v>
       </c>
       <c r="B51" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717084</v>
+        <v>717505</v>
       </c>
       <c r="R51" t="n">
-        <v>6373295</v>
+        <v>6373241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5670,19 +5670,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5697,22 +5687,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128806034</v>
+        <v>128806334</v>
       </c>
       <c r="B52" t="n">
-        <v>86963</v>
+        <v>90969</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5720,21 +5710,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5744,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717303</v>
+        <v>717324</v>
       </c>
       <c r="R52" t="n">
-        <v>6373236</v>
+        <v>6373355</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5788,29 +5778,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128815141</v>
+        <v>128815131</v>
       </c>
       <c r="B53" t="n">
-        <v>86985</v>
+        <v>91044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5807,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5831,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717505</v>
+        <v>717416</v>
       </c>
       <c r="R53" t="n">
-        <v>6373241</v>
+        <v>6373162</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5880,12 +5869,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5904,32 +5899,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128806334</v>
+        <v>128806069</v>
       </c>
       <c r="B54" t="n">
-        <v>90969</v>
+        <v>86926</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5934,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717324</v>
+        <v>717117</v>
       </c>
       <c r="R54" t="n">
-        <v>6373355</v>
+        <v>6373208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5989,57 +5984,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128815131</v>
+        <v>128806074</v>
       </c>
       <c r="B55" t="n">
-        <v>91044</v>
+        <v>86926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717416</v>
+        <v>717445</v>
       </c>
       <c r="R55" t="n">
-        <v>6373162</v>
+        <v>6373269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6074,62 +6069,56 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128806069</v>
+        <v>128806034</v>
       </c>
       <c r="B56" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6139,10 +6128,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717117</v>
+        <v>717303</v>
       </c>
       <c r="R56" t="n">
-        <v>6373208</v>
+        <v>6373236</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6183,6 +6172,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6194,39 +6184,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128806074</v>
+        <v>128813042</v>
       </c>
       <c r="B57" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6236,10 +6226,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717445</v>
+        <v>717084</v>
       </c>
       <c r="R57" t="n">
-        <v>6373269</v>
+        <v>6373295</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6269,9 +6259,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6286,57 +6286,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128806330</v>
+        <v>128815116</v>
       </c>
       <c r="B58" t="n">
-        <v>107550</v>
+        <v>87008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>3767</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717069</v>
+        <v>717420</v>
       </c>
       <c r="R58" t="n">
-        <v>6373282</v>
+        <v>6373147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6383,57 +6383,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128806322</v>
+        <v>128815152</v>
       </c>
       <c r="B59" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717234</v>
+        <v>717329</v>
       </c>
       <c r="R59" t="n">
-        <v>6373222</v>
+        <v>6373260</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6474,64 +6474,63 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128815116</v>
+        <v>128806054</v>
       </c>
       <c r="B60" t="n">
-        <v>87008</v>
+        <v>86788</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717420</v>
+        <v>717273</v>
       </c>
       <c r="R60" t="n">
-        <v>6373147</v>
+        <v>6373345</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6578,19 +6577,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128815152</v>
+        <v>128815148</v>
       </c>
       <c r="B61" t="n">
         <v>86926</v>
@@ -6625,10 +6624,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717329</v>
+        <v>717239</v>
       </c>
       <c r="R61" t="n">
-        <v>6373260</v>
+        <v>6373262</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6687,32 +6686,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128806054</v>
+        <v>128806322</v>
       </c>
       <c r="B62" t="n">
-        <v>86788</v>
+        <v>86963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6722,10 +6721,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717273</v>
+        <v>717234</v>
       </c>
       <c r="R62" t="n">
-        <v>6373345</v>
+        <v>6373222</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,63 +6765,64 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128815148</v>
+        <v>128806330</v>
       </c>
       <c r="B63" t="n">
-        <v>86926</v>
+        <v>107550</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3674</v>
+        <v>220079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717239</v>
+        <v>717069</v>
       </c>
       <c r="R63" t="n">
-        <v>6373262</v>
+        <v>6373282</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6869,22 +6869,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128813012</v>
+        <v>128813066</v>
       </c>
       <c r="B64" t="n">
-        <v>87008</v>
+        <v>86985</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717435</v>
+        <v>717515</v>
       </c>
       <c r="R64" t="n">
-        <v>6373156</v>
+        <v>6373166</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6988,32 +6988,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128813044</v>
+        <v>128806333</v>
       </c>
       <c r="B65" t="n">
-        <v>86963</v>
+        <v>86985</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717135</v>
+        <v>717331</v>
       </c>
       <c r="R65" t="n">
-        <v>6373174</v>
+        <v>6373327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7056,19 +7056,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7083,44 +7073,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128806036</v>
+        <v>128813079</v>
       </c>
       <c r="B66" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7130,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717449</v>
+        <v>717315</v>
       </c>
       <c r="R66" t="n">
-        <v>6373281</v>
+        <v>6373221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7163,62 +7153,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813066</v>
+        <v>128806350</v>
       </c>
       <c r="B67" t="n">
-        <v>86985</v>
+        <v>86926</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7228,10 +7227,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717515</v>
+        <v>717330</v>
       </c>
       <c r="R67" t="n">
-        <v>6373166</v>
+        <v>6373328</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7261,19 +7260,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7288,22 +7277,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128806333</v>
+        <v>128813012</v>
       </c>
       <c r="B68" t="n">
-        <v>86985</v>
+        <v>87008</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7311,21 +7300,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7335,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717331</v>
+        <v>717435</v>
       </c>
       <c r="R68" t="n">
-        <v>6373327</v>
+        <v>6373156</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,9 +7357,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7385,12 +7384,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7494,45 +7493,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128813079</v>
+        <v>128806342</v>
       </c>
       <c r="B70" t="n">
-        <v>86926</v>
+        <v>86717</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3674</v>
+        <v>249278</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717315</v>
+        <v>717179</v>
       </c>
       <c r="R70" t="n">
-        <v>6373221</v>
+        <v>6373227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7562,19 +7564,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:38</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7583,50 +7580,51 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128806350</v>
+        <v>128813044</v>
       </c>
       <c r="B71" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7636,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717330</v>
+        <v>717135</v>
       </c>
       <c r="R71" t="n">
-        <v>6373328</v>
+        <v>6373174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7669,9 +7667,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7686,22 +7694,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806342</v>
+        <v>128806036</v>
       </c>
       <c r="B72" t="n">
-        <v>86717</v>
+        <v>86963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7709,37 +7717,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717179</v>
+        <v>717449</v>
       </c>
       <c r="R72" t="n">
-        <v>6373227</v>
+        <v>6373281</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7774,11 +7779,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7792,44 +7792,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128813020</v>
+        <v>128806046</v>
       </c>
       <c r="B73" t="n">
-        <v>57717</v>
+        <v>86985</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7839,13 +7839,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717395</v>
+        <v>717129</v>
       </c>
       <c r="R73" t="n">
-        <v>6373086</v>
+        <v>6373201</v>
       </c>
       <c r="S73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7872,19 +7872,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7899,44 +7889,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128806046</v>
+        <v>128813020</v>
       </c>
       <c r="B74" t="n">
-        <v>86985</v>
+        <v>57717</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7946,13 +7936,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>717129</v>
+        <v>717395</v>
       </c>
       <c r="R74" t="n">
-        <v>6373201</v>
+        <v>6373086</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7979,9 +7969,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,12 +7996,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8115,32 +8115,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128806047</v>
+        <v>128813055</v>
       </c>
       <c r="B76" t="n">
-        <v>86985</v>
+        <v>98670</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>449</v>
+        <v>219874</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717290</v>
+        <v>717326</v>
       </c>
       <c r="R76" t="n">
-        <v>6373221</v>
+        <v>6373144</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8183,9 +8183,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8200,60 +8210,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806316</v>
+        <v>128806026</v>
       </c>
       <c r="B77" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717125</v>
+        <v>717211</v>
       </c>
       <c r="R77" t="n">
-        <v>6373250</v>
+        <v>6373375</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8301,44 +8308,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128813077</v>
+        <v>128806031</v>
       </c>
       <c r="B78" t="n">
-        <v>86810</v>
+        <v>86963</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8348,10 +8355,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717116</v>
+        <v>717071</v>
       </c>
       <c r="R78" t="n">
-        <v>6373207</v>
+        <v>6373294</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,84 +8388,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128806067</v>
+        <v>128815128</v>
       </c>
       <c r="B79" t="n">
-        <v>86926</v>
+        <v>91044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717298</v>
+        <v>717418</v>
       </c>
       <c r="R79" t="n">
-        <v>6373345</v>
+        <v>6373171</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,28 +8497,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128815128</v>
+        <v>128806001</v>
       </c>
       <c r="B80" t="n">
-        <v>91044</v>
+        <v>87008</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8528,34 +8527,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717418</v>
+        <v>717159</v>
       </c>
       <c r="R80" t="n">
-        <v>6373171</v>
+        <v>6373378</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8596,26 +8595,25 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128806001</v>
+        <v>128815117</v>
       </c>
       <c r="B81" t="n">
         <v>87008</v>
@@ -8646,14 +8644,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717159</v>
+        <v>717416</v>
       </c>
       <c r="R81" t="n">
-        <v>6373378</v>
+        <v>6373167</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8700,57 +8698,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128815117</v>
+        <v>128806067</v>
       </c>
       <c r="B82" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717416</v>
+        <v>717298</v>
       </c>
       <c r="R82" t="n">
-        <v>6373167</v>
+        <v>6373345</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8797,44 +8795,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128813055</v>
+        <v>128806047</v>
       </c>
       <c r="B83" t="n">
-        <v>98670</v>
+        <v>86985</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219874</v>
+        <v>449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8844,10 +8842,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717326</v>
+        <v>717290</v>
       </c>
       <c r="R83" t="n">
-        <v>6373144</v>
+        <v>6373221</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8877,19 +8875,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8904,57 +8892,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128806026</v>
+        <v>128806316</v>
       </c>
       <c r="B84" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717211</v>
+        <v>717125</v>
       </c>
       <c r="R84" t="n">
-        <v>6373375</v>
+        <v>6373250</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9002,44 +8993,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128806031</v>
+        <v>128813077</v>
       </c>
       <c r="B85" t="n">
-        <v>86963</v>
+        <v>86810</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9049,10 +9040,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717071</v>
+        <v>717116</v>
       </c>
       <c r="R85" t="n">
-        <v>6373294</v>
+        <v>6373207</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9082,62 +9073,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128815156</v>
+        <v>128815130</v>
       </c>
       <c r="B86" t="n">
-        <v>86926</v>
+        <v>91044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717444</v>
+        <v>717326</v>
       </c>
       <c r="R86" t="n">
-        <v>6373273</v>
+        <v>6373267</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9191,6 +9191,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9209,53 +9210,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806007</v>
+        <v>128813078</v>
       </c>
       <c r="B87" t="n">
-        <v>57717</v>
+        <v>86810</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717083</v>
+        <v>717243</v>
       </c>
       <c r="R87" t="n">
-        <v>6373260</v>
+        <v>6373192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9285,9 +9278,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9302,57 +9305,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128806318</v>
+        <v>128815156</v>
       </c>
       <c r="B88" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717062</v>
+        <v>717444</v>
       </c>
       <c r="R88" t="n">
-        <v>6373304</v>
+        <v>6373273</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9393,29 +9396,28 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128813078</v>
+        <v>128815120</v>
       </c>
       <c r="B89" t="n">
-        <v>86810</v>
+        <v>87008</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9423,34 +9425,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>3767</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717243</v>
+        <v>717479</v>
       </c>
       <c r="R89" t="n">
-        <v>6373192</v>
+        <v>6373226</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9480,19 +9482,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9507,57 +9499,65 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128815130</v>
+        <v>128806007</v>
       </c>
       <c r="B90" t="n">
-        <v>91044</v>
+        <v>57717</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717326</v>
+        <v>717083</v>
       </c>
       <c r="R90" t="n">
-        <v>6373267</v>
+        <v>6373260</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9598,29 +9598,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128815120</v>
+        <v>128813061</v>
       </c>
       <c r="B91" t="n">
-        <v>87008</v>
+        <v>86879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9628,34 +9627,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717479</v>
+        <v>717085</v>
       </c>
       <c r="R91" t="n">
-        <v>6373226</v>
+        <v>6373261</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9685,9 +9684,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9702,44 +9711,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128813061</v>
+        <v>128806318</v>
       </c>
       <c r="B92" t="n">
-        <v>86879</v>
+        <v>86963</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9749,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717085</v>
+        <v>717062</v>
       </c>
       <c r="R92" t="n">
-        <v>6373261</v>
+        <v>6373304</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9782,39 +9791,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10230,45 +10230,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128815123</v>
+        <v>128806071</v>
       </c>
       <c r="B97" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717500</v>
+        <v>717287</v>
       </c>
       <c r="R97" t="n">
-        <v>6373237</v>
+        <v>6373292</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10315,19 +10315,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815118</v>
+        <v>128815123</v>
       </c>
       <c r="B98" t="n">
         <v>87008</v>
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717431</v>
+        <v>717500</v>
       </c>
       <c r="R98" t="n">
-        <v>6373173</v>
+        <v>6373237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10424,45 +10424,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128806071</v>
+        <v>128815118</v>
       </c>
       <c r="B99" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717287</v>
+        <v>717431</v>
       </c>
       <c r="R99" t="n">
-        <v>6373292</v>
+        <v>6373173</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10509,12 +10509,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10632,7 +10632,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128815137</v>
+        <v>128813052</v>
       </c>
       <c r="B101" t="n">
         <v>86963</v>
@@ -10663,14 +10663,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717433</v>
+        <v>717411</v>
       </c>
       <c r="R101" t="n">
-        <v>6373170</v>
+        <v>6373077</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10700,37 +10700,46 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128813052</v>
+        <v>128815137</v>
       </c>
       <c r="B102" t="n">
         <v>86963</v>
@@ -10761,14 +10770,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717411</v>
+        <v>717433</v>
       </c>
       <c r="R102" t="n">
-        <v>6373077</v>
+        <v>6373170</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10798,84 +10807,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128806323</v>
+        <v>128815129</v>
       </c>
       <c r="B103" t="n">
-        <v>86963</v>
+        <v>91044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717241</v>
+        <v>717424</v>
       </c>
       <c r="R103" t="n">
-        <v>6373264</v>
+        <v>6373165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10916,64 +10916,63 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128806028</v>
+        <v>128815151</v>
       </c>
       <c r="B104" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717179</v>
+        <v>717270</v>
       </c>
       <c r="R104" t="n">
-        <v>6373374</v>
+        <v>6373304</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11014,64 +11013,63 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128806320</v>
+        <v>128815149</v>
       </c>
       <c r="B105" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717131</v>
+        <v>717269</v>
       </c>
       <c r="R105" t="n">
-        <v>6373249</v>
+        <v>6373207</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11112,29 +11110,28 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128815129</v>
+        <v>128815110</v>
       </c>
       <c r="B106" t="n">
-        <v>91044</v>
+        <v>87008</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11142,21 +11139,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11166,10 +11163,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717424</v>
+        <v>717281</v>
       </c>
       <c r="R106" t="n">
-        <v>6373165</v>
+        <v>6373300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11228,45 +11225,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128815110</v>
+        <v>128813073</v>
       </c>
       <c r="B107" t="n">
-        <v>87008</v>
+        <v>92834</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3767</v>
+        <v>5964</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717281</v>
+        <v>717453</v>
       </c>
       <c r="R107" t="n">
-        <v>6373300</v>
+        <v>6373125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11296,74 +11296,85 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128815151</v>
+        <v>128806320</v>
       </c>
       <c r="B108" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717270</v>
+        <v>717131</v>
       </c>
       <c r="R108" t="n">
-        <v>6373304</v>
+        <v>6373249</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11404,63 +11415,64 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128815149</v>
+        <v>128806028</v>
       </c>
       <c r="B109" t="n">
-        <v>86926</v>
+        <v>86963</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717269</v>
+        <v>717179</v>
       </c>
       <c r="R109" t="n">
-        <v>6373207</v>
+        <v>6373374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11501,66 +11513,64 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128813073</v>
+        <v>128806323</v>
       </c>
       <c r="B110" t="n">
-        <v>92834</v>
+        <v>86963</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717453</v>
+        <v>717241</v>
       </c>
       <c r="R110" t="n">
-        <v>6373125</v>
+        <v>6373264</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11590,19 +11600,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,44 +11618,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813063</v>
+        <v>128813568</v>
       </c>
       <c r="B111" t="n">
-        <v>92262</v>
+        <v>86906</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>232138</v>
+        <v>473</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11665,10 +11665,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717511</v>
+        <v>717322</v>
       </c>
       <c r="R111" t="n">
-        <v>6373145</v>
+        <v>6373203</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11737,45 +11737,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128813048</v>
+        <v>128815121</v>
       </c>
       <c r="B112" t="n">
-        <v>86963</v>
+        <v>87008</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717248</v>
+        <v>717499</v>
       </c>
       <c r="R112" t="n">
-        <v>6373196</v>
+        <v>6373239</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11805,19 +11805,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11832,60 +11822,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806055</v>
+        <v>128806313</v>
       </c>
       <c r="B113" t="n">
-        <v>86717</v>
+        <v>87008</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717283</v>
+        <v>717369</v>
       </c>
       <c r="R113" t="n">
-        <v>6373299</v>
+        <v>6373319</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11920,75 +11907,72 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128815139</v>
+        <v>128806055</v>
       </c>
       <c r="B114" t="n">
-        <v>86879</v>
+        <v>86717</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717313</v>
+        <v>717283</v>
       </c>
       <c r="R114" t="n">
-        <v>6373361</v>
+        <v>6373299</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12023,69 +12007,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128813568</v>
+        <v>128815139</v>
       </c>
       <c r="B115" t="n">
-        <v>86906</v>
+        <v>86879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>473</v>
+        <v>248956</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717322</v>
+        <v>717313</v>
       </c>
       <c r="R115" t="n">
-        <v>6373203</v>
+        <v>6373361</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12115,19 +12105,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12142,57 +12122,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128815121</v>
+        <v>128813048</v>
       </c>
       <c r="B116" t="n">
-        <v>87008</v>
+        <v>86963</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717499</v>
+        <v>717248</v>
       </c>
       <c r="R116" t="n">
-        <v>6373239</v>
+        <v>6373196</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12222,9 +12202,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12239,22 +12229,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128806313</v>
+        <v>128813063</v>
       </c>
       <c r="B117" t="n">
-        <v>87008</v>
+        <v>92262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12262,21 +12252,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3767</v>
+        <v>232138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12286,10 +12276,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717369</v>
+        <v>717511</v>
       </c>
       <c r="R117" t="n">
-        <v>6373319</v>
+        <v>6373145</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12319,9 +12309,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12336,44 +12336,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128813030</v>
+        <v>128806315</v>
       </c>
       <c r="B118" t="n">
-        <v>86939</v>
+        <v>86810</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1988</v>
+        <v>424</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717079</v>
+        <v>717165</v>
       </c>
       <c r="R118" t="n">
-        <v>6373300</v>
+        <v>6373195</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12416,19 +12416,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12443,44 +12433,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806347</v>
+        <v>128806312</v>
       </c>
       <c r="B119" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717092</v>
+        <v>717332</v>
       </c>
       <c r="R119" t="n">
-        <v>6373322</v>
+        <v>6373350</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12552,45 +12542,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806340</v>
+        <v>128815111</v>
       </c>
       <c r="B120" t="n">
-        <v>86788</v>
+        <v>87008</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717314</v>
+        <v>717318</v>
       </c>
       <c r="R120" t="n">
-        <v>6373345</v>
+        <v>6373242</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12637,44 +12627,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806032</v>
+        <v>128806347</v>
       </c>
       <c r="B121" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12684,10 +12674,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717081</v>
+        <v>717092</v>
       </c>
       <c r="R121" t="n">
-        <v>6373276</v>
+        <v>6373322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12728,51 +12718,50 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128813056</v>
+        <v>128813014</v>
       </c>
       <c r="B122" t="n">
-        <v>98670</v>
+        <v>87008</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12782,10 +12771,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717484</v>
+        <v>717462</v>
       </c>
       <c r="R122" t="n">
-        <v>6373174</v>
+        <v>6373231</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12817,7 +12806,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -12827,7 +12816,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12854,32 +12843,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806315</v>
+        <v>128806340</v>
       </c>
       <c r="B123" t="n">
-        <v>86810</v>
+        <v>86788</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12889,10 +12878,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717165</v>
+        <v>717314</v>
       </c>
       <c r="R123" t="n">
-        <v>6373195</v>
+        <v>6373345</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12951,32 +12940,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806312</v>
+        <v>128806331</v>
       </c>
       <c r="B124" t="n">
-        <v>87008</v>
+        <v>90344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3767</v>
+        <v>6292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12986,10 +12975,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717332</v>
+        <v>717106</v>
       </c>
       <c r="R124" t="n">
-        <v>6373350</v>
+        <v>6373238</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13048,45 +13037,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128815111</v>
+        <v>128813030</v>
       </c>
       <c r="B125" t="n">
-        <v>87008</v>
+        <v>86939</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3767</v>
+        <v>1988</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717318</v>
+        <v>717079</v>
       </c>
       <c r="R125" t="n">
-        <v>6373242</v>
+        <v>6373300</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13116,9 +13105,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13133,44 +13132,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128813014</v>
+        <v>128813056</v>
       </c>
       <c r="B126" t="n">
-        <v>87008</v>
+        <v>98670</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3767</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13180,10 +13179,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717462</v>
+        <v>717484</v>
       </c>
       <c r="R126" t="n">
-        <v>6373231</v>
+        <v>6373174</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13215,7 +13214,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13225,7 +13224,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13252,32 +13251,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806331</v>
+        <v>128806032</v>
       </c>
       <c r="B127" t="n">
-        <v>90344</v>
+        <v>86963</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6292</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13286,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717106</v>
+        <v>717081</v>
       </c>
       <c r="R127" t="n">
-        <v>6373238</v>
+        <v>6373276</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13331,28 +13330,29 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128815115</v>
+        <v>128813075</v>
       </c>
       <c r="B128" t="n">
-        <v>87008</v>
+        <v>86879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13360,34 +13360,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717424</v>
+        <v>717344</v>
       </c>
       <c r="R128" t="n">
-        <v>6373147</v>
+        <v>6373206</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13417,59 +13420,79 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128815126</v>
+        <v>128815115</v>
       </c>
       <c r="B129" t="n">
-        <v>87029</v>
+        <v>87008</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3624</v>
+        <v>3767</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13477,10 +13500,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717337</v>
+        <v>717424</v>
       </c>
       <c r="R129" t="n">
-        <v>6373382</v>
+        <v>6373147</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13539,10 +13562,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128813080</v>
+        <v>128815126</v>
       </c>
       <c r="B130" t="n">
-        <v>86926</v>
+        <v>87029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13550,34 +13573,30 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717456</v>
+        <v>717337</v>
       </c>
       <c r="R130" t="n">
-        <v>6373273</v>
+        <v>6373382</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13607,19 +13626,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>08:59</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13634,44 +13643,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813049</v>
+        <v>128813080</v>
       </c>
       <c r="B131" t="n">
-        <v>86963</v>
+        <v>86926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13681,10 +13690,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717330</v>
+        <v>717456</v>
       </c>
       <c r="R131" t="n">
-        <v>6373178</v>
+        <v>6373273</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13716,7 +13725,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13726,7 +13735,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13753,48 +13762,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813075</v>
+        <v>128813018</v>
       </c>
       <c r="B132" t="n">
-        <v>86879</v>
+        <v>110763</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>248956</v>
+        <v>219711</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717344</v>
+        <v>717512</v>
       </c>
       <c r="R132" t="n">
-        <v>6373206</v>
+        <v>6373149</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13826,7 +13832,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13836,12 +13842,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13850,7 +13851,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13869,32 +13869,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813018</v>
+        <v>128813049</v>
       </c>
       <c r="B133" t="n">
-        <v>110763</v>
+        <v>86963</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717512</v>
+        <v>717330</v>
       </c>
       <c r="R133" t="n">
-        <v>6373149</v>
+        <v>6373178</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13976,10 +13976,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128815155</v>
+        <v>128813027</v>
       </c>
       <c r="B134" t="n">
-        <v>86926</v>
+        <v>91017</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13987,34 +13987,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3674</v>
+        <v>5741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>717498</v>
+        <v>717343</v>
       </c>
       <c r="R134" t="n">
-        <v>6373233</v>
+        <v>6373129</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14044,9 +14044,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14061,22 +14071,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128815133</v>
+        <v>128815155</v>
       </c>
       <c r="B135" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14084,21 +14094,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14108,10 +14118,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717314</v>
+        <v>717498</v>
       </c>
       <c r="R135" t="n">
-        <v>6373361</v>
+        <v>6373233</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14170,32 +14180,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128813027</v>
+        <v>128806000</v>
       </c>
       <c r="B136" t="n">
-        <v>91017</v>
+        <v>87008</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5741</v>
+        <v>3767</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14205,10 +14215,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717343</v>
+        <v>717298</v>
       </c>
       <c r="R136" t="n">
-        <v>6373129</v>
+        <v>6373343</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14238,19 +14248,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>10:05</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14265,57 +14265,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128806000</v>
+        <v>128815133</v>
       </c>
       <c r="B137" t="n">
-        <v>87008</v>
+        <v>86764</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717298</v>
+        <v>717314</v>
       </c>
       <c r="R137" t="n">
-        <v>6373343</v>
+        <v>6373361</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14362,12 +14362,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -14472,45 +14472,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128815124</v>
+        <v>128806066</v>
       </c>
       <c r="B139" t="n">
-        <v>87008</v>
+        <v>86926</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717467</v>
+        <v>717348</v>
       </c>
       <c r="R139" t="n">
-        <v>6373240</v>
+        <v>6373330</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14557,19 +14557,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806066</v>
+        <v>128806070</v>
       </c>
       <c r="B140" t="n">
         <v>86926</v>
@@ -14604,10 +14604,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717348</v>
+        <v>717289</v>
       </c>
       <c r="R140" t="n">
-        <v>6373330</v>
+        <v>6373225</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806070</v>
+        <v>128806008</v>
       </c>
       <c r="B141" t="n">
-        <v>86926</v>
+        <v>86764</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14677,21 +14677,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14701,10 +14701,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717289</v>
+        <v>717255</v>
       </c>
       <c r="R141" t="n">
-        <v>6373225</v>
+        <v>6373321</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14763,10 +14763,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128806008</v>
+        <v>128813081</v>
       </c>
       <c r="B142" t="n">
-        <v>86764</v>
+        <v>86926</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14774,21 +14774,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14798,10 +14798,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717255</v>
+        <v>717161</v>
       </c>
       <c r="R142" t="n">
-        <v>6373321</v>
+        <v>6373174</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14831,9 +14831,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14848,19 +14858,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128813081</v>
+        <v>128815147</v>
       </c>
       <c r="B143" t="n">
         <v>86926</v>
@@ -14891,14 +14901,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717161</v>
+        <v>717312</v>
       </c>
       <c r="R143" t="n">
-        <v>6373174</v>
+        <v>6373366</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14928,19 +14938,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14955,44 +14955,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128815147</v>
+        <v>128815124</v>
       </c>
       <c r="B144" t="n">
-        <v>86926</v>
+        <v>87008</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717312</v>
+        <v>717467</v>
       </c>
       <c r="R144" t="n">
-        <v>6373366</v>
+        <v>6373240</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128813071</v>
       </c>
       <c r="B2" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128815135</v>
       </c>
       <c r="B3" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128805999</v>
       </c>
       <c r="B4" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806348</v>
+        <v>128806048</v>
       </c>
       <c r="B5" t="n">
-        <v>86926</v>
+        <v>90935</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717239</v>
+        <v>717322</v>
       </c>
       <c r="R5" t="n">
-        <v>6373234</v>
+        <v>6373213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,57 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128815113</v>
+        <v>128806348</v>
       </c>
       <c r="B6" t="n">
-        <v>87008</v>
+        <v>86931</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717317</v>
+        <v>717239</v>
       </c>
       <c r="R6" t="n">
-        <v>6373308</v>
+        <v>6373234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,57 +1158,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128806072</v>
+        <v>128815113</v>
       </c>
       <c r="B7" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717289</v>
+        <v>717317</v>
       </c>
       <c r="R7" t="n">
-        <v>6373288</v>
+        <v>6373308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806048</v>
+        <v>128806072</v>
       </c>
       <c r="B8" t="n">
-        <v>90930</v>
+        <v>86931</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717322</v>
+        <v>717289</v>
       </c>
       <c r="R8" t="n">
-        <v>6373213</v>
+        <v>6373288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>128813022</v>
       </c>
       <c r="B9" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128813034</v>
+        <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,14 +1599,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717425</v>
+        <v>717412</v>
       </c>
       <c r="R11" t="n">
-        <v>6373083</v>
+        <v>6373217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1636,39 +1636,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1678,7 +1669,7 @@
         <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,10 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128815136</v>
+        <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,14 +1795,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717412</v>
+        <v>717425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373217</v>
+        <v>6373083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,75 +1832,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128805997</v>
+        <v>128815153</v>
       </c>
       <c r="B14" t="n">
-        <v>87008</v>
+        <v>86931</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717416</v>
+        <v>717341</v>
       </c>
       <c r="R14" t="n">
-        <v>6373282</v>
+        <v>6373251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,22 +1956,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128806003</v>
+        <v>128805997</v>
       </c>
       <c r="B15" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717431</v>
+        <v>717416</v>
       </c>
       <c r="R15" t="n">
-        <v>6373255</v>
+        <v>6373282</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,45 +2065,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815153</v>
+        <v>128806003</v>
       </c>
       <c r="B16" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717341</v>
+        <v>717431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373251</v>
+        <v>6373255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,22 +2150,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813054</v>
+        <v>128815145</v>
       </c>
       <c r="B17" t="n">
-        <v>86963</v>
+        <v>86934</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,34 +2173,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>6037417</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717402</v>
+        <v>717299</v>
       </c>
       <c r="R17" t="n">
-        <v>6373098</v>
+        <v>6373241</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,49 +2230,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128813050</v>
+        <v>128806343</v>
       </c>
       <c r="B18" t="n">
-        <v>86963</v>
+        <v>86722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2280,34 +2271,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717330</v>
+        <v>717258</v>
       </c>
       <c r="R18" t="n">
-        <v>6373140</v>
+        <v>6373299</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,19 +2331,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:06</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,28 +2347,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128815145</v>
+        <v>128813050</v>
       </c>
       <c r="B19" t="n">
-        <v>86929</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2387,34 +2377,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717299</v>
+        <v>717330</v>
       </c>
       <c r="R19" t="n">
-        <v>6373241</v>
+        <v>6373140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,40 +2434,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128806343</v>
+        <v>128813054</v>
       </c>
       <c r="B20" t="n">
-        <v>86717</v>
+        <v>86968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2485,37 +2484,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717258</v>
+        <v>717402</v>
       </c>
       <c r="R20" t="n">
-        <v>6373299</v>
+        <v>6373098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,14 +2541,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2561,19 +2562,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
         <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>128815134</v>
       </c>
       <c r="B22" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128806027</v>
+        <v>128813032</v>
       </c>
       <c r="B23" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717195</v>
+        <v>717409</v>
       </c>
       <c r="R23" t="n">
-        <v>6373376</v>
+        <v>6373057</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,30 +2842,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2875,7 +2884,7 @@
         <v>128806324</v>
       </c>
       <c r="B24" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2970,10 +2979,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128813032</v>
+        <v>128806027</v>
       </c>
       <c r="B25" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,10 +3014,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717409</v>
+        <v>717195</v>
       </c>
       <c r="R25" t="n">
-        <v>6373057</v>
+        <v>6373376</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,39 +3047,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3080,7 +3080,7 @@
         <v>128806029</v>
       </c>
       <c r="B26" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128815122</v>
       </c>
       <c r="B27" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128805998</v>
       </c>
       <c r="B28" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128806042</v>
+        <v>128813028</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>91022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,43 +3380,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>5741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717134</v>
+        <v>717490</v>
       </c>
       <c r="R29" t="n">
-        <v>6373159</v>
+        <v>6373178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3446,40 +3437,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128813028</v>
+        <v>128806042</v>
       </c>
       <c r="B30" t="n">
-        <v>91017</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3487,34 +3487,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5741</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717490</v>
+        <v>717134</v>
       </c>
       <c r="R30" t="n">
-        <v>6373178</v>
+        <v>6373159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3544,39 +3553,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:13</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
         <v>128813051</v>
       </c>
       <c r="B31" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,45 +3690,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128813070</v>
+        <v>128815154</v>
       </c>
       <c r="B32" t="n">
-        <v>86985</v>
+        <v>86931</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717323</v>
+        <v>717416</v>
       </c>
       <c r="R32" t="n">
-        <v>6373241</v>
+        <v>6373159</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,19 +3758,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3785,44 +3775,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128813068</v>
+        <v>128806349</v>
       </c>
       <c r="B33" t="n">
-        <v>86985</v>
+        <v>86931</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3832,10 +3822,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717085</v>
+        <v>717337</v>
       </c>
       <c r="R33" t="n">
-        <v>6373275</v>
+        <v>6373337</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,19 +3855,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3892,22 +3872,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128815154</v>
+        <v>128806351</v>
       </c>
       <c r="B34" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,14 +3915,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717416</v>
+        <v>717390</v>
       </c>
       <c r="R34" t="n">
-        <v>6373159</v>
+        <v>6373317</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3989,44 +3969,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806349</v>
+        <v>128806002</v>
       </c>
       <c r="B35" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4016,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717337</v>
+        <v>717297</v>
       </c>
       <c r="R35" t="n">
-        <v>6373337</v>
+        <v>6373295</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4086,44 +4066,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128806351</v>
+        <v>128813070</v>
       </c>
       <c r="B36" t="n">
-        <v>86926</v>
+        <v>86990</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4133,10 +4113,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717390</v>
+        <v>717323</v>
       </c>
       <c r="R36" t="n">
-        <v>6373317</v>
+        <v>6373241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,9 +4146,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,22 +4173,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128806002</v>
+        <v>128813068</v>
       </c>
       <c r="B37" t="n">
-        <v>87008</v>
+        <v>86990</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,21 +4196,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4230,10 +4220,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717297</v>
+        <v>717085</v>
       </c>
       <c r="R37" t="n">
-        <v>6373295</v>
+        <v>6373275</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4263,9 +4253,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,12 +4280,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
         <v>128806025</v>
       </c>
       <c r="B38" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128806317</v>
       </c>
       <c r="B39" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128813065</v>
+        <v>128815114</v>
       </c>
       <c r="B40" t="n">
-        <v>86985</v>
+        <v>87013</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4495,34 +4495,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>717407</v>
+        <v>717431</v>
       </c>
       <c r="R40" t="n">
-        <v>6373048</v>
+        <v>6373147</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4552,19 +4552,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4579,57 +4569,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128815140</v>
+        <v>128813036</v>
       </c>
       <c r="B41" t="n">
-        <v>86985</v>
+        <v>86968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>717460</v>
+        <v>717436</v>
       </c>
       <c r="R41" t="n">
-        <v>6373180</v>
+        <v>6373168</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4659,9 +4649,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4676,57 +4676,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128815114</v>
+        <v>128806035</v>
       </c>
       <c r="B42" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>717431</v>
+        <v>717263</v>
       </c>
       <c r="R42" t="n">
-        <v>6373147</v>
+        <v>6373307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4767,63 +4767,64 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128815143</v>
+        <v>128813065</v>
       </c>
       <c r="B43" t="n">
-        <v>90969</v>
+        <v>86990</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3286</v>
+        <v>449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>717335</v>
+        <v>717407</v>
       </c>
       <c r="R43" t="n">
-        <v>6373383</v>
+        <v>6373048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,9 +4854,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4870,57 +4881,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128806035</v>
+        <v>128815140</v>
       </c>
       <c r="B44" t="n">
-        <v>86963</v>
+        <v>86990</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>717263</v>
+        <v>717460</v>
       </c>
       <c r="R44" t="n">
-        <v>6373307</v>
+        <v>6373180</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4961,29 +4972,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128813036</v>
+        <v>128815143</v>
       </c>
       <c r="B45" t="n">
-        <v>86963</v>
+        <v>90974</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,34 +5001,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>717436</v>
+        <v>717335</v>
       </c>
       <c r="R45" t="n">
-        <v>6373168</v>
+        <v>6373383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5048,19 +5058,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5075,44 +5075,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128813067</v>
+        <v>128813046</v>
       </c>
       <c r="B46" t="n">
-        <v>86985</v>
+        <v>86968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717325</v>
+        <v>717216</v>
       </c>
       <c r="R46" t="n">
-        <v>6373229</v>
+        <v>6373176</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5194,32 +5194,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128806053</v>
+        <v>128813040</v>
       </c>
       <c r="B47" t="n">
-        <v>86788</v>
+        <v>86968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717382</v>
+        <v>717487</v>
       </c>
       <c r="R47" t="n">
-        <v>6373309</v>
+        <v>6373202</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5262,9 +5262,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5279,44 +5289,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128806345</v>
+        <v>128813067</v>
       </c>
       <c r="B48" t="n">
-        <v>86926</v>
+        <v>86990</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5326,10 +5336,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717170</v>
+        <v>717325</v>
       </c>
       <c r="R48" t="n">
-        <v>6373195</v>
+        <v>6373229</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5359,9 +5369,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5376,44 +5396,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128813040</v>
+        <v>128806053</v>
       </c>
       <c r="B49" t="n">
-        <v>86963</v>
+        <v>86793</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5423,10 +5443,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>717487</v>
+        <v>717382</v>
       </c>
       <c r="R49" t="n">
-        <v>6373202</v>
+        <v>6373309</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5456,19 +5476,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5483,44 +5493,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128813046</v>
+        <v>128806345</v>
       </c>
       <c r="B50" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5530,10 +5540,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>717216</v>
+        <v>717170</v>
       </c>
       <c r="R50" t="n">
-        <v>6373176</v>
+        <v>6373195</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5563,19 +5573,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5590,57 +5590,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128815141</v>
+        <v>128806069</v>
       </c>
       <c r="B51" t="n">
-        <v>86985</v>
+        <v>86931</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717505</v>
+        <v>717117</v>
       </c>
       <c r="R51" t="n">
-        <v>6373241</v>
+        <v>6373208</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5687,12 +5687,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
         <v>128806334</v>
       </c>
       <c r="B52" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5796,45 +5796,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128815131</v>
+        <v>128806074</v>
       </c>
       <c r="B53" t="n">
-        <v>91044</v>
+        <v>86931</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717416</v>
+        <v>717445</v>
       </c>
       <c r="R53" t="n">
-        <v>6373162</v>
+        <v>6373269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5869,75 +5869,69 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128806069</v>
+        <v>128815131</v>
       </c>
       <c r="B54" t="n">
-        <v>86926</v>
+        <v>91049</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717117</v>
+        <v>717416</v>
       </c>
       <c r="R54" t="n">
-        <v>6373208</v>
+        <v>6373162</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5972,69 +5966,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806074</v>
+        <v>128815141</v>
       </c>
       <c r="B55" t="n">
-        <v>86926</v>
+        <v>86990</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717445</v>
+        <v>717505</v>
       </c>
       <c r="R55" t="n">
-        <v>6373269</v>
+        <v>6373241</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6081,22 +6081,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128806034</v>
+        <v>128813042</v>
       </c>
       <c r="B56" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>717303</v>
+        <v>717084</v>
       </c>
       <c r="R56" t="n">
-        <v>6373236</v>
+        <v>6373295</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6161,40 +6161,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128813042</v>
+        <v>128806034</v>
       </c>
       <c r="B57" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6226,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>717084</v>
+        <v>717303</v>
       </c>
       <c r="R57" t="n">
-        <v>6373295</v>
+        <v>6373236</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6259,39 +6268,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
         <v>128815116</v>
       </c>
       <c r="B58" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>128815152</v>
       </c>
       <c r="B59" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>128806054</v>
       </c>
       <c r="B60" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>128815148</v>
       </c>
       <c r="B61" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>128806322</v>
       </c>
       <c r="B62" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>128806330</v>
       </c>
       <c r="B63" t="n">
-        <v>107550</v>
+        <v>107558</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6881,32 +6881,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128813066</v>
+        <v>128813079</v>
       </c>
       <c r="B64" t="n">
-        <v>86985</v>
+        <v>86931</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717515</v>
+        <v>717315</v>
       </c>
       <c r="R64" t="n">
-        <v>6373166</v>
+        <v>6373221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6988,32 +6988,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128806333</v>
+        <v>128806350</v>
       </c>
       <c r="B65" t="n">
-        <v>86985</v>
+        <v>86931</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717331</v>
+        <v>717330</v>
       </c>
       <c r="R65" t="n">
-        <v>6373327</v>
+        <v>6373328</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7085,32 +7085,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128813079</v>
+        <v>128813012</v>
       </c>
       <c r="B66" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717315</v>
+        <v>717435</v>
       </c>
       <c r="R66" t="n">
-        <v>6373221</v>
+        <v>6373156</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7192,32 +7192,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128806350</v>
+        <v>128813066</v>
       </c>
       <c r="B67" t="n">
-        <v>86926</v>
+        <v>86990</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717330</v>
+        <v>717515</v>
       </c>
       <c r="R67" t="n">
-        <v>6373328</v>
+        <v>6373166</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7260,9 +7260,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7277,22 +7287,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128813012</v>
+        <v>128806333</v>
       </c>
       <c r="B68" t="n">
-        <v>87008</v>
+        <v>86990</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7300,21 +7310,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7334,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717435</v>
+        <v>717331</v>
       </c>
       <c r="R68" t="n">
-        <v>6373156</v>
+        <v>6373327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7357,19 +7367,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7384,12 +7384,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7399,7 +7399,7 @@
         <v>128806326</v>
       </c>
       <c r="B69" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>128806342</v>
       </c>
       <c r="B70" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>128813044</v>
       </c>
       <c r="B71" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>128806036</v>
       </c>
       <c r="B72" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7804,45 +7804,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128806046</v>
+        <v>128806041</v>
       </c>
       <c r="B73" t="n">
-        <v>86985</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>717129</v>
+        <v>717150</v>
       </c>
       <c r="R73" t="n">
-        <v>6373201</v>
+        <v>6373384</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7883,6 +7892,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7904,7 +7914,7 @@
         <v>128813020</v>
       </c>
       <c r="B74" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,54 +8018,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128806041</v>
+        <v>128806046</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>86990</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>717150</v>
+        <v>717129</v>
       </c>
       <c r="R75" t="n">
-        <v>6373384</v>
+        <v>6373201</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,7 +8097,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8115,32 +8115,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128813055</v>
+        <v>128806047</v>
       </c>
       <c r="B76" t="n">
-        <v>98670</v>
+        <v>86990</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219874</v>
+        <v>449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717326</v>
+        <v>717290</v>
       </c>
       <c r="R76" t="n">
-        <v>6373144</v>
+        <v>6373221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8183,19 +8183,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8210,57 +8200,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806026</v>
+        <v>128806316</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>86815</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717211</v>
+        <v>717125</v>
       </c>
       <c r="R77" t="n">
-        <v>6373375</v>
+        <v>6373250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8308,44 +8301,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128806031</v>
+        <v>128813077</v>
       </c>
       <c r="B78" t="n">
-        <v>86963</v>
+        <v>86815</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8355,10 +8348,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717071</v>
+        <v>717116</v>
       </c>
       <c r="R78" t="n">
-        <v>6373294</v>
+        <v>6373207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8388,30 +8381,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8421,7 +8423,7 @@
         <v>128815128</v>
       </c>
       <c r="B79" t="n">
-        <v>91044</v>
+        <v>91049</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8516,32 +8518,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128806001</v>
+        <v>128806026</v>
       </c>
       <c r="B80" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8551,10 +8553,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717159</v>
+        <v>717211</v>
       </c>
       <c r="R80" t="n">
-        <v>6373378</v>
+        <v>6373375</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8595,6 +8597,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8606,52 +8609,52 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128815117</v>
+        <v>128806031</v>
       </c>
       <c r="B81" t="n">
-        <v>87008</v>
+        <v>86968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717416</v>
+        <v>717071</v>
       </c>
       <c r="R81" t="n">
-        <v>6373167</v>
+        <v>6373294</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8692,50 +8695,51 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128806067</v>
+        <v>128806001</v>
       </c>
       <c r="B82" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8745,10 +8749,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717298</v>
+        <v>717159</v>
       </c>
       <c r="R82" t="n">
-        <v>6373345</v>
+        <v>6373378</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8807,10 +8811,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128806047</v>
+        <v>128815117</v>
       </c>
       <c r="B83" t="n">
-        <v>86985</v>
+        <v>87013</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8818,34 +8822,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717290</v>
+        <v>717416</v>
       </c>
       <c r="R83" t="n">
-        <v>6373221</v>
+        <v>6373167</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8892,60 +8896,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128806316</v>
+        <v>128806067</v>
       </c>
       <c r="B84" t="n">
-        <v>86810</v>
+        <v>86931</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>717125</v>
+        <v>717298</v>
       </c>
       <c r="R84" t="n">
-        <v>6373250</v>
+        <v>6373345</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8986,51 +8987,50 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128813077</v>
+        <v>128813055</v>
       </c>
       <c r="B85" t="n">
-        <v>86810</v>
+        <v>98677</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>424</v>
+        <v>219874</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>717116</v>
+        <v>717326</v>
       </c>
       <c r="R85" t="n">
-        <v>6373207</v>
+        <v>6373144</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9115,7 +9115,7 @@
         <v>128815130</v>
       </c>
       <c r="B86" t="n">
-        <v>91044</v>
+        <v>91049</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9210,10 +9210,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128813078</v>
+        <v>128813061</v>
       </c>
       <c r="B87" t="n">
-        <v>86810</v>
+        <v>86884</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9221,21 +9221,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717243</v>
+        <v>717085</v>
       </c>
       <c r="R87" t="n">
-        <v>6373192</v>
+        <v>6373261</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9317,45 +9317,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815156</v>
+        <v>128806318</v>
       </c>
       <c r="B88" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717444</v>
+        <v>717062</v>
       </c>
       <c r="R88" t="n">
-        <v>6373273</v>
+        <v>6373304</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9396,28 +9396,29 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128815120</v>
+        <v>128813078</v>
       </c>
       <c r="B89" t="n">
-        <v>87008</v>
+        <v>86815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9425,34 +9426,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3767</v>
+        <v>424</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717479</v>
+        <v>717243</v>
       </c>
       <c r="R89" t="n">
-        <v>6373226</v>
+        <v>6373192</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9482,9 +9483,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9499,65 +9510,57 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128806007</v>
+        <v>128815156</v>
       </c>
       <c r="B90" t="n">
-        <v>57717</v>
+        <v>86931</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717083</v>
+        <v>717444</v>
       </c>
       <c r="R90" t="n">
-        <v>6373260</v>
+        <v>6373273</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9604,22 +9607,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128813061</v>
+        <v>128815120</v>
       </c>
       <c r="B91" t="n">
-        <v>86879</v>
+        <v>87013</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9627,34 +9630,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717085</v>
+        <v>717479</v>
       </c>
       <c r="R91" t="n">
-        <v>6373261</v>
+        <v>6373226</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9684,19 +9687,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9711,22 +9704,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128806318</v>
+        <v>128806007</v>
       </c>
       <c r="B92" t="n">
-        <v>86963</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9734,34 +9727,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717062</v>
+        <v>717083</v>
       </c>
       <c r="R92" t="n">
-        <v>6373304</v>
+        <v>6373260</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9802,19 +9803,18 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
         <v>128813069</v>
       </c>
       <c r="B93" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9928,41 +9928,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128813074</v>
+        <v>128815109</v>
       </c>
       <c r="B94" t="n">
-        <v>87020</v>
+        <v>86911</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717185</v>
+        <v>717314</v>
       </c>
       <c r="R94" t="n">
-        <v>6373128</v>
+        <v>6373229</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9992,24 +9996,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10024,57 +10013,53 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815109</v>
+        <v>128813074</v>
       </c>
       <c r="B95" t="n">
-        <v>86906</v>
+        <v>87025</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bon</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717314</v>
+        <v>717185</v>
       </c>
       <c r="R95" t="n">
-        <v>6373229</v>
+        <v>6373128</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10104,9 +10089,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10121,12 +10121,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10136,7 +10136,7 @@
         <v>128815112</v>
       </c>
       <c r="B96" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>128806071</v>
       </c>
       <c r="B97" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>128815123</v>
       </c>
       <c r="B98" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>128815118</v>
       </c>
       <c r="B99" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>128813076</v>
       </c>
       <c r="B100" t="n">
-        <v>90275</v>
+        <v>90280</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128813052</v>
+        <v>128815137</v>
       </c>
       <c r="B101" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10663,14 +10663,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717411</v>
+        <v>717433</v>
       </c>
       <c r="R101" t="n">
-        <v>6373077</v>
+        <v>6373170</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10700,49 +10700,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128815137</v>
+        <v>128813052</v>
       </c>
       <c r="B102" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10770,14 +10761,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717433</v>
+        <v>717411</v>
       </c>
       <c r="R102" t="n">
-        <v>6373170</v>
+        <v>6373077</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10807,62 +10798,71 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128815129</v>
+        <v>128815149</v>
       </c>
       <c r="B103" t="n">
-        <v>91044</v>
+        <v>86931</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>717424</v>
+        <v>717269</v>
       </c>
       <c r="R103" t="n">
-        <v>6373165</v>
+        <v>6373207</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10934,32 +10934,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128815151</v>
+        <v>128815110</v>
       </c>
       <c r="B104" t="n">
-        <v>86926</v>
+        <v>87013</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>717270</v>
+        <v>717281</v>
       </c>
       <c r="R104" t="n">
-        <v>6373304</v>
+        <v>6373300</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11031,32 +11031,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815149</v>
+        <v>128815129</v>
       </c>
       <c r="B105" t="n">
-        <v>86926</v>
+        <v>91049</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717269</v>
+        <v>717424</v>
       </c>
       <c r="R105" t="n">
-        <v>6373207</v>
+        <v>6373165</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11128,45 +11128,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128815110</v>
+        <v>128813073</v>
       </c>
       <c r="B106" t="n">
-        <v>87008</v>
+        <v>92839</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3767</v>
+        <v>5964</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717281</v>
+        <v>717453</v>
       </c>
       <c r="R106" t="n">
-        <v>6373300</v>
+        <v>6373125</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11196,39 +11199,50 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128813073</v>
+        <v>128815151</v>
       </c>
       <c r="B107" t="n">
-        <v>92834</v>
+        <v>86931</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11236,37 +11250,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717453</v>
+        <v>717270</v>
       </c>
       <c r="R107" t="n">
-        <v>6373125</v>
+        <v>6373304</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11296,50 +11307,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806320</v>
+        <v>128806323</v>
       </c>
       <c r="B108" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717131</v>
+        <v>717241</v>
       </c>
       <c r="R108" t="n">
-        <v>6373249</v>
+        <v>6373264</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11437,7 +11437,7 @@
         <v>128806028</v>
       </c>
       <c r="B109" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11532,10 +11532,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806323</v>
+        <v>128806320</v>
       </c>
       <c r="B110" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717241</v>
+        <v>717131</v>
       </c>
       <c r="R110" t="n">
-        <v>6373264</v>
+        <v>6373249</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11630,45 +11630,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813568</v>
+        <v>128815121</v>
       </c>
       <c r="B111" t="n">
-        <v>86906</v>
+        <v>87013</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717322</v>
+        <v>717499</v>
       </c>
       <c r="R111" t="n">
-        <v>6373203</v>
+        <v>6373239</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,19 +11698,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11725,22 +11715,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128815121</v>
+        <v>128806313</v>
       </c>
       <c r="B112" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11768,14 +11758,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717499</v>
+        <v>717369</v>
       </c>
       <c r="R112" t="n">
-        <v>6373239</v>
+        <v>6373319</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11822,22 +11812,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806313</v>
+        <v>128813063</v>
       </c>
       <c r="B113" t="n">
-        <v>87008</v>
+        <v>92267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11845,21 +11835,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>232138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11869,10 +11859,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717369</v>
+        <v>717511</v>
       </c>
       <c r="R113" t="n">
-        <v>6373319</v>
+        <v>6373145</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11902,9 +11892,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11919,12 +11919,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -11934,7 +11934,7 @@
         <v>128806055</v>
       </c>
       <c r="B114" t="n">
-        <v>86717</v>
+        <v>86722</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12037,45 +12037,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815139</v>
+        <v>128813048</v>
       </c>
       <c r="B115" t="n">
-        <v>86879</v>
+        <v>86968</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717313</v>
+        <v>717248</v>
       </c>
       <c r="R115" t="n">
-        <v>6373361</v>
+        <v>6373196</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12105,9 +12105,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12122,57 +12132,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128813048</v>
+        <v>128815139</v>
       </c>
       <c r="B116" t="n">
-        <v>86963</v>
+        <v>86884</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717248</v>
+        <v>717313</v>
       </c>
       <c r="R116" t="n">
-        <v>6373196</v>
+        <v>6373361</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12202,19 +12212,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12229,44 +12229,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128813063</v>
+        <v>128813568</v>
       </c>
       <c r="B117" t="n">
-        <v>92262</v>
+        <v>86911</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>232138</v>
+        <v>473</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717511</v>
+        <v>717322</v>
       </c>
       <c r="R117" t="n">
-        <v>6373145</v>
+        <v>6373203</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12351,7 +12351,7 @@
         <v>128806315</v>
       </c>
       <c r="B118" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128806312</v>
+        <v>128813014</v>
       </c>
       <c r="B119" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>717332</v>
+        <v>717462</v>
       </c>
       <c r="R119" t="n">
-        <v>6373350</v>
+        <v>6373231</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12513,9 +12513,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12530,57 +12540,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128815111</v>
+        <v>128806340</v>
       </c>
       <c r="B120" t="n">
-        <v>87008</v>
+        <v>86793</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717318</v>
+        <v>717314</v>
       </c>
       <c r="R120" t="n">
-        <v>6373242</v>
+        <v>6373345</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12627,22 +12637,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128806347</v>
+        <v>128813030</v>
       </c>
       <c r="B121" t="n">
-        <v>86926</v>
+        <v>86944</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12650,21 +12660,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12674,10 +12684,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717092</v>
+        <v>717079</v>
       </c>
       <c r="R121" t="n">
-        <v>6373322</v>
+        <v>6373300</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12707,9 +12717,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12724,44 +12744,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128813014</v>
+        <v>128806331</v>
       </c>
       <c r="B122" t="n">
-        <v>87008</v>
+        <v>90349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3767</v>
+        <v>6292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12771,10 +12791,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717462</v>
+        <v>717106</v>
       </c>
       <c r="R122" t="n">
-        <v>6373231</v>
+        <v>6373238</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12804,19 +12824,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12831,44 +12841,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128806340</v>
+        <v>128806032</v>
       </c>
       <c r="B123" t="n">
-        <v>86788</v>
+        <v>86968</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12878,10 +12888,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717314</v>
+        <v>717081</v>
       </c>
       <c r="R123" t="n">
-        <v>6373345</v>
+        <v>6373276</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12922,28 +12932,29 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806331</v>
+        <v>128813056</v>
       </c>
       <c r="B124" t="n">
-        <v>90344</v>
+        <v>98677</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12951,21 +12962,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6292</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12975,10 +12986,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717106</v>
+        <v>717484</v>
       </c>
       <c r="R124" t="n">
-        <v>6373238</v>
+        <v>6373174</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13008,9 +13019,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13025,44 +13046,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128813030</v>
+        <v>128806312</v>
       </c>
       <c r="B125" t="n">
-        <v>86939</v>
+        <v>87013</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1988</v>
+        <v>3767</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13072,10 +13093,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717079</v>
+        <v>717332</v>
       </c>
       <c r="R125" t="n">
-        <v>6373300</v>
+        <v>6373350</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13105,19 +13126,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13132,57 +13143,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128813056</v>
+        <v>128815111</v>
       </c>
       <c r="B126" t="n">
-        <v>98670</v>
+        <v>87013</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717484</v>
+        <v>717318</v>
       </c>
       <c r="R126" t="n">
-        <v>6373174</v>
+        <v>6373242</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13212,19 +13223,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>09:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13239,44 +13240,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806032</v>
+        <v>128806347</v>
       </c>
       <c r="B127" t="n">
-        <v>86963</v>
+        <v>86931</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13286,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717081</v>
+        <v>717092</v>
       </c>
       <c r="R127" t="n">
-        <v>6373276</v>
+        <v>6373322</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13330,29 +13331,28 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128813075</v>
+        <v>128815115</v>
       </c>
       <c r="B128" t="n">
-        <v>86879</v>
+        <v>87013</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13360,37 +13360,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717344</v>
+        <v>717424</v>
       </c>
       <c r="R128" t="n">
-        <v>6373206</v>
+        <v>6373147</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13420,79 +13417,59 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128815115</v>
+        <v>128815126</v>
       </c>
       <c r="B129" t="n">
-        <v>87008</v>
+        <v>87034</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3767</v>
+        <v>3624</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13500,10 +13477,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717424</v>
+        <v>717337</v>
       </c>
       <c r="R129" t="n">
-        <v>6373147</v>
+        <v>6373382</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13562,10 +13539,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128815126</v>
+        <v>128813080</v>
       </c>
       <c r="B130" t="n">
-        <v>87029</v>
+        <v>86931</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13573,30 +13550,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3624</v>
+        <v>3674</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717337</v>
+        <v>717456</v>
       </c>
       <c r="R130" t="n">
-        <v>6373382</v>
+        <v>6373273</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13626,9 +13607,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13643,22 +13634,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813080</v>
+        <v>128813018</v>
       </c>
       <c r="B131" t="n">
-        <v>86926</v>
+        <v>110771</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13666,21 +13657,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3674</v>
+        <v>219711</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13690,10 +13681,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717456</v>
+        <v>717512</v>
       </c>
       <c r="R131" t="n">
-        <v>6373273</v>
+        <v>6373149</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13725,7 +13716,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13735,7 +13726,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13762,32 +13753,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813018</v>
+        <v>128813049</v>
       </c>
       <c r="B132" t="n">
-        <v>110763</v>
+        <v>86968</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13797,10 +13788,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717512</v>
+        <v>717330</v>
       </c>
       <c r="R132" t="n">
-        <v>6373149</v>
+        <v>6373178</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13832,7 +13823,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13842,7 +13833,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13869,45 +13860,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813049</v>
+        <v>128813075</v>
       </c>
       <c r="B133" t="n">
-        <v>86963</v>
+        <v>86884</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717330</v>
+        <v>717344</v>
       </c>
       <c r="R133" t="n">
-        <v>6373178</v>
+        <v>6373206</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13939,7 +13933,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -13949,7 +13943,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13958,6 +13957,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>128813027</v>
       </c>
       <c r="B134" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14083,45 +14083,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128815155</v>
+        <v>128806319</v>
       </c>
       <c r="B135" t="n">
-        <v>86926</v>
+        <v>86968</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717498</v>
+        <v>717087</v>
       </c>
       <c r="R135" t="n">
-        <v>6373233</v>
+        <v>6373291</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14162,63 +14162,64 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128806000</v>
+        <v>128815155</v>
       </c>
       <c r="B136" t="n">
-        <v>87008</v>
+        <v>86931</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717298</v>
+        <v>717498</v>
       </c>
       <c r="R136" t="n">
-        <v>6373343</v>
+        <v>6373233</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14265,57 +14266,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128815133</v>
+        <v>128806000</v>
       </c>
       <c r="B137" t="n">
-        <v>86764</v>
+        <v>87013</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717314</v>
+        <v>717298</v>
       </c>
       <c r="R137" t="n">
-        <v>6373361</v>
+        <v>6373343</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14362,57 +14363,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806319</v>
+        <v>128815133</v>
       </c>
       <c r="B138" t="n">
-        <v>86963</v>
+        <v>86769</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717087</v>
+        <v>717314</v>
       </c>
       <c r="R138" t="n">
-        <v>6373291</v>
+        <v>6373361</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14453,19 +14454,18 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14475,7 +14475,7 @@
         <v>128806066</v>
       </c>
       <c r="B139" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>128806070</v>
       </c>
       <c r="B140" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>128806008</v>
       </c>
       <c r="B141" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>128813081</v>
       </c>
       <c r="B142" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>128815147</v>
       </c>
       <c r="B143" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>128815124</v>
       </c>
       <c r="B144" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>128815150</v>
       </c>
       <c r="B145" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128813064</v>
       </c>
       <c r="B146" t="n">
-        <v>91506</v>
+        <v>91511</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128815136</v>
+        <v>128813071</v>
       </c>
       <c r="B2" t="n">
-        <v>86975</v>
+        <v>86997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717412</v>
+        <v>717455</v>
       </c>
       <c r="R2" t="n">
-        <v>6373217</v>
+        <v>6373115</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,75 +743,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128806033</v>
+        <v>128815135</v>
       </c>
       <c r="B3" t="n">
-        <v>86975</v>
+        <v>86776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717315</v>
+        <v>717476</v>
       </c>
       <c r="R3" t="n">
-        <v>6373232</v>
+        <v>6373242</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,51 +861,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128813034</v>
+        <v>128806348</v>
       </c>
       <c r="B4" t="n">
-        <v>86975</v>
+        <v>86938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -906,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717425</v>
+        <v>717239</v>
       </c>
       <c r="R4" t="n">
-        <v>6373083</v>
+        <v>6373234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,19 +947,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128815135</v>
+        <v>128806072</v>
       </c>
       <c r="B5" t="n">
-        <v>86776</v>
+        <v>86938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717476</v>
+        <v>717289</v>
       </c>
       <c r="R5" t="n">
-        <v>6373242</v>
+        <v>6373288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,44 +1061,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128806348</v>
+        <v>128805999</v>
       </c>
       <c r="B6" t="n">
-        <v>86938</v>
+        <v>87020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717239</v>
+        <v>717287</v>
       </c>
       <c r="R6" t="n">
-        <v>6373234</v>
+        <v>6373354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128806072</v>
+        <v>128806048</v>
       </c>
       <c r="B7" t="n">
-        <v>86938</v>
+        <v>90942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717289</v>
+        <v>717322</v>
       </c>
       <c r="R7" t="n">
-        <v>6373288</v>
+        <v>6373213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128805999</v>
+        <v>128815113</v>
       </c>
       <c r="B8" t="n">
         <v>87020</v>
@@ -1300,14 +1298,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717287</v>
+        <v>717317</v>
       </c>
       <c r="R8" t="n">
-        <v>6373354</v>
+        <v>6373308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128806048</v>
+        <v>128813022</v>
       </c>
       <c r="B9" t="n">
-        <v>90942</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4188</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1401,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717322</v>
+        <v>717130</v>
       </c>
       <c r="R9" t="n">
-        <v>6373213</v>
+        <v>6373194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,9 +1432,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,57 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128815113</v>
+        <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>87020</v>
+        <v>92456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717317</v>
+        <v>717370</v>
       </c>
       <c r="R10" t="n">
-        <v>6373308</v>
+        <v>6373322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,57 +1556,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128813022</v>
+        <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>92823</v>
+        <v>86975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717130</v>
+        <v>717412</v>
       </c>
       <c r="R11" t="n">
-        <v>6373194</v>
+        <v>6373217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1628,71 +1636,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128806006</v>
+        <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>86975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717370</v>
+        <v>717315</v>
       </c>
       <c r="R12" t="n">
-        <v>6373322</v>
+        <v>6373232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1745,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1757,39 +1757,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128813071</v>
+        <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86997</v>
+        <v>86975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717455</v>
+        <v>717425</v>
       </c>
       <c r="R13" t="n">
-        <v>6373115</v>
+        <v>6373083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1871,45 +1871,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128805997</v>
+        <v>128815145</v>
       </c>
       <c r="B14" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>6037417</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717416</v>
+        <v>717299</v>
       </c>
       <c r="R14" t="n">
-        <v>6373282</v>
+        <v>6373241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,50 +1950,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128806003</v>
+        <v>128813050</v>
       </c>
       <c r="B15" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717431</v>
+        <v>717330</v>
       </c>
       <c r="R15" t="n">
-        <v>6373255</v>
+        <v>6373140</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,9 +2037,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,22 +2064,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815145</v>
+        <v>128813054</v>
       </c>
       <c r="B16" t="n">
-        <v>86941</v>
+        <v>86975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,34 +2087,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717299</v>
+        <v>717402</v>
       </c>
       <c r="R16" t="n">
-        <v>6373241</v>
+        <v>6373098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,40 +2144,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128813050</v>
+        <v>128806343</v>
       </c>
       <c r="B17" t="n">
-        <v>86975</v>
+        <v>86729</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,34 +2194,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717330</v>
+        <v>717258</v>
       </c>
       <c r="R17" t="n">
-        <v>6373140</v>
+        <v>6373299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,19 +2254,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:06</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,63 +2270,64 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128813054</v>
+        <v>128815153</v>
       </c>
       <c r="B18" t="n">
-        <v>86975</v>
+        <v>86938</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717402</v>
+        <v>717341</v>
       </c>
       <c r="R18" t="n">
-        <v>6373098</v>
+        <v>6373251</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,19 +2357,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2365,57 +2374,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128815153</v>
+        <v>128805997</v>
       </c>
       <c r="B19" t="n">
-        <v>86938</v>
+        <v>87020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717341</v>
+        <v>717416</v>
       </c>
       <c r="R19" t="n">
-        <v>6373251</v>
+        <v>6373282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,60 +2471,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128806343</v>
+        <v>128806003</v>
       </c>
       <c r="B20" t="n">
-        <v>86729</v>
+        <v>87020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>249278</v>
+        <v>3767</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717258</v>
+        <v>717431</v>
       </c>
       <c r="R20" t="n">
-        <v>6373299</v>
+        <v>6373255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,30 +2556,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3175,45 +3175,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128815122</v>
+        <v>128813028</v>
       </c>
       <c r="B27" t="n">
-        <v>87020</v>
+        <v>91029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717534</v>
+        <v>717490</v>
       </c>
       <c r="R27" t="n">
-        <v>6373182</v>
+        <v>6373178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3243,9 +3243,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3260,57 +3270,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128805998</v>
+        <v>128806042</v>
       </c>
       <c r="B28" t="n">
-        <v>87020</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3767</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717299</v>
+        <v>717134</v>
       </c>
       <c r="R28" t="n">
-        <v>6373359</v>
+        <v>6373159</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3351,6 +3370,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3369,54 +3389,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128806042</v>
+        <v>128815122</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>87020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>3767</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717134</v>
+        <v>717534</v>
       </c>
       <c r="R29" t="n">
-        <v>6373159</v>
+        <v>6373182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,51 +3468,50 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128813051</v>
+        <v>128805998</v>
       </c>
       <c r="B30" t="n">
-        <v>86975</v>
+        <v>87020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3511,10 +3521,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717385</v>
+        <v>717299</v>
       </c>
       <c r="R30" t="n">
-        <v>6373091</v>
+        <v>6373359</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3544,19 +3554,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3571,44 +3571,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128813028</v>
+        <v>128813051</v>
       </c>
       <c r="B31" t="n">
-        <v>91029</v>
+        <v>86975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5741</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717490</v>
+        <v>717385</v>
       </c>
       <c r="R31" t="n">
-        <v>6373178</v>
+        <v>6373091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6881,32 +6881,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128813044</v>
+        <v>128813079</v>
       </c>
       <c r="B64" t="n">
-        <v>86975</v>
+        <v>86938</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717135</v>
+        <v>717315</v>
       </c>
       <c r="R64" t="n">
-        <v>6373174</v>
+        <v>6373221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6988,32 +6988,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128806036</v>
+        <v>128806350</v>
       </c>
       <c r="B65" t="n">
-        <v>86975</v>
+        <v>86938</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717449</v>
+        <v>717330</v>
       </c>
       <c r="R65" t="n">
-        <v>6373281</v>
+        <v>6373328</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7067,67 +7067,63 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128806342</v>
+        <v>128806326</v>
       </c>
       <c r="B66" t="n">
-        <v>86729</v>
+        <v>86951</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>249278</v>
+        <v>1988</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>717179</v>
+        <v>717084</v>
       </c>
       <c r="R66" t="n">
-        <v>6373227</v>
+        <v>6373294</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7162,18 +7158,12 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7192,32 +7182,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813079</v>
+        <v>128813012</v>
       </c>
       <c r="B67" t="n">
-        <v>86938</v>
+        <v>87020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7227,10 +7217,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717315</v>
+        <v>717435</v>
       </c>
       <c r="R67" t="n">
-        <v>6373221</v>
+        <v>6373156</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7262,7 +7252,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7272,7 +7262,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7299,32 +7289,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128806350</v>
+        <v>128813066</v>
       </c>
       <c r="B68" t="n">
-        <v>86938</v>
+        <v>86997</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7334,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717330</v>
+        <v>717515</v>
       </c>
       <c r="R68" t="n">
-        <v>6373328</v>
+        <v>6373166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7367,9 +7357,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7384,44 +7384,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128806326</v>
+        <v>128806333</v>
       </c>
       <c r="B69" t="n">
-        <v>86951</v>
+        <v>86997</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1988</v>
+        <v>449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717084</v>
+        <v>717331</v>
       </c>
       <c r="R69" t="n">
-        <v>6373294</v>
+        <v>6373327</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,32 +7493,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128813012</v>
+        <v>128813044</v>
       </c>
       <c r="B70" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717435</v>
+        <v>717135</v>
       </c>
       <c r="R70" t="n">
-        <v>6373156</v>
+        <v>6373174</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7600,32 +7600,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128813066</v>
+        <v>128806036</v>
       </c>
       <c r="B71" t="n">
-        <v>86997</v>
+        <v>86975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717515</v>
+        <v>717449</v>
       </c>
       <c r="R71" t="n">
-        <v>6373166</v>
+        <v>6373281</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7668,84 +7668,78 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806333</v>
+        <v>128806342</v>
       </c>
       <c r="B72" t="n">
-        <v>86997</v>
+        <v>86729</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>449</v>
+        <v>249278</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717331</v>
+        <v>717179</v>
       </c>
       <c r="R72" t="n">
-        <v>6373327</v>
+        <v>6373227</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,12 +7774,18 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8115,10 +8115,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128806047</v>
+        <v>128815128</v>
       </c>
       <c r="B76" t="n">
-        <v>86997</v>
+        <v>91056</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8126,34 +8126,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717290</v>
+        <v>717418</v>
       </c>
       <c r="R76" t="n">
-        <v>6373221</v>
+        <v>6373171</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8194,28 +8194,29 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806316</v>
+        <v>128806047</v>
       </c>
       <c r="B77" t="n">
-        <v>86822</v>
+        <v>86997</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,37 +8224,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717125</v>
+        <v>717290</v>
       </c>
       <c r="R77" t="n">
-        <v>6373250</v>
+        <v>6373221</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,26 +8292,25 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128813077</v>
+        <v>128806316</v>
       </c>
       <c r="B78" t="n">
         <v>86822</v>
@@ -8342,16 +8339,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717116</v>
+        <v>717125</v>
       </c>
       <c r="R78" t="n">
-        <v>6373207</v>
+        <v>6373250</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8381,49 +8381,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128815128</v>
+        <v>128813077</v>
       </c>
       <c r="B79" t="n">
-        <v>91056</v>
+        <v>86822</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8431,34 +8422,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1357</v>
+        <v>424</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717418</v>
+        <v>717116</v>
       </c>
       <c r="R79" t="n">
-        <v>6373171</v>
+        <v>6373207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8488,40 +8479,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128806067</v>
+        <v>128813055</v>
       </c>
       <c r="B80" t="n">
-        <v>86938</v>
+        <v>98685</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717298</v>
+        <v>717326</v>
       </c>
       <c r="R80" t="n">
-        <v>6373345</v>
+        <v>6373144</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8586,9 +8586,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8603,44 +8613,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128806001</v>
+        <v>128806067</v>
       </c>
       <c r="B81" t="n">
-        <v>87020</v>
+        <v>86938</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8650,10 +8660,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717159</v>
+        <v>717298</v>
       </c>
       <c r="R81" t="n">
-        <v>6373378</v>
+        <v>6373345</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8712,7 +8722,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128815117</v>
+        <v>128806001</v>
       </c>
       <c r="B82" t="n">
         <v>87020</v>
@@ -8743,14 +8753,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717416</v>
+        <v>717159</v>
       </c>
       <c r="R82" t="n">
-        <v>6373167</v>
+        <v>6373378</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8797,57 +8807,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128813055</v>
+        <v>128815117</v>
       </c>
       <c r="B83" t="n">
-        <v>98685</v>
+        <v>87020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219874</v>
+        <v>3767</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717326</v>
+        <v>717416</v>
       </c>
       <c r="R83" t="n">
-        <v>6373144</v>
+        <v>6373167</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8877,19 +8887,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8904,12 +8904,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128806007</v>
+        <v>128806318</v>
       </c>
       <c r="B86" t="n">
-        <v>57720</v>
+        <v>86975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9123,42 +9123,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717083</v>
+        <v>717062</v>
       </c>
       <c r="R86" t="n">
-        <v>6373260</v>
+        <v>6373304</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9199,63 +9191,64 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128806318</v>
+        <v>128815130</v>
       </c>
       <c r="B87" t="n">
-        <v>86975</v>
+        <v>91056</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717062</v>
+        <v>717326</v>
       </c>
       <c r="R87" t="n">
-        <v>6373304</v>
+        <v>6373267</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9303,57 +9296,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128815156</v>
+        <v>128813078</v>
       </c>
       <c r="B88" t="n">
-        <v>86938</v>
+        <v>86822</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717444</v>
+        <v>717243</v>
       </c>
       <c r="R88" t="n">
-        <v>6373273</v>
+        <v>6373192</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9383,9 +9376,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9400,57 +9403,65 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128813061</v>
+        <v>128806007</v>
       </c>
       <c r="B89" t="n">
-        <v>86891</v>
+        <v>57720</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>248956</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717085</v>
+        <v>717083</v>
       </c>
       <c r="R89" t="n">
-        <v>6373261</v>
+        <v>6373260</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9480,19 +9491,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9507,44 +9508,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128815130</v>
+        <v>128815156</v>
       </c>
       <c r="B90" t="n">
-        <v>91056</v>
+        <v>86938</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9554,10 +9555,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717326</v>
+        <v>717444</v>
       </c>
       <c r="R90" t="n">
-        <v>6373267</v>
+        <v>6373273</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9598,7 +9599,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9714,10 +9714,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128813078</v>
+        <v>128813061</v>
       </c>
       <c r="B92" t="n">
-        <v>86822</v>
+        <v>86891</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9725,21 +9725,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717243</v>
+        <v>717085</v>
       </c>
       <c r="R92" t="n">
-        <v>6373192</v>
+        <v>6373261</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9821,32 +9821,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128813069</v>
+        <v>128806071</v>
       </c>
       <c r="B93" t="n">
-        <v>86997</v>
+        <v>86938</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717134</v>
+        <v>717287</v>
       </c>
       <c r="R93" t="n">
-        <v>6373192</v>
+        <v>6373292</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9889,19 +9889,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9916,22 +9906,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128813074</v>
+        <v>128815112</v>
       </c>
       <c r="B94" t="n">
-        <v>87032</v>
+        <v>87020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9939,30 +9929,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>433</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717185</v>
+        <v>717270</v>
       </c>
       <c r="R94" t="n">
-        <v>6373128</v>
+        <v>6373304</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9992,24 +9986,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10024,44 +10003,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815109</v>
+        <v>128815123</v>
       </c>
       <c r="B95" t="n">
-        <v>86918</v>
+        <v>87020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10071,10 +10050,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717314</v>
+        <v>717500</v>
       </c>
       <c r="R95" t="n">
-        <v>6373229</v>
+        <v>6373237</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10133,45 +10112,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128806071</v>
+        <v>128815118</v>
       </c>
       <c r="B96" t="n">
-        <v>86938</v>
+        <v>87020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717287</v>
+        <v>717431</v>
       </c>
       <c r="R96" t="n">
-        <v>6373292</v>
+        <v>6373173</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10218,44 +10197,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128815112</v>
+        <v>128815137</v>
       </c>
       <c r="B97" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10265,10 +10244,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717270</v>
+        <v>717433</v>
       </c>
       <c r="R97" t="n">
-        <v>6373304</v>
+        <v>6373170</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10309,6 +10288,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10327,45 +10307,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128815123</v>
+        <v>128813052</v>
       </c>
       <c r="B98" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717500</v>
+        <v>717411</v>
       </c>
       <c r="R98" t="n">
-        <v>6373237</v>
+        <v>6373077</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10395,9 +10375,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10412,57 +10402,60 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128815118</v>
+        <v>128813076</v>
       </c>
       <c r="B99" t="n">
-        <v>87020</v>
+        <v>90287</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>245042</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717431</v>
+        <v>717322</v>
       </c>
       <c r="R99" t="n">
-        <v>6373173</v>
+        <v>6373147</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,74 +10485,85 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128815137</v>
+        <v>128813069</v>
       </c>
       <c r="B100" t="n">
-        <v>86975</v>
+        <v>86997</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717433</v>
+        <v>717134</v>
       </c>
       <c r="R100" t="n">
-        <v>6373170</v>
+        <v>6373192</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10589,64 +10593,69 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128813052</v>
+        <v>128813074</v>
       </c>
       <c r="B101" t="n">
-        <v>86975</v>
+        <v>87032</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10654,10 +10663,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717411</v>
+        <v>717185</v>
       </c>
       <c r="R101" t="n">
-        <v>6373077</v>
+        <v>6373128</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10689,7 +10698,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10699,7 +10708,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10726,48 +10740,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128813076</v>
+        <v>128815109</v>
       </c>
       <c r="B102" t="n">
-        <v>90287</v>
+        <v>86918</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>245042</v>
+        <v>473</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717322</v>
+        <v>717314</v>
       </c>
       <c r="R102" t="n">
-        <v>6373147</v>
+        <v>6373229</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10797,40 +10808,29 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11225,45 +11225,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128806323</v>
+        <v>128813073</v>
       </c>
       <c r="B107" t="n">
-        <v>86975</v>
+        <v>92847</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717241</v>
+        <v>717453</v>
       </c>
       <c r="R107" t="n">
-        <v>6373264</v>
+        <v>6373125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11293,9 +11296,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11311,19 +11324,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806028</v>
+        <v>128806323</v>
       </c>
       <c r="B108" t="n">
         <v>86975</v>
@@ -11358,10 +11371,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717179</v>
+        <v>717241</v>
       </c>
       <c r="R108" t="n">
-        <v>6373374</v>
+        <v>6373264</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11409,19 +11422,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806320</v>
+        <v>128806028</v>
       </c>
       <c r="B109" t="n">
         <v>86975</v>
@@ -11456,10 +11469,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717131</v>
+        <v>717179</v>
       </c>
       <c r="R109" t="n">
-        <v>6373249</v>
+        <v>6373374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11507,60 +11520,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128813073</v>
+        <v>128806320</v>
       </c>
       <c r="B110" t="n">
-        <v>92847</v>
+        <v>86975</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717453</v>
+        <v>717131</v>
       </c>
       <c r="R110" t="n">
-        <v>6373125</v>
+        <v>6373249</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11590,19 +11600,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,22 +11618,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128813063</v>
+        <v>128815121</v>
       </c>
       <c r="B111" t="n">
-        <v>92275</v>
+        <v>87020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11641,34 +11641,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>232138</v>
+        <v>3767</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717511</v>
+        <v>717499</v>
       </c>
       <c r="R111" t="n">
-        <v>6373145</v>
+        <v>6373239</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,19 +11698,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11725,44 +11715,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128813048</v>
+        <v>128806313</v>
       </c>
       <c r="B112" t="n">
-        <v>86975</v>
+        <v>87020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11772,10 +11762,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717248</v>
+        <v>717369</v>
       </c>
       <c r="R112" t="n">
-        <v>6373196</v>
+        <v>6373319</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11805,19 +11795,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11832,22 +11812,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128806055</v>
+        <v>128813568</v>
       </c>
       <c r="B113" t="n">
-        <v>86729</v>
+        <v>86918</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11855,37 +11835,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>249278</v>
+        <v>473</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717283</v>
+        <v>717322</v>
       </c>
       <c r="R113" t="n">
-        <v>6373299</v>
+        <v>6373203</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11915,14 +11892,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11931,64 +11913,66 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128815139</v>
+        <v>128806055</v>
       </c>
       <c r="B114" t="n">
-        <v>86891</v>
+        <v>86729</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717313</v>
+        <v>717283</v>
       </c>
       <c r="R114" t="n">
-        <v>6373361</v>
+        <v>6373299</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12023,34 +12007,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815121</v>
+        <v>128815139</v>
       </c>
       <c r="B115" t="n">
-        <v>87020</v>
+        <v>86891</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12058,21 +12048,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12082,10 +12072,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717499</v>
+        <v>717313</v>
       </c>
       <c r="R115" t="n">
-        <v>6373239</v>
+        <v>6373361</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12144,10 +12134,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128806313</v>
+        <v>128813063</v>
       </c>
       <c r="B116" t="n">
-        <v>87020</v>
+        <v>92275</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12155,21 +12145,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3767</v>
+        <v>232138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12179,10 +12169,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717369</v>
+        <v>717511</v>
       </c>
       <c r="R116" t="n">
-        <v>6373319</v>
+        <v>6373145</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12212,9 +12202,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12229,22 +12229,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128813568</v>
+        <v>128813048</v>
       </c>
       <c r="B117" t="n">
-        <v>86918</v>
+        <v>86975</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12252,21 +12252,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>717322</v>
+        <v>717248</v>
       </c>
       <c r="R117" t="n">
-        <v>6373203</v>
+        <v>6373196</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13442,10 +13442,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128813080</v>
+        <v>128813018</v>
       </c>
       <c r="B129" t="n">
-        <v>86938</v>
+        <v>110779</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13453,21 +13453,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3674</v>
+        <v>219711</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13477,10 +13477,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717456</v>
+        <v>717512</v>
       </c>
       <c r="R129" t="n">
-        <v>6373273</v>
+        <v>6373149</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13549,45 +13549,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128815115</v>
+        <v>128813049</v>
       </c>
       <c r="B130" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717424</v>
+        <v>717330</v>
       </c>
       <c r="R130" t="n">
-        <v>6373147</v>
+        <v>6373178</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13617,9 +13617,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13634,57 +13644,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813049</v>
+        <v>128813075</v>
       </c>
       <c r="B131" t="n">
-        <v>86975</v>
+        <v>86891</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717330</v>
+        <v>717344</v>
       </c>
       <c r="R131" t="n">
-        <v>6373178</v>
+        <v>6373206</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13716,7 +13729,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13726,7 +13739,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13735,6 +13753,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13753,10 +13772,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813018</v>
+        <v>128813080</v>
       </c>
       <c r="B132" t="n">
-        <v>110779</v>
+        <v>86938</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13764,21 +13783,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219711</v>
+        <v>3674</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13788,10 +13807,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717512</v>
+        <v>717456</v>
       </c>
       <c r="R132" t="n">
-        <v>6373149</v>
+        <v>6373273</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13823,7 +13842,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -13833,7 +13852,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13860,10 +13879,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128813075</v>
+        <v>128815115</v>
       </c>
       <c r="B133" t="n">
-        <v>86891</v>
+        <v>87020</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13871,37 +13890,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>248956</v>
+        <v>3767</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717344</v>
+        <v>717424</v>
       </c>
       <c r="R133" t="n">
-        <v>6373206</v>
+        <v>6373147</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13931,45 +13947,29 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14073,10 +14073,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128813027</v>
+        <v>128815133</v>
       </c>
       <c r="B135" t="n">
-        <v>91029</v>
+        <v>86776</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14084,34 +14084,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5741</v>
+        <v>3762</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717343</v>
+        <v>717314</v>
       </c>
       <c r="R135" t="n">
-        <v>6373129</v>
+        <v>6373361</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14141,19 +14141,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>10:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14168,44 +14158,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128806319</v>
+        <v>128813027</v>
       </c>
       <c r="B136" t="n">
-        <v>86975</v>
+        <v>91029</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6003295</v>
+        <v>5741</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14215,10 +14205,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>717087</v>
+        <v>717343</v>
       </c>
       <c r="R136" t="n">
-        <v>6373291</v>
+        <v>6373129</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14248,75 +14238,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128815133</v>
+        <v>128806000</v>
       </c>
       <c r="B137" t="n">
-        <v>86776</v>
+        <v>87020</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>717314</v>
+        <v>717298</v>
       </c>
       <c r="R137" t="n">
-        <v>6373361</v>
+        <v>6373343</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14363,44 +14362,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806000</v>
+        <v>128806319</v>
       </c>
       <c r="B138" t="n">
-        <v>87020</v>
+        <v>86975</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14410,10 +14409,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717298</v>
+        <v>717087</v>
       </c>
       <c r="R138" t="n">
-        <v>6373343</v>
+        <v>6373291</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14454,18 +14453,19 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128813071</v>
       </c>
       <c r="B2" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128815135</v>
+        <v>128815136</v>
       </c>
       <c r="B3" t="n">
-        <v>86776</v>
+        <v>86978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717476</v>
+        <v>717412</v>
       </c>
       <c r="R3" t="n">
-        <v>6373242</v>
+        <v>6373217</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,32 +880,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128806348</v>
+        <v>128806033</v>
       </c>
       <c r="B4" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717239</v>
+        <v>717315</v>
       </c>
       <c r="R4" t="n">
-        <v>6373234</v>
+        <v>6373232</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,28 +959,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806072</v>
+        <v>128806006</v>
       </c>
       <c r="B5" t="n">
-        <v>86938</v>
+        <v>92461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717289</v>
+        <v>717370</v>
       </c>
       <c r="R5" t="n">
-        <v>6373288</v>
+        <v>6373322</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,45 +1075,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128805999</v>
+        <v>128815135</v>
       </c>
       <c r="B6" t="n">
-        <v>87020</v>
+        <v>86779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717287</v>
+        <v>717476</v>
       </c>
       <c r="R6" t="n">
-        <v>6373354</v>
+        <v>6373242</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,44 +1160,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128806048</v>
+        <v>128805999</v>
       </c>
       <c r="B7" t="n">
-        <v>90942</v>
+        <v>87023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4188</v>
+        <v>3767</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717322</v>
+        <v>717287</v>
       </c>
       <c r="R7" t="n">
-        <v>6373213</v>
+        <v>6373354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,45 +1269,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128815113</v>
+        <v>128806048</v>
       </c>
       <c r="B8" t="n">
-        <v>87020</v>
+        <v>90945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3767</v>
+        <v>4188</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717317</v>
+        <v>717322</v>
       </c>
       <c r="R8" t="n">
-        <v>6373308</v>
+        <v>6373213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,22 +1354,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128813022</v>
+        <v>128806348</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>86941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717130</v>
+        <v>717239</v>
       </c>
       <c r="R9" t="n">
-        <v>6373194</v>
+        <v>6373234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1432,19 +1434,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,57 +1451,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128806006</v>
+        <v>128815113</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>87023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717370</v>
+        <v>717317</v>
       </c>
       <c r="R10" t="n">
-        <v>6373322</v>
+        <v>6373308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,57 +1548,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128815136</v>
+        <v>128806072</v>
       </c>
       <c r="B11" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717412</v>
+        <v>717289</v>
       </c>
       <c r="R11" t="n">
-        <v>6373217</v>
+        <v>6373288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,51 +1639,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128806033</v>
+        <v>128813022</v>
       </c>
       <c r="B12" t="n">
-        <v>86975</v>
+        <v>92828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1701,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717315</v>
+        <v>717130</v>
       </c>
       <c r="R12" t="n">
-        <v>6373232</v>
+        <v>6373194</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,30 +1725,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
         <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,45 +1871,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128815145</v>
+        <v>128805997</v>
       </c>
       <c r="B14" t="n">
-        <v>86941</v>
+        <v>87023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037417</v>
+        <v>3767</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717299</v>
+        <v>717416</v>
       </c>
       <c r="R14" t="n">
-        <v>6373241</v>
+        <v>6373282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,51 +1950,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128813050</v>
+        <v>128806003</v>
       </c>
       <c r="B15" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717330</v>
+        <v>717431</v>
       </c>
       <c r="R15" t="n">
-        <v>6373140</v>
+        <v>6373255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,19 +2036,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2064,57 +2053,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128813054</v>
+        <v>128815153</v>
       </c>
       <c r="B16" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717402</v>
+        <v>717341</v>
       </c>
       <c r="R16" t="n">
-        <v>6373098</v>
+        <v>6373251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,19 +2133,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2171,12 +2150,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2186,7 +2165,7 @@
         <v>128806343</v>
       </c>
       <c r="B17" t="n">
-        <v>86729</v>
+        <v>86732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,32 +2268,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128815153</v>
+        <v>128815145</v>
       </c>
       <c r="B18" t="n">
-        <v>86938</v>
+        <v>86944</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>6037417</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2324,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717341</v>
+        <v>717299</v>
       </c>
       <c r="R18" t="n">
-        <v>6373251</v>
+        <v>6373241</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,6 +2347,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2386,32 +2366,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128805997</v>
+        <v>128813050</v>
       </c>
       <c r="B19" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2421,10 +2401,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717416</v>
+        <v>717330</v>
       </c>
       <c r="R19" t="n">
-        <v>6373282</v>
+        <v>6373140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,9 +2434,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,44 +2461,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128806003</v>
+        <v>128813054</v>
       </c>
       <c r="B20" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717431</v>
+        <v>717402</v>
       </c>
       <c r="R20" t="n">
-        <v>6373255</v>
+        <v>6373098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,9 +2541,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2568,12 +2568,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
         <v>128813032</v>
       </c>
       <c r="B21" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128806324</v>
       </c>
       <c r="B22" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>128806027</v>
       </c>
       <c r="B23" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>128806029</v>
       </c>
       <c r="B24" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,45 +2981,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128815134</v>
+        <v>128806311</v>
       </c>
       <c r="B25" t="n">
-        <v>86776</v>
+        <v>87023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
         <v>717316</v>
       </c>
       <c r="R25" t="n">
-        <v>6373365</v>
+        <v>6373307</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,57 +3066,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128806311</v>
+        <v>128815134</v>
       </c>
       <c r="B26" t="n">
-        <v>87020</v>
+        <v>86779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
         <v>717316</v>
       </c>
       <c r="R26" t="n">
-        <v>6373307</v>
+        <v>6373365</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3178,7 +3178,7 @@
         <v>128813028</v>
       </c>
       <c r="B27" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,54 +3282,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128806042</v>
+        <v>128815122</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>87023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>3767</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717134</v>
+        <v>717534</v>
       </c>
       <c r="R28" t="n">
-        <v>6373159</v>
+        <v>6373182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3370,29 +3361,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128815122</v>
+        <v>128805998</v>
       </c>
       <c r="B29" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3420,14 +3410,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717534</v>
+        <v>717299</v>
       </c>
       <c r="R29" t="n">
-        <v>6373182</v>
+        <v>6373359</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3474,57 +3464,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128805998</v>
+        <v>128806042</v>
       </c>
       <c r="B30" t="n">
-        <v>87020</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3767</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717299</v>
+        <v>717134</v>
       </c>
       <c r="R30" t="n">
-        <v>6373359</v>
+        <v>6373159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3565,6 +3564,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>128813051</v>
       </c>
       <c r="B31" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,45 +3690,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128815154</v>
+        <v>128813070</v>
       </c>
       <c r="B32" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717416</v>
+        <v>717323</v>
       </c>
       <c r="R32" t="n">
-        <v>6373159</v>
+        <v>6373241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,9 +3758,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3775,44 +3785,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128806349</v>
+        <v>128813068</v>
       </c>
       <c r="B33" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3822,10 +3832,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717337</v>
+        <v>717085</v>
       </c>
       <c r="R33" t="n">
-        <v>6373337</v>
+        <v>6373275</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3855,9 +3865,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3872,22 +3892,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128806351</v>
+        <v>128815154</v>
       </c>
       <c r="B34" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,14 +3935,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717390</v>
+        <v>717416</v>
       </c>
       <c r="R34" t="n">
-        <v>6373317</v>
+        <v>6373159</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,44 +3989,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128806002</v>
+        <v>128806349</v>
       </c>
       <c r="B35" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4016,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717297</v>
+        <v>717337</v>
       </c>
       <c r="R35" t="n">
-        <v>6373295</v>
+        <v>6373337</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,44 +4086,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128813070</v>
+        <v>128806351</v>
       </c>
       <c r="B36" t="n">
-        <v>86997</v>
+        <v>86941</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4113,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>717323</v>
+        <v>717390</v>
       </c>
       <c r="R36" t="n">
-        <v>6373241</v>
+        <v>6373317</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4146,19 +4166,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4173,22 +4183,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128813068</v>
+        <v>128806002</v>
       </c>
       <c r="B37" t="n">
-        <v>86997</v>
+        <v>87023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4196,21 +4206,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4220,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>717085</v>
+        <v>717297</v>
       </c>
       <c r="R37" t="n">
-        <v>6373275</v>
+        <v>6373295</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,19 +4263,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,12 +4280,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
         <v>128806025</v>
       </c>
       <c r="B38" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>128806317</v>
       </c>
       <c r="B39" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>128815143</v>
       </c>
       <c r="B40" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>128815114</v>
       </c>
       <c r="B41" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>128813065</v>
       </c>
       <c r="B42" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>128815140</v>
       </c>
       <c r="B43" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>128813036</v>
       </c>
       <c r="B44" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>128806035</v>
       </c>
       <c r="B45" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5087,32 +5087,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128806053</v>
+        <v>128813067</v>
       </c>
       <c r="B46" t="n">
-        <v>86800</v>
+        <v>87000</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>717382</v>
+        <v>717325</v>
       </c>
       <c r="R46" t="n">
-        <v>6373309</v>
+        <v>6373229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,9 +5155,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5172,22 +5182,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128806345</v>
+        <v>128806053</v>
       </c>
       <c r="B47" t="n">
-        <v>86938</v>
+        <v>86803</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5195,21 +5205,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5219,10 +5229,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>717170</v>
+        <v>717382</v>
       </c>
       <c r="R47" t="n">
-        <v>6373195</v>
+        <v>6373309</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,44 +5279,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128813067</v>
+        <v>128806345</v>
       </c>
       <c r="B48" t="n">
-        <v>86997</v>
+        <v>86941</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5316,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>717325</v>
+        <v>717170</v>
       </c>
       <c r="R48" t="n">
-        <v>6373229</v>
+        <v>6373195</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,19 +5359,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5376,12 +5376,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5391,7 +5391,7 @@
         <v>128813046</v>
       </c>
       <c r="B49" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>128813040</v>
       </c>
       <c r="B50" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5602,45 +5602,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128806069</v>
+        <v>128815131</v>
       </c>
       <c r="B51" t="n">
-        <v>86938</v>
+        <v>91059</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717117</v>
+        <v>717416</v>
       </c>
       <c r="R51" t="n">
-        <v>6373208</v>
+        <v>6373162</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,69 +5675,75 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I mossa, gran mest. Tall nära</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128806074</v>
+        <v>128815141</v>
       </c>
       <c r="B52" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717445</v>
+        <v>717505</v>
       </c>
       <c r="R52" t="n">
-        <v>6373269</v>
+        <v>6373241</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,57 +5790,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128815131</v>
+        <v>128806334</v>
       </c>
       <c r="B53" t="n">
-        <v>91056</v>
+        <v>90984</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1357</v>
+        <v>3286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>717416</v>
+        <v>717324</v>
       </c>
       <c r="R53" t="n">
-        <v>6373162</v>
+        <v>6373355</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5869,75 +5875,69 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>I mossa, gran mest. Tall nära</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128815141</v>
+        <v>128806069</v>
       </c>
       <c r="B54" t="n">
-        <v>86997</v>
+        <v>86941</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>717505</v>
+        <v>717117</v>
       </c>
       <c r="R54" t="n">
-        <v>6373241</v>
+        <v>6373208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5984,44 +5984,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128806334</v>
+        <v>128806074</v>
       </c>
       <c r="B55" t="n">
-        <v>90981</v>
+        <v>86941</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>717324</v>
+        <v>717445</v>
       </c>
       <c r="R55" t="n">
-        <v>6373355</v>
+        <v>6373269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6081,12 +6081,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6096,7 +6096,7 @@
         <v>128813042</v>
       </c>
       <c r="B56" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>128806034</v>
       </c>
       <c r="B57" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128806322</v>
+        <v>128806330</v>
       </c>
       <c r="B58" t="n">
-        <v>86975</v>
+        <v>107571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6309,21 +6309,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>717234</v>
+        <v>717069</v>
       </c>
       <c r="R58" t="n">
-        <v>6373222</v>
+        <v>6373282</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6377,7 +6377,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6396,45 +6395,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128815152</v>
+        <v>128806322</v>
       </c>
       <c r="B59" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>717329</v>
+        <v>717234</v>
       </c>
       <c r="R59" t="n">
-        <v>6373260</v>
+        <v>6373222</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6475,63 +6474,64 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128806054</v>
+        <v>128815116</v>
       </c>
       <c r="B60" t="n">
-        <v>86800</v>
+        <v>87023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>717273</v>
+        <v>717420</v>
       </c>
       <c r="R60" t="n">
-        <v>6373345</v>
+        <v>6373147</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6578,22 +6578,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128815148</v>
+        <v>128815152</v>
       </c>
       <c r="B61" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>717239</v>
+        <v>717329</v>
       </c>
       <c r="R61" t="n">
-        <v>6373262</v>
+        <v>6373260</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6687,45 +6687,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128815116</v>
+        <v>128806054</v>
       </c>
       <c r="B62" t="n">
-        <v>87020</v>
+        <v>86803</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>717420</v>
+        <v>717273</v>
       </c>
       <c r="R62" t="n">
-        <v>6373147</v>
+        <v>6373345</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,57 +6772,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128806330</v>
+        <v>128815148</v>
       </c>
       <c r="B63" t="n">
-        <v>107566</v>
+        <v>86941</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>3674</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>717069</v>
+        <v>717239</v>
       </c>
       <c r="R63" t="n">
-        <v>6373282</v>
+        <v>6373262</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6869,44 +6869,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128813079</v>
+        <v>128813066</v>
       </c>
       <c r="B64" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>717315</v>
+        <v>717515</v>
       </c>
       <c r="R64" t="n">
-        <v>6373221</v>
+        <v>6373166</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6988,32 +6988,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128806350</v>
+        <v>128806333</v>
       </c>
       <c r="B65" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>717330</v>
+        <v>717331</v>
       </c>
       <c r="R65" t="n">
-        <v>6373328</v>
+        <v>6373327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7088,7 +7088,7 @@
         <v>128806326</v>
       </c>
       <c r="B66" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7182,32 +7182,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128813012</v>
+        <v>128813079</v>
       </c>
       <c r="B67" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>717435</v>
+        <v>717315</v>
       </c>
       <c r="R67" t="n">
-        <v>6373156</v>
+        <v>6373221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7289,32 +7289,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128813066</v>
+        <v>128806350</v>
       </c>
       <c r="B68" t="n">
-        <v>86997</v>
+        <v>86941</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>717515</v>
+        <v>717330</v>
       </c>
       <c r="R68" t="n">
-        <v>6373166</v>
+        <v>6373328</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7357,19 +7357,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7384,22 +7374,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128806333</v>
+        <v>128813012</v>
       </c>
       <c r="B69" t="n">
-        <v>86997</v>
+        <v>87023</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7407,21 +7397,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7431,10 +7421,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>717331</v>
+        <v>717435</v>
       </c>
       <c r="R69" t="n">
-        <v>6373327</v>
+        <v>6373156</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7464,9 +7454,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7481,22 +7481,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128813044</v>
+        <v>128806342</v>
       </c>
       <c r="B70" t="n">
-        <v>86975</v>
+        <v>86732</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7504,34 +7504,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>717135</v>
+        <v>717179</v>
       </c>
       <c r="R70" t="n">
-        <v>6373174</v>
+        <v>6373227</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7561,19 +7564,14 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7582,28 +7580,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128806036</v>
+        <v>128813044</v>
       </c>
       <c r="B71" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7635,10 +7634,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>717449</v>
+        <v>717135</v>
       </c>
       <c r="R71" t="n">
-        <v>6373281</v>
+        <v>6373174</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7668,40 +7667,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128806342</v>
+        <v>128806036</v>
       </c>
       <c r="B72" t="n">
-        <v>86729</v>
+        <v>86978</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7709,37 +7717,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>249278</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>717179</v>
+        <v>717449</v>
       </c>
       <c r="R72" t="n">
-        <v>6373227</v>
+        <v>6373281</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7774,11 +7779,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7792,12 +7792,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7807,7 +7807,7 @@
         <v>128806046</v>
       </c>
       <c r="B73" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8115,45 +8115,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128815128</v>
+        <v>128813055</v>
       </c>
       <c r="B76" t="n">
-        <v>91056</v>
+        <v>98690</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1357</v>
+        <v>219874</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>717418</v>
+        <v>717326</v>
       </c>
       <c r="R76" t="n">
-        <v>6373171</v>
+        <v>6373144</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8183,40 +8183,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128806047</v>
+        <v>128815128</v>
       </c>
       <c r="B77" t="n">
-        <v>86997</v>
+        <v>91059</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8224,34 +8233,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>717290</v>
+        <v>717418</v>
       </c>
       <c r="R77" t="n">
-        <v>6373221</v>
+        <v>6373171</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8292,28 +8301,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128806316</v>
+        <v>128806047</v>
       </c>
       <c r="B78" t="n">
-        <v>86822</v>
+        <v>87000</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8321,37 +8331,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>717125</v>
+        <v>717290</v>
       </c>
       <c r="R78" t="n">
-        <v>6373250</v>
+        <v>6373221</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8392,29 +8399,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128813077</v>
+        <v>128806316</v>
       </c>
       <c r="B79" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8440,16 +8446,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>717116</v>
+        <v>717125</v>
       </c>
       <c r="R79" t="n">
-        <v>6373207</v>
+        <v>6373250</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8479,71 +8488,62 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128813055</v>
+        <v>128813077</v>
       </c>
       <c r="B80" t="n">
-        <v>98685</v>
+        <v>86825</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219874</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>717326</v>
+        <v>717116</v>
       </c>
       <c r="R80" t="n">
-        <v>6373144</v>
+        <v>6373207</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128806067</v>
+        <v>128806001</v>
       </c>
       <c r="B81" t="n">
-        <v>86938</v>
+        <v>87023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>717298</v>
+        <v>717159</v>
       </c>
       <c r="R81" t="n">
-        <v>6373345</v>
+        <v>6373378</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128806001</v>
+        <v>128815117</v>
       </c>
       <c r="B82" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8753,14 +8753,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>717159</v>
+        <v>717416</v>
       </c>
       <c r="R82" t="n">
-        <v>6373378</v>
+        <v>6373167</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8807,57 +8807,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128815117</v>
+        <v>128806067</v>
       </c>
       <c r="B83" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>717416</v>
+        <v>717298</v>
       </c>
       <c r="R83" t="n">
-        <v>6373167</v>
+        <v>6373345</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8904,12 +8904,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8919,7 +8919,7 @@
         <v>128806026</v>
       </c>
       <c r="B84" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>128806031</v>
       </c>
       <c r="B85" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9112,32 +9112,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128806318</v>
+        <v>128813061</v>
       </c>
       <c r="B86" t="n">
-        <v>86975</v>
+        <v>86894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>717062</v>
+        <v>717085</v>
       </c>
       <c r="R86" t="n">
-        <v>6373304</v>
+        <v>6373261</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9180,75 +9180,84 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128815130</v>
+        <v>128806318</v>
       </c>
       <c r="B87" t="n">
-        <v>91056</v>
+        <v>86978</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>717326</v>
+        <v>717062</v>
       </c>
       <c r="R87" t="n">
-        <v>6373267</v>
+        <v>6373304</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9296,57 +9305,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128813078</v>
+        <v>128815156</v>
       </c>
       <c r="B88" t="n">
-        <v>86822</v>
+        <v>86941</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>717243</v>
+        <v>717444</v>
       </c>
       <c r="R88" t="n">
-        <v>6373192</v>
+        <v>6373273</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9376,19 +9385,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9403,65 +9402,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128806007</v>
+        <v>128815120</v>
       </c>
       <c r="B89" t="n">
-        <v>57720</v>
+        <v>87023</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>3767</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>717083</v>
+        <v>717479</v>
       </c>
       <c r="R89" t="n">
-        <v>6373260</v>
+        <v>6373226</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9508,57 +9499,57 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128815156</v>
+        <v>128813078</v>
       </c>
       <c r="B90" t="n">
-        <v>86938</v>
+        <v>86825</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>717444</v>
+        <v>717243</v>
       </c>
       <c r="R90" t="n">
-        <v>6373273</v>
+        <v>6373192</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9588,9 +9579,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9605,22 +9606,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128815120</v>
+        <v>128815130</v>
       </c>
       <c r="B91" t="n">
-        <v>87020</v>
+        <v>91059</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9628,21 +9629,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9652,10 +9653,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>717479</v>
+        <v>717326</v>
       </c>
       <c r="R91" t="n">
-        <v>6373226</v>
+        <v>6373267</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9696,6 +9697,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9714,45 +9716,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128813061</v>
+        <v>128806007</v>
       </c>
       <c r="B92" t="n">
-        <v>86891</v>
+        <v>57720</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>248956</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>717085</v>
+        <v>717083</v>
       </c>
       <c r="R92" t="n">
-        <v>6373261</v>
+        <v>6373260</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9782,19 +9792,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9809,44 +9809,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128806071</v>
+        <v>128813069</v>
       </c>
       <c r="B93" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9856,10 +9856,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>717287</v>
+        <v>717134</v>
       </c>
       <c r="R93" t="n">
-        <v>6373292</v>
+        <v>6373192</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9889,9 +9889,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9906,22 +9916,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128815112</v>
+        <v>128813074</v>
       </c>
       <c r="B94" t="n">
-        <v>87020</v>
+        <v>87035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9929,34 +9939,30 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>433</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>717270</v>
+        <v>717185</v>
       </c>
       <c r="R94" t="n">
-        <v>6373304</v>
+        <v>6373128</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9986,9 +9992,24 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10003,44 +10024,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128815123</v>
+        <v>128815109</v>
       </c>
       <c r="B95" t="n">
-        <v>87020</v>
+        <v>86921</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10050,10 +10071,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>717500</v>
+        <v>717314</v>
       </c>
       <c r="R95" t="n">
-        <v>6373237</v>
+        <v>6373229</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10112,45 +10133,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128815118</v>
+        <v>128813076</v>
       </c>
       <c r="B96" t="n">
-        <v>87020</v>
+        <v>90290</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3767</v>
+        <v>245042</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>717431</v>
+        <v>717322</v>
       </c>
       <c r="R96" t="n">
-        <v>6373173</v>
+        <v>6373147</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10180,61 +10204,72 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128815137</v>
+        <v>128815112</v>
       </c>
       <c r="B97" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10244,10 +10279,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>717433</v>
+        <v>717270</v>
       </c>
       <c r="R97" t="n">
-        <v>6373170</v>
+        <v>6373304</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10288,7 +10323,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10307,32 +10341,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128813052</v>
+        <v>128806071</v>
       </c>
       <c r="B98" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10342,10 +10376,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>717411</v>
+        <v>717287</v>
       </c>
       <c r="R98" t="n">
-        <v>6373077</v>
+        <v>6373292</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10375,19 +10409,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>09:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10402,60 +10426,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128813076</v>
+        <v>128815123</v>
       </c>
       <c r="B99" t="n">
-        <v>90287</v>
+        <v>87023</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>245042</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>717322</v>
+        <v>717500</v>
       </c>
       <c r="R99" t="n">
-        <v>6373147</v>
+        <v>6373237</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10485,50 +10506,39 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128813069</v>
+        <v>128815118</v>
       </c>
       <c r="B100" t="n">
-        <v>86997</v>
+        <v>87023</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10536,34 +10546,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>717134</v>
+        <v>717431</v>
       </c>
       <c r="R100" t="n">
-        <v>6373192</v>
+        <v>6373173</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10593,19 +10603,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10620,53 +10620,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128813074</v>
+        <v>128815137</v>
       </c>
       <c r="B101" t="n">
-        <v>87032</v>
+        <v>86978</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>717185</v>
+        <v>717433</v>
       </c>
       <c r="R101" t="n">
-        <v>6373128</v>
+        <v>6373170</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10696,54 +10700,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Brun KOH reaktion på hattkant, luktar malt.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128815109</v>
+        <v>128813052</v>
       </c>
       <c r="B102" t="n">
-        <v>86918</v>
+        <v>86978</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10751,34 +10741,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>717314</v>
+        <v>717411</v>
       </c>
       <c r="R102" t="n">
-        <v>6373229</v>
+        <v>6373077</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10808,9 +10798,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10825,12 +10825,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10840,7 +10840,7 @@
         <v>128815151</v>
       </c>
       <c r="B103" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>128815149</v>
       </c>
       <c r="B104" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11031,10 +11031,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128815129</v>
+        <v>128815110</v>
       </c>
       <c r="B105" t="n">
-        <v>91056</v>
+        <v>87023</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11042,21 +11042,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>717424</v>
+        <v>717281</v>
       </c>
       <c r="R105" t="n">
-        <v>6373165</v>
+        <v>6373300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11128,45 +11128,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128815110</v>
+        <v>128806323</v>
       </c>
       <c r="B106" t="n">
-        <v>87020</v>
+        <v>86978</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>717281</v>
+        <v>717241</v>
       </c>
       <c r="R106" t="n">
-        <v>6373300</v>
+        <v>6373264</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11207,66 +11207,64 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128813073</v>
+        <v>128806028</v>
       </c>
       <c r="B107" t="n">
-        <v>92847</v>
+        <v>86978</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5964</v>
+        <v>6003295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>717453</v>
+        <v>717179</v>
       </c>
       <c r="R107" t="n">
-        <v>6373125</v>
+        <v>6373374</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11296,19 +11294,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11324,22 +11312,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128806323</v>
+        <v>128806320</v>
       </c>
       <c r="B108" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11371,10 +11359,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>717241</v>
+        <v>717131</v>
       </c>
       <c r="R108" t="n">
-        <v>6373264</v>
+        <v>6373249</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11434,45 +11422,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128806028</v>
+        <v>128815129</v>
       </c>
       <c r="B109" t="n">
-        <v>86975</v>
+        <v>91059</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>717179</v>
+        <v>717424</v>
       </c>
       <c r="R109" t="n">
-        <v>6373374</v>
+        <v>6373165</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11513,64 +11501,66 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128806320</v>
+        <v>128813073</v>
       </c>
       <c r="B110" t="n">
-        <v>86975</v>
+        <v>92852</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>717131</v>
+        <v>717453</v>
       </c>
       <c r="R110" t="n">
-        <v>6373249</v>
+        <v>6373125</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11600,9 +11590,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11618,57 +11618,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128815121</v>
+        <v>128813568</v>
       </c>
       <c r="B111" t="n">
-        <v>87020</v>
+        <v>86921</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3767</v>
+        <v>473</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>717499</v>
+        <v>717322</v>
       </c>
       <c r="R111" t="n">
-        <v>6373239</v>
+        <v>6373203</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11698,9 +11698,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11715,22 +11725,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128806313</v>
+        <v>128815121</v>
       </c>
       <c r="B112" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11758,14 +11768,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>717369</v>
+        <v>717499</v>
       </c>
       <c r="R112" t="n">
-        <v>6373319</v>
+        <v>6373239</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11812,44 +11822,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128813568</v>
+        <v>128806313</v>
       </c>
       <c r="B113" t="n">
-        <v>86918</v>
+        <v>87023</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>473</v>
+        <v>3767</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11859,10 +11869,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>717322</v>
+        <v>717369</v>
       </c>
       <c r="R113" t="n">
-        <v>6373203</v>
+        <v>6373319</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11892,19 +11902,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11919,60 +11919,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128806055</v>
+        <v>128813063</v>
       </c>
       <c r="B114" t="n">
-        <v>86729</v>
+        <v>92280</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>249278</v>
+        <v>232138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>717283</v>
+        <v>717511</v>
       </c>
       <c r="R114" t="n">
-        <v>6373299</v>
+        <v>6373145</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12002,14 +11999,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Inga aspar inom 20 meter.</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12018,64 +12020,66 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128815139</v>
+        <v>128806055</v>
       </c>
       <c r="B115" t="n">
-        <v>86891</v>
+        <v>86732</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>248956</v>
+        <v>249278</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>717313</v>
+        <v>717283</v>
       </c>
       <c r="R115" t="n">
-        <v>6373361</v>
+        <v>6373299</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12110,34 +12114,40 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Inga aspar inom 20 meter.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128813063</v>
+        <v>128815139</v>
       </c>
       <c r="B116" t="n">
-        <v>92275</v>
+        <v>86894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12145,34 +12155,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>232138</v>
+        <v>248956</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>717511</v>
+        <v>717313</v>
       </c>
       <c r="R116" t="n">
-        <v>6373145</v>
+        <v>6373361</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12202,19 +12212,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:33</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12229,12 +12229,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12244,7 +12244,7 @@
         <v>128813048</v>
       </c>
       <c r="B117" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12348,32 +12348,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128806340</v>
+        <v>128806315</v>
       </c>
       <c r="B118" t="n">
-        <v>86800</v>
+        <v>86825</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>717314</v>
+        <v>717165</v>
       </c>
       <c r="R118" t="n">
-        <v>6373345</v>
+        <v>6373195</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12448,7 +12448,7 @@
         <v>128813030</v>
       </c>
       <c r="B119" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12552,32 +12552,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128806312</v>
+        <v>128806331</v>
       </c>
       <c r="B120" t="n">
-        <v>87020</v>
+        <v>90359</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3767</v>
+        <v>6292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>717332</v>
+        <v>717106</v>
       </c>
       <c r="R120" t="n">
-        <v>6373350</v>
+        <v>6373238</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128815111</v>
+        <v>128806312</v>
       </c>
       <c r="B121" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12680,14 +12680,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>717318</v>
+        <v>717332</v>
       </c>
       <c r="R121" t="n">
-        <v>6373242</v>
+        <v>6373350</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12734,22 +12734,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128813014</v>
+        <v>128815111</v>
       </c>
       <c r="B122" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12777,14 +12777,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>717462</v>
+        <v>717318</v>
       </c>
       <c r="R122" t="n">
-        <v>6373231</v>
+        <v>6373242</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12814,19 +12814,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>09:05</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12841,22 +12831,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128813056</v>
+        <v>128806347</v>
       </c>
       <c r="B123" t="n">
-        <v>98685</v>
+        <v>86941</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12864,21 +12854,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12888,10 +12878,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>717484</v>
+        <v>717092</v>
       </c>
       <c r="R123" t="n">
-        <v>6373174</v>
+        <v>6373322</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12921,19 +12911,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:12</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12948,44 +12928,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128806032</v>
+        <v>128813014</v>
       </c>
       <c r="B124" t="n">
-        <v>86975</v>
+        <v>87023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12995,10 +12975,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>717081</v>
+        <v>717462</v>
       </c>
       <c r="R124" t="n">
-        <v>6373276</v>
+        <v>6373231</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13028,40 +13008,49 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128806347</v>
+        <v>128806340</v>
       </c>
       <c r="B125" t="n">
-        <v>86938</v>
+        <v>86803</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13069,21 +13058,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13093,10 +13082,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>717092</v>
+        <v>717314</v>
       </c>
       <c r="R125" t="n">
-        <v>6373322</v>
+        <v>6373345</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13155,32 +13144,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128806315</v>
+        <v>128813056</v>
       </c>
       <c r="B126" t="n">
-        <v>86822</v>
+        <v>98690</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>424</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13190,10 +13179,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>717165</v>
+        <v>717484</v>
       </c>
       <c r="R126" t="n">
-        <v>6373195</v>
+        <v>6373174</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13223,9 +13212,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13240,44 +13239,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128806331</v>
+        <v>128806032</v>
       </c>
       <c r="B127" t="n">
-        <v>90356</v>
+        <v>86978</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6292</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13286,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>717106</v>
+        <v>717081</v>
       </c>
       <c r="R127" t="n">
-        <v>6373238</v>
+        <v>6373276</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13331,28 +13330,29 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128815126</v>
+        <v>128813018</v>
       </c>
       <c r="B128" t="n">
-        <v>87041</v>
+        <v>110784</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13360,30 +13360,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3624</v>
+        <v>219711</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>717337</v>
+        <v>717512</v>
       </c>
       <c r="R128" t="n">
-        <v>6373382</v>
+        <v>6373149</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13413,9 +13417,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13430,44 +13444,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128813018</v>
+        <v>128813049</v>
       </c>
       <c r="B129" t="n">
-        <v>110779</v>
+        <v>86978</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219711</v>
+        <v>6003295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13477,10 +13491,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>717512</v>
+        <v>717330</v>
       </c>
       <c r="R129" t="n">
-        <v>6373149</v>
+        <v>6373178</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13512,7 +13526,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13522,7 +13536,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13549,45 +13563,41 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128813049</v>
+        <v>128815126</v>
       </c>
       <c r="B130" t="n">
-        <v>86975</v>
+        <v>87044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003295</v>
+        <v>3624</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>717330</v>
+        <v>717337</v>
       </c>
       <c r="R130" t="n">
-        <v>6373178</v>
+        <v>6373382</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13617,19 +13627,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13644,60 +13644,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128813075</v>
+        <v>128813080</v>
       </c>
       <c r="B131" t="n">
-        <v>86891</v>
+        <v>86941</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>717344</v>
+        <v>717456</v>
       </c>
       <c r="R131" t="n">
-        <v>6373206</v>
+        <v>6373273</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13729,7 +13726,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -13739,12 +13736,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13753,7 +13745,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -13772,45 +13763,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128813080</v>
+        <v>128815115</v>
       </c>
       <c r="B132" t="n">
-        <v>86938</v>
+        <v>87023</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>717456</v>
+        <v>717424</v>
       </c>
       <c r="R132" t="n">
-        <v>6373273</v>
+        <v>6373147</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13840,19 +13831,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>08:59</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>08:59</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13867,22 +13848,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128815115</v>
+        <v>128813075</v>
       </c>
       <c r="B133" t="n">
-        <v>87020</v>
+        <v>86894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13890,34 +13871,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3767</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>717424</v>
+        <v>717344</v>
       </c>
       <c r="R133" t="n">
-        <v>6373147</v>
+        <v>6373206</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13947,29 +13931,45 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Negativ KOH hattkant och bulbkant, gult basalmycel.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13979,7 +13979,7 @@
         <v>128815155</v>
       </c>
       <c r="B134" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14073,45 +14073,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128815133</v>
+        <v>128806319</v>
       </c>
       <c r="B135" t="n">
-        <v>86776</v>
+        <v>86978</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>717314</v>
+        <v>717087</v>
       </c>
       <c r="R135" t="n">
-        <v>6373361</v>
+        <v>6373291</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14152,18 +14152,19 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14173,7 +14174,7 @@
         <v>128813027</v>
       </c>
       <c r="B136" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14280,7 +14281,7 @@
         <v>128806000</v>
       </c>
       <c r="B137" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14374,45 +14375,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128806319</v>
+        <v>128815133</v>
       </c>
       <c r="B138" t="n">
-        <v>86975</v>
+        <v>86779</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>717087</v>
+        <v>717314</v>
       </c>
       <c r="R138" t="n">
-        <v>6373291</v>
+        <v>6373361</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14453,64 +14454,63 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128815124</v>
+        <v>128806066</v>
       </c>
       <c r="B139" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>717467</v>
+        <v>717348</v>
       </c>
       <c r="R139" t="n">
-        <v>6373240</v>
+        <v>6373330</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14557,22 +14557,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128806066</v>
+        <v>128806070</v>
       </c>
       <c r="B140" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14604,10 +14604,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>717348</v>
+        <v>717289</v>
       </c>
       <c r="R140" t="n">
-        <v>6373330</v>
+        <v>6373225</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128806070</v>
+        <v>128806008</v>
       </c>
       <c r="B141" t="n">
-        <v>86938</v>
+        <v>86779</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14677,21 +14677,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14701,10 +14701,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>717289</v>
+        <v>717255</v>
       </c>
       <c r="R141" t="n">
-        <v>6373225</v>
+        <v>6373321</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14763,10 +14763,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128806008</v>
+        <v>128813081</v>
       </c>
       <c r="B142" t="n">
-        <v>86776</v>
+        <v>86941</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14774,21 +14774,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14798,10 +14798,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>717255</v>
+        <v>717161</v>
       </c>
       <c r="R142" t="n">
-        <v>6373321</v>
+        <v>6373174</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14831,9 +14831,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14848,22 +14858,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128813081</v>
+        <v>128815147</v>
       </c>
       <c r="B143" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14891,14 +14901,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>717161</v>
+        <v>717312</v>
       </c>
       <c r="R143" t="n">
-        <v>6373174</v>
+        <v>6373366</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14928,19 +14938,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14955,44 +14955,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128815147</v>
+        <v>128815124</v>
       </c>
       <c r="B144" t="n">
-        <v>86938</v>
+        <v>87023</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15002,10 +15002,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>717312</v>
+        <v>717467</v>
       </c>
       <c r="R144" t="n">
-        <v>6373366</v>
+        <v>6373240</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15067,7 +15067,7 @@
         <v>128815150</v>
       </c>
       <c r="B145" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>128813064</v>
       </c>
       <c r="B146" t="n">
-        <v>91518</v>
+        <v>91521</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 43785-2024 artfynd.xlsx
+++ b/artfynd/A 43785-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128813071</v>
+        <v>128815135</v>
       </c>
       <c r="B2" t="n">
-        <v>87000</v>
+        <v>86782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717455</v>
+        <v>717476</v>
       </c>
       <c r="R2" t="n">
-        <v>6373115</v>
+        <v>6373242</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,57 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128815136</v>
+        <v>128805999</v>
       </c>
       <c r="B3" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717412</v>
+        <v>717287</v>
       </c>
       <c r="R3" t="n">
-        <v>6373217</v>
+        <v>6373354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,51 +851,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128806033</v>
+        <v>128806048</v>
       </c>
       <c r="B4" t="n">
-        <v>86978</v>
+        <v>90948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>4188</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717315</v>
+        <v>717322</v>
       </c>
       <c r="R4" t="n">
-        <v>6373232</v>
+        <v>6373213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,52 +959,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128806006</v>
+        <v>128815113</v>
       </c>
       <c r="B5" t="n">
-        <v>92461</v>
+        <v>87026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>3767</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717370</v>
+        <v>717317</v>
       </c>
       <c r="R5" t="n">
-        <v>6373322</v>
+        <v>6373308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128815135</v>
+        <v>128813022</v>
       </c>
       <c r="B6" t="n">
-        <v>86779</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717476</v>
+        <v>717130</v>
       </c>
       <c r="R6" t="n">
-        <v>6373242</v>
+        <v>6373194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,9 +1131,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128805999</v>
+        <v>128813071</v>
       </c>
       <c r="B7" t="n">
-        <v>87023</v>
+        <v>87003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717287</v>
+        <v>717455</v>
       </c>
       <c r="R7" t="n">
-        <v>6373354</v>
+        <v>6373115</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,9 +1238,19 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,22 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806048</v>
+        <v>128806348</v>
       </c>
       <c r="B8" t="n">
-        <v>90945</v>
+        <v>86944</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717322</v>
+        <v>717239</v>
       </c>
       <c r="R8" t="n">
-        <v>6373213</v>
+        <v>6373234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,22 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128806348</v>
+        <v>128806072</v>
       </c>
       <c r="B9" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717239</v>
+        <v>717289</v>
       </c>
       <c r="R9" t="n">
-        <v>6373234</v>
+        <v>6373288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,57 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128815113</v>
+        <v>128806006</v>
       </c>
       <c r="B10" t="n">
-        <v>87023</v>
+        <v>92464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3767</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717317</v>
+        <v>717370</v>
       </c>
       <c r="R10" t="n">
-        <v>6373308</v>
+        <v>6373322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,57 +1556,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128806072</v>
+        <v>128815136</v>
       </c>
       <c r="B11" t="n">
-        <v>86941</v>
+        <v>86981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717289</v>
+        <v>717412</v>
       </c>
       <c r="R11" t="n">
-        <v>6373288</v>
+        <v>6373217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,50 +1647,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128813022</v>
+        <v>128806033</v>
       </c>
       <c r="B12" t="n">
-        <v>92828</v>
+        <v>86981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717130</v>
+        <v>717315</v>
       </c>
       <c r="R12" t="n">
-        <v>6373194</v>
+        <v>6373232</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1725,39 +1734,30 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
         <v>128813034</v>
       </c>
       <c r="B13" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,45 +1871,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128805997</v>
+        <v>128815153</v>
       </c>
       <c r="B14" t="n">
-        <v>87023</v>
+        <v>86944</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717416</v>
+        <v>717341</v>
       </c>
       <c r="R14" t="n">
-        <v>6373282</v>
+        <v>6373251</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,22 +1956,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128806003</v>
+        <v>128805997</v>
       </c>
       <c r="B15" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717431</v>
+        <v>717416</v>
       </c>
       <c r="R15" t="n">
-        <v>6373255</v>
+        <v>6373282</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,45 +2065,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128815153</v>
+        <v>128806003</v>
       </c>
       <c r="B16" t="n">
-        <v>86941</v>
+        <v>87026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717341</v>
+        <v>717431</v>
       </c>
       <c r="R16" t="n">
-        <v>6373251</v>
+        <v>6373255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,22 +2150,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128806343</v>
+        <v>128815145</v>
       </c>
       <c r="B17" t="n">
-        <v>86732</v>
+        <v>86947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,37 +2173,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>249278</v>
+        <v>6037417</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Gurpe Ådrebovät, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717258</v>
+        <v>717299</v>
       </c>
       <c r="R17" t="n">
-        <v>6373299</v>
+        <v>6373241</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2238,11 +2235,6 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ingen asp i området.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2256,22 +2248,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128815145</v>
+        <v>128806343</v>
       </c>
       <c r="B18" t="n">
-        <v>86944</v>
+        <v>86735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2271,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6037417</v>
+        <v>249278</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gurpe Ådrebovät, Gtl</t>
+          <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717299</v>
+        <v>717258</v>
       </c>
       <c r="R18" t="n">
-        <v>6373241</v>
+        <v>6373299</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,6 +2336,11 @@
           <t>2025-09-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ingen asp i området.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2354,12 +2354,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         <v>128813050</v>
       </c>
       <c r="B19" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>128813054</v>
       </c>
       <c r="B20" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128813032</v>
+        <v>128806311</v>
       </c>
       <c r="B21" t="n">
-        <v>86978</v>
+        <v>87026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t